--- a/Excel/一方通行/余.xlsx
+++ b/Excel/一方通行/余.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785FE8FD-3BFA-4D42-9FB3-726B6F57173F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C217906-D291-46D5-A4A4-3C110C0254C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/一方通行/余.xlsx
+++ b/Excel/一方通行/余.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C217906-D291-46D5-A4A4-3C110C0254C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1CC9D7-4749-44DB-BB93-77B1077AC2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="525">
   <si>
     <t>Id</t>
   </si>
@@ -9096,16 +9096,21 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A2:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="3" max="3" width="27.25" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -9131,10 +9136,13 @@
         <v>467</v>
       </c>
       <c r="I2" t="s">
+        <v>323</v>
+      </c>
+      <c r="J2" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -9160,6 +9168,9 @@
         <v>118</v>
       </c>
       <c r="I3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J3" t="s">
         <v>125</v>
       </c>
     </row>

--- a/Excel/一方通行/余.xlsx
+++ b/Excel/一方通行/余.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1CC9D7-4749-44DB-BB93-77B1077AC2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAA7362-A6A6-4E31-A9F0-69574671D2B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="525">
   <si>
     <t>Id</t>
   </si>
@@ -388,12 +388,6 @@
     <t>高度</t>
   </si>
   <si>
-    <t>高台单位？</t>
-  </si>
-  <si>
-    <t>地面</t>
-  </si>
-  <si>
     <t>阻挡个数</t>
   </si>
   <si>
@@ -548,12 +542,6 @@
   </si>
   <si>
     <t>Height</t>
-  </si>
-  <si>
-    <t>CanSetHigh</t>
-  </si>
-  <si>
-    <t>CanSetGround</t>
   </si>
   <si>
     <t>StopCount</t>
@@ -1886,6 +1874,22 @@
   </si>
   <si>
     <t>string</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>可部署位</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>CanSetPos</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>string[]</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>地面位</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2402,7 +2406,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BS571"/>
+  <dimension ref="A1:BR571"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -2432,22 +2436,22 @@
     <col min="34" max="34" width="13.83203125" customWidth="1"/>
     <col min="35" max="35" width="34.5" customWidth="1"/>
     <col min="36" max="37" width="9.83203125" customWidth="1"/>
-    <col min="43" max="43" width="12.5" customWidth="1"/>
-    <col min="50" max="50" width="24.33203125" customWidth="1"/>
-    <col min="52" max="52" width="17.75" customWidth="1"/>
-    <col min="53" max="53" width="7.83203125" customWidth="1"/>
-    <col min="56" max="56" width="24.25" customWidth="1"/>
-    <col min="57" max="57" width="13.25" customWidth="1"/>
-    <col min="58" max="58" width="16.08203125" customWidth="1"/>
-    <col min="59" max="59" width="8" customWidth="1"/>
-    <col min="64" max="64" width="39.58203125" customWidth="1"/>
-    <col min="65" max="65" width="14" customWidth="1"/>
-    <col min="66" max="66" width="14.83203125" customWidth="1"/>
-    <col min="67" max="70" width="14" customWidth="1"/>
-    <col min="71" max="71" width="19.1640625" customWidth="1"/>
+    <col min="42" max="42" width="12.5" customWidth="1"/>
+    <col min="49" max="49" width="24.33203125" customWidth="1"/>
+    <col min="51" max="51" width="17.75" customWidth="1"/>
+    <col min="52" max="52" width="7.83203125" customWidth="1"/>
+    <col min="55" max="55" width="24.25" customWidth="1"/>
+    <col min="56" max="56" width="13.25" customWidth="1"/>
+    <col min="57" max="57" width="16.08203125" customWidth="1"/>
+    <col min="58" max="58" width="8" customWidth="1"/>
+    <col min="63" max="63" width="39.58203125" customWidth="1"/>
+    <col min="64" max="64" width="14" customWidth="1"/>
+    <col min="65" max="65" width="14.83203125" customWidth="1"/>
+    <col min="66" max="69" width="14" customWidth="1"/>
+    <col min="70" max="70" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
         <v>5</v>
       </c>
@@ -2523,274 +2527,268 @@
       <c r="AL1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="13" t="s">
+        <v>521</v>
+      </c>
+      <c r="AN1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>33</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>34</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>35</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>36</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>37</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>38</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>39</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>40</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BC1" t="s">
         <v>41</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BD1" t="s">
         <v>42</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>43</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>44</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>45</v>
       </c>
-      <c r="BG1" t="s">
-        <v>46</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:71" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>49</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>50</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>51</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>52</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>53</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>54</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>55</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>56</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>57</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>58</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>59</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>60</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>61</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>62</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
         <v>63</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>64</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>65</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>66</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>67</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>68</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>69</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>70</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AC2" t="s">
         <v>71</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>72</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AE2" t="s">
         <v>73</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AF2" t="s">
         <v>74</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AG2" t="s">
         <v>75</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AH2" t="s">
         <v>76</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AI2" t="s">
         <v>77</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AJ2" t="s">
         <v>78</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AK2" t="s">
         <v>79</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AL2" t="s">
         <v>80</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AM2" s="13" t="s">
+        <v>522</v>
+      </c>
+      <c r="AN2" t="s">
         <v>81</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AO2" t="s">
         <v>82</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AP2" t="s">
         <v>83</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AQ2" t="s">
         <v>84</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AR2" t="s">
         <v>85</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AS2" t="s">
         <v>86</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AT2" t="s">
         <v>87</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AU2" t="s">
         <v>88</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AV2" t="s">
         <v>89</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AW2" t="s">
         <v>90</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AX2" t="s">
         <v>91</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AY2" t="s">
         <v>92</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AZ2" t="s">
         <v>93</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="BA2" t="s">
         <v>94</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BB2" t="s">
         <v>95</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BC2" t="s">
         <v>96</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BD2" t="s">
         <v>97</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BE2" t="s">
         <v>98</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BF2" t="s">
         <v>99</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BG2" t="s">
         <v>100</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BH2" t="s">
         <v>101</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BI2" t="s">
         <v>102</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BJ2" t="s">
         <v>103</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BK2" t="s">
         <v>104</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BL2" t="s">
         <v>105</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BM2" t="s">
         <v>106</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BN2" t="s">
         <v>107</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BO2" t="s">
         <v>108</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BP2" t="s">
         <v>109</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BQ2" t="s">
         <v>110</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BR2" t="s">
         <v>111</v>
       </c>
-      <c r="BP2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>114</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2798,88 +2796,88 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F3" t="s">
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H3" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="O3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Q3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="R3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="S3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="T3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="U3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="V3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="W3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="X3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Y3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Z3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AA3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AB3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AC3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AD3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AE3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AF3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AG3" t="s">
         <v>2</v>
@@ -2888,61 +2886,61 @@
         <v>2</v>
       </c>
       <c r="AI3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AJ3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AK3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AM3" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AU3" t="s">
         <v>116</v>
       </c>
-      <c r="AN3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>118</v>
-      </c>
       <c r="AV3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="AW3" t="s">
         <v>117</v>
       </c>
       <c r="AX3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AZ3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="BA3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BB3" t="s">
-        <v>122</v>
+        <v>2</v>
       </c>
       <c r="BC3" t="s">
         <v>2</v>
@@ -2954,60 +2952,57 @@
         <v>2</v>
       </c>
       <c r="BF3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BH3" t="s">
         <v>2</v>
       </c>
-      <c r="BG3" t="s">
-        <v>123</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>118</v>
-      </c>
       <c r="BI3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BJ3" t="s">
         <v>2</v>
       </c>
-      <c r="BJ3" t="s">
-        <v>124</v>
-      </c>
       <c r="BK3" t="s">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="BL3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="BM3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BN3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BO3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BP3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BQ3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BR3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:71" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F4" t="str">
         <f>"char_"&amp;E4&amp;"_"&amp;D4</f>
@@ -3056,2410 +3051,2416 @@
         <v>4</v>
       </c>
       <c r="AH4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>126</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AM4" s="13" t="s">
+        <v>524</v>
+      </c>
+      <c r="AN4">
+        <v>3</v>
+      </c>
+      <c r="AO4">
+        <v>0.5</v>
+      </c>
+      <c r="AV4">
+        <v>0.25</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>128</v>
+      </c>
+      <c r="BB4" t="s">
         <v>129</v>
       </c>
-      <c r="AI4" t="s">
-        <v>130</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AN4">
-        <v>1</v>
-      </c>
-      <c r="AO4">
-        <v>3</v>
-      </c>
-      <c r="AP4">
-        <v>0.5</v>
-      </c>
-      <c r="AW4">
-        <v>0.25</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>132</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>133</v>
-      </c>
-      <c r="BD4" t="str">
+      <c r="BC4" t="str">
         <f>"icon_"&amp;D4</f>
         <v>icon_yu</v>
       </c>
-      <c r="BE4" t="str">
+      <c r="BD4" t="str">
         <f>"half_"&amp;D4</f>
         <v>half_yu</v>
       </c>
-      <c r="BF4" t="str">
+      <c r="BE4" t="str">
         <f>D4</f>
         <v>yu</v>
       </c>
-      <c r="BG4" t="s">
+      <c r="BF4" t="s">
+        <v>130</v>
+      </c>
+      <c r="BG4">
+        <v>6</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>131</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>132</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>133</v>
+      </c>
+      <c r="BL4" t="s">
         <v>134</v>
       </c>
-      <c r="BH4">
-        <v>6</v>
-      </c>
-      <c r="BI4" t="s">
+      <c r="BM4" t="s">
         <v>135</v>
       </c>
-      <c r="BJ4" t="s">
+      <c r="BO4" t="s">
         <v>136</v>
       </c>
-      <c r="BK4" t="s">
-        <v>137</v>
-      </c>
-      <c r="BM4" t="s">
-        <v>138</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>139</v>
-      </c>
       <c r="BP4" t="s">
-        <v>140</v>
-      </c>
-      <c r="BQ4" t="s">
-        <v>140</v>
-      </c>
-      <c r="BS4">
+        <v>136</v>
+      </c>
+      <c r="BR4">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="BR8" s="11"/>
-    </row>
-    <row r="9" spans="1:71" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="AM5" s="13"/>
+    </row>
+    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="AM6" s="13"/>
+    </row>
+    <row r="8" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="BQ8" s="11"/>
+    </row>
+    <row r="9" spans="1:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D9" s="10"/>
       <c r="E9" s="9"/>
-      <c r="BO9" s="11"/>
-      <c r="BR9" s="11"/>
-    </row>
-    <row r="10" spans="1:71" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN9" s="11"/>
+      <c r="BQ9" s="11"/>
+    </row>
+    <row r="10" spans="1:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
-      <c r="BO10" s="11"/>
-      <c r="BR10" s="11"/>
-    </row>
-    <row r="11" spans="1:71" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN10" s="11"/>
+      <c r="BQ10" s="11"/>
+    </row>
+    <row r="11" spans="1:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D11" s="10"/>
       <c r="E11" s="9"/>
-      <c r="BO11" s="11"/>
-      <c r="BR11" s="11"/>
-    </row>
-    <row r="12" spans="1:71" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN11" s="11"/>
+      <c r="BQ11" s="11"/>
+    </row>
+    <row r="12" spans="1:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D12" s="10"/>
       <c r="E12" s="9"/>
-      <c r="BO12" s="11"/>
-      <c r="BR12" s="11"/>
-    </row>
-    <row r="13" spans="1:71" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN12" s="11"/>
+      <c r="BQ12" s="11"/>
+    </row>
+    <row r="13" spans="1:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D13" s="10"/>
       <c r="E13" s="9"/>
-      <c r="BO13" s="11"/>
-      <c r="BR13" s="11"/>
-    </row>
-    <row r="14" spans="1:71" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN13" s="11"/>
+      <c r="BQ13" s="11"/>
+    </row>
+    <row r="14" spans="1:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D14" s="10"/>
       <c r="E14" s="9"/>
-      <c r="BO14" s="11"/>
-      <c r="BR14" s="11"/>
-    </row>
-    <row r="15" spans="1:71" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN14" s="11"/>
+      <c r="BQ14" s="11"/>
+    </row>
+    <row r="15" spans="1:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D15" s="10"/>
       <c r="E15" s="9"/>
-      <c r="BO15" s="11"/>
-      <c r="BR15" s="11"/>
-    </row>
-    <row r="16" spans="1:71" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN15" s="11"/>
+      <c r="BQ15" s="11"/>
+    </row>
+    <row r="16" spans="1:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D16" s="10"/>
       <c r="E16" s="9"/>
-      <c r="BR16" s="11"/>
-    </row>
-    <row r="17" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ16" s="11"/>
+    </row>
+    <row r="17" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D17" s="10"/>
       <c r="E17" s="9"/>
-      <c r="BR17" s="11"/>
-    </row>
-    <row r="18" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ17" s="11"/>
+    </row>
+    <row r="18" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D18" s="10"/>
       <c r="E18" s="9"/>
-      <c r="BR18" s="11"/>
-    </row>
-    <row r="19" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ18" s="11"/>
+    </row>
+    <row r="19" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D19" s="10"/>
       <c r="E19" s="9"/>
-      <c r="BO19" s="11"/>
-      <c r="BR19" s="11"/>
-    </row>
-    <row r="20" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN19" s="11"/>
+      <c r="BQ19" s="11"/>
+    </row>
+    <row r="20" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D20" s="10"/>
       <c r="E20" s="9"/>
-      <c r="BO20" s="11"/>
-      <c r="BR20" s="11"/>
-    </row>
-    <row r="21" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN20" s="11"/>
+      <c r="BQ20" s="11"/>
+    </row>
+    <row r="21" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D21" s="10"/>
       <c r="E21" s="9"/>
-      <c r="BO21" s="11"/>
-      <c r="BR21" s="11"/>
-    </row>
-    <row r="22" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN21" s="11"/>
+      <c r="BQ21" s="11"/>
+    </row>
+    <row r="22" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D22" s="10"/>
       <c r="E22" s="9"/>
-      <c r="BO22" s="11"/>
-      <c r="BR22" s="11"/>
-    </row>
-    <row r="23" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN22" s="11"/>
+      <c r="BQ22" s="11"/>
+    </row>
+    <row r="23" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D23" s="10"/>
       <c r="E23" s="9"/>
-      <c r="BO23" s="11"/>
-      <c r="BR23" s="11"/>
-    </row>
-    <row r="24" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN23" s="11"/>
+      <c r="BQ23" s="11"/>
+    </row>
+    <row r="24" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D24" s="10"/>
       <c r="E24" s="9"/>
-      <c r="BO24" s="11"/>
-      <c r="BR24" s="11"/>
-    </row>
-    <row r="25" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN24" s="11"/>
+      <c r="BQ24" s="11"/>
+    </row>
+    <row r="25" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D25" s="10"/>
       <c r="E25" s="9"/>
-      <c r="BO25" s="11"/>
-      <c r="BR25" s="11"/>
-    </row>
-    <row r="26" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN25" s="11"/>
+      <c r="BQ25" s="11"/>
+    </row>
+    <row r="26" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D26" s="10"/>
       <c r="E26" s="9"/>
-      <c r="BO26" s="11"/>
-      <c r="BR26" s="11"/>
-    </row>
-    <row r="27" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN26" s="11"/>
+      <c r="BQ26" s="11"/>
+    </row>
+    <row r="27" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D27" s="10"/>
       <c r="E27" s="9"/>
-      <c r="BO27" s="11"/>
-      <c r="BR27" s="11"/>
-    </row>
-    <row r="28" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN27" s="11"/>
+      <c r="BQ27" s="11"/>
+    </row>
+    <row r="28" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D28" s="10"/>
       <c r="E28" s="9"/>
-      <c r="BO28" s="11"/>
-      <c r="BR28" s="11"/>
-    </row>
-    <row r="29" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN28" s="11"/>
+      <c r="BQ28" s="11"/>
+    </row>
+    <row r="29" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D29" s="10"/>
       <c r="E29" s="9"/>
-      <c r="BO29" s="11"/>
-      <c r="BR29" s="11"/>
-    </row>
-    <row r="30" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN29" s="11"/>
+      <c r="BQ29" s="11"/>
+    </row>
+    <row r="30" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D30" s="10"/>
       <c r="E30" s="9"/>
-      <c r="BO30" s="11"/>
-      <c r="BR30" s="11"/>
-    </row>
-    <row r="31" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN30" s="11"/>
+      <c r="BQ30" s="11"/>
+    </row>
+    <row r="31" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D31" s="10"/>
       <c r="E31" s="9"/>
-      <c r="BO31" s="11"/>
-      <c r="BR31" s="11"/>
-    </row>
-    <row r="32" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN31" s="11"/>
+      <c r="BQ31" s="11"/>
+    </row>
+    <row r="32" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D32" s="10"/>
       <c r="E32" s="9"/>
-      <c r="BO32" s="11"/>
-      <c r="BR32" s="11"/>
-    </row>
-    <row r="33" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN32" s="11"/>
+      <c r="BQ32" s="11"/>
+    </row>
+    <row r="33" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D33" s="10"/>
       <c r="E33" s="9"/>
-      <c r="BO33" s="11"/>
-      <c r="BR33" s="11"/>
-    </row>
-    <row r="34" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN33" s="11"/>
+      <c r="BQ33" s="11"/>
+    </row>
+    <row r="34" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D34" s="10"/>
       <c r="E34" s="9"/>
-      <c r="BO34" s="11"/>
-      <c r="BR34" s="11"/>
-    </row>
-    <row r="35" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN34" s="11"/>
+      <c r="BQ34" s="11"/>
+    </row>
+    <row r="35" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D35" s="10"/>
       <c r="E35" s="9"/>
-      <c r="BO35" s="11"/>
-      <c r="BR35" s="11"/>
-    </row>
-    <row r="36" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN35" s="11"/>
+      <c r="BQ35" s="11"/>
+    </row>
+    <row r="36" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D36" s="10"/>
       <c r="E36" s="9"/>
-      <c r="BO36" s="11"/>
-      <c r="BR36" s="11"/>
-    </row>
-    <row r="37" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN36" s="11"/>
+      <c r="BQ36" s="11"/>
+    </row>
+    <row r="37" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D37" s="10"/>
       <c r="E37" s="9"/>
-      <c r="BO37" s="11"/>
-      <c r="BR37" s="11"/>
-    </row>
-    <row r="38" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN37" s="11"/>
+      <c r="BQ37" s="11"/>
+    </row>
+    <row r="38" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D38" s="10"/>
       <c r="E38" s="9"/>
-      <c r="BO38" s="11"/>
-      <c r="BR38" s="11"/>
-    </row>
-    <row r="39" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN38" s="11"/>
+      <c r="BQ38" s="11"/>
+    </row>
+    <row r="39" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D39" s="10"/>
       <c r="E39" s="9"/>
-      <c r="BO39" s="11"/>
-      <c r="BR39" s="11"/>
-    </row>
-    <row r="40" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN39" s="11"/>
+      <c r="BQ39" s="11"/>
+    </row>
+    <row r="40" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D40" s="10"/>
       <c r="E40" s="9"/>
-      <c r="BO40" s="11"/>
-      <c r="BR40" s="11"/>
-    </row>
-    <row r="41" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN40" s="11"/>
+      <c r="BQ40" s="11"/>
+    </row>
+    <row r="41" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D41" s="10"/>
       <c r="E41" s="9"/>
-      <c r="BO41" s="11"/>
-      <c r="BR41" s="11"/>
-    </row>
-    <row r="42" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN41" s="11"/>
+      <c r="BQ41" s="11"/>
+    </row>
+    <row r="42" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D42" s="10"/>
       <c r="E42" s="9"/>
-      <c r="BO42" s="11"/>
-      <c r="BR42" s="11"/>
-    </row>
-    <row r="43" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN42" s="11"/>
+      <c r="BQ42" s="11"/>
+    </row>
+    <row r="43" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D43" s="10"/>
       <c r="E43" s="9"/>
-      <c r="BO43" s="11"/>
-      <c r="BR43" s="11"/>
-    </row>
-    <row r="44" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN43" s="11"/>
+      <c r="BQ43" s="11"/>
+    </row>
+    <row r="44" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D44" s="10"/>
       <c r="E44" s="9"/>
-      <c r="BO44" s="11"/>
-      <c r="BR44" s="11"/>
-    </row>
-    <row r="45" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN44" s="11"/>
+      <c r="BQ44" s="11"/>
+    </row>
+    <row r="45" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D45" s="10"/>
       <c r="E45" s="9"/>
-      <c r="BO45" s="11"/>
-      <c r="BR45" s="11"/>
-    </row>
-    <row r="46" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN45" s="11"/>
+      <c r="BQ45" s="11"/>
+    </row>
+    <row r="46" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D46" s="10"/>
       <c r="E46" s="9"/>
-      <c r="BO46" s="11"/>
-      <c r="BR46" s="11"/>
-    </row>
-    <row r="47" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN46" s="11"/>
+      <c r="BQ46" s="11"/>
+    </row>
+    <row r="47" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D47" s="10"/>
       <c r="E47" s="9"/>
-      <c r="BO47" s="11"/>
-      <c r="BR47" s="11"/>
-    </row>
-    <row r="48" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN47" s="11"/>
+      <c r="BQ47" s="11"/>
+    </row>
+    <row r="48" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D48" s="10"/>
       <c r="E48" s="9"/>
-      <c r="BO48" s="11"/>
-      <c r="BR48" s="11"/>
-    </row>
-    <row r="49" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN48" s="11"/>
+      <c r="BQ48" s="11"/>
+    </row>
+    <row r="49" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D49" s="10"/>
       <c r="E49" s="9"/>
-      <c r="BO49" s="11"/>
-      <c r="BR49" s="11"/>
-    </row>
-    <row r="50" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN49" s="11"/>
+      <c r="BQ49" s="11"/>
+    </row>
+    <row r="50" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D50" s="10"/>
       <c r="E50" s="9"/>
-      <c r="BO50" s="11"/>
-      <c r="BR50" s="11"/>
-    </row>
-    <row r="51" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN50" s="11"/>
+      <c r="BQ50" s="11"/>
+    </row>
+    <row r="51" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D51" s="10"/>
       <c r="E51" s="9"/>
-      <c r="BO51" s="11"/>
-      <c r="BR51" s="11"/>
-    </row>
-    <row r="52" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN51" s="11"/>
+      <c r="BQ51" s="11"/>
+    </row>
+    <row r="52" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D52" s="10"/>
       <c r="E52" s="9"/>
-      <c r="BO52" s="11"/>
-      <c r="BR52" s="11"/>
-    </row>
-    <row r="53" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN52" s="11"/>
+      <c r="BQ52" s="11"/>
+    </row>
+    <row r="53" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D53" s="10"/>
       <c r="E53" s="9"/>
-      <c r="BO53" s="11"/>
-      <c r="BR53" s="11"/>
-    </row>
-    <row r="54" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN53" s="11"/>
+      <c r="BQ53" s="11"/>
+    </row>
+    <row r="54" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D54" s="10"/>
       <c r="E54" s="9"/>
-      <c r="BO54" s="11"/>
-      <c r="BR54" s="11"/>
-    </row>
-    <row r="55" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN54" s="11"/>
+      <c r="BQ54" s="11"/>
+    </row>
+    <row r="55" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D55" s="10"/>
       <c r="E55" s="9"/>
-      <c r="BO55" s="11"/>
-      <c r="BR55" s="11"/>
-    </row>
-    <row r="56" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN55" s="11"/>
+      <c r="BQ55" s="11"/>
+    </row>
+    <row r="56" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D56" s="10"/>
       <c r="E56" s="9"/>
-      <c r="BO56" s="11"/>
-      <c r="BR56" s="11"/>
-    </row>
-    <row r="57" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN56" s="11"/>
+      <c r="BQ56" s="11"/>
+    </row>
+    <row r="57" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D57" s="10"/>
       <c r="E57" s="9"/>
-      <c r="BO57" s="11"/>
-      <c r="BR57" s="11"/>
-    </row>
-    <row r="58" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN57" s="11"/>
+      <c r="BQ57" s="11"/>
+    </row>
+    <row r="58" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D58" s="10"/>
       <c r="E58" s="9"/>
-      <c r="BO58" s="11"/>
-      <c r="BR58" s="11"/>
-    </row>
-    <row r="59" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN58" s="11"/>
+      <c r="BQ58" s="11"/>
+    </row>
+    <row r="59" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D59" s="10"/>
       <c r="E59" s="9"/>
-      <c r="BO59" s="11"/>
-      <c r="BR59" s="11"/>
-    </row>
-    <row r="60" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN59" s="11"/>
+      <c r="BQ59" s="11"/>
+    </row>
+    <row r="60" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D60" s="10"/>
       <c r="E60" s="9"/>
-      <c r="BO60" s="11"/>
-      <c r="BR60" s="11"/>
-    </row>
-    <row r="61" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN60" s="11"/>
+      <c r="BQ60" s="11"/>
+    </row>
+    <row r="61" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D61" s="10"/>
       <c r="E61" s="9"/>
-      <c r="BO61" s="11"/>
-      <c r="BR61" s="11"/>
-    </row>
-    <row r="62" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN61" s="11"/>
+      <c r="BQ61" s="11"/>
+    </row>
+    <row r="62" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D62" s="10"/>
       <c r="E62" s="9"/>
-      <c r="BO62" s="11"/>
-      <c r="BR62" s="11"/>
-    </row>
-    <row r="63" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN62" s="11"/>
+      <c r="BQ62" s="11"/>
+    </row>
+    <row r="63" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D63" s="10"/>
       <c r="E63" s="9"/>
-      <c r="BO63" s="11"/>
-      <c r="BR63" s="11"/>
-    </row>
-    <row r="64" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN63" s="11"/>
+      <c r="BQ63" s="11"/>
+    </row>
+    <row r="64" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D64" s="10"/>
       <c r="E64" s="9"/>
-      <c r="BO64" s="11"/>
-      <c r="BR64" s="11"/>
-    </row>
-    <row r="65" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN64" s="11"/>
+      <c r="BQ64" s="11"/>
+    </row>
+    <row r="65" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D65" s="10"/>
       <c r="E65" s="9"/>
-      <c r="BO65" s="11"/>
-      <c r="BR65" s="11"/>
-    </row>
-    <row r="66" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN65" s="11"/>
+      <c r="BQ65" s="11"/>
+    </row>
+    <row r="66" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D66" s="10"/>
       <c r="E66" s="9"/>
-      <c r="BO66" s="11"/>
-      <c r="BR66" s="11"/>
-    </row>
-    <row r="67" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN66" s="11"/>
+      <c r="BQ66" s="11"/>
+    </row>
+    <row r="67" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D67" s="10"/>
       <c r="E67" s="9"/>
-      <c r="BO67" s="11"/>
-      <c r="BR67" s="11"/>
-    </row>
-    <row r="68" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN67" s="11"/>
+      <c r="BQ67" s="11"/>
+    </row>
+    <row r="68" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D68" s="10"/>
       <c r="E68" s="9"/>
-      <c r="BO68" s="11"/>
-      <c r="BR68" s="11"/>
-    </row>
-    <row r="69" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN68" s="11"/>
+      <c r="BQ68" s="11"/>
+    </row>
+    <row r="69" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D69" s="10"/>
       <c r="E69" s="9"/>
-      <c r="BO69" s="11"/>
-      <c r="BR69" s="11"/>
-    </row>
-    <row r="70" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN69" s="11"/>
+      <c r="BQ69" s="11"/>
+    </row>
+    <row r="70" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D70" s="10"/>
       <c r="E70" s="9"/>
-      <c r="BO70" s="11"/>
-      <c r="BR70" s="11"/>
-    </row>
-    <row r="71" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN70" s="11"/>
+      <c r="BQ70" s="11"/>
+    </row>
+    <row r="71" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D71" s="10"/>
       <c r="E71" s="9"/>
-      <c r="BO71" s="11"/>
-      <c r="BR71" s="11"/>
-    </row>
-    <row r="72" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN71" s="11"/>
+      <c r="BQ71" s="11"/>
+    </row>
+    <row r="72" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D72" s="10"/>
       <c r="E72" s="9"/>
-      <c r="BO72" s="11"/>
-      <c r="BR72" s="11"/>
-    </row>
-    <row r="73" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN72" s="11"/>
+      <c r="BQ72" s="11"/>
+    </row>
+    <row r="73" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D73" s="10"/>
       <c r="E73" s="9"/>
-      <c r="BO73" s="11"/>
-      <c r="BR73" s="11"/>
-    </row>
-    <row r="74" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN73" s="11"/>
+      <c r="BQ73" s="11"/>
+    </row>
+    <row r="74" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D74" s="10"/>
       <c r="E74" s="9"/>
-      <c r="BO74" s="11"/>
-      <c r="BR74" s="11"/>
-    </row>
-    <row r="75" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN74" s="11"/>
+      <c r="BQ74" s="11"/>
+    </row>
+    <row r="75" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D75" s="10"/>
       <c r="E75" s="9"/>
-      <c r="BO75" s="11"/>
-      <c r="BR75" s="11"/>
-    </row>
-    <row r="76" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN75" s="11"/>
+      <c r="BQ75" s="11"/>
+    </row>
+    <row r="76" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D76" s="10"/>
       <c r="E76" s="9"/>
-      <c r="BO76" s="11"/>
-      <c r="BR76" s="11"/>
-    </row>
-    <row r="77" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN76" s="11"/>
+      <c r="BQ76" s="11"/>
+    </row>
+    <row r="77" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D77" s="10"/>
       <c r="E77" s="9"/>
-      <c r="BO77" s="11"/>
-      <c r="BR77" s="11"/>
-    </row>
-    <row r="78" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN77" s="11"/>
+      <c r="BQ77" s="11"/>
+    </row>
+    <row r="78" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D78" s="10"/>
       <c r="E78" s="9"/>
-      <c r="BO78" s="11"/>
-      <c r="BR78" s="11"/>
-    </row>
-    <row r="79" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN78" s="11"/>
+      <c r="BQ78" s="11"/>
+    </row>
+    <row r="79" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D79" s="10"/>
       <c r="E79" s="9"/>
-      <c r="BO79" s="11"/>
-      <c r="BR79" s="11"/>
-    </row>
-    <row r="80" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN79" s="11"/>
+      <c r="BQ79" s="11"/>
+    </row>
+    <row r="80" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D80" s="10"/>
       <c r="E80" s="9"/>
-      <c r="BO80" s="11"/>
-      <c r="BR80" s="11"/>
-    </row>
-    <row r="81" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN80" s="11"/>
+      <c r="BQ80" s="11"/>
+    </row>
+    <row r="81" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D81" s="10"/>
       <c r="E81" s="9"/>
-      <c r="BO81" s="11"/>
-      <c r="BR81" s="11"/>
-    </row>
-    <row r="82" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN81" s="11"/>
+      <c r="BQ81" s="11"/>
+    </row>
+    <row r="82" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D82" s="10"/>
       <c r="E82" s="9"/>
-      <c r="BO82" s="11"/>
-      <c r="BR82" s="11"/>
-    </row>
-    <row r="83" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN82" s="11"/>
+      <c r="BQ82" s="11"/>
+    </row>
+    <row r="83" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D83" s="10"/>
       <c r="E83" s="9"/>
-      <c r="BO83" s="11"/>
-      <c r="BR83" s="11"/>
-    </row>
-    <row r="84" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN83" s="11"/>
+      <c r="BQ83" s="11"/>
+    </row>
+    <row r="84" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D84" s="10"/>
       <c r="E84" s="9"/>
-      <c r="BO84" s="11"/>
-      <c r="BR84" s="11"/>
-    </row>
-    <row r="85" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN84" s="11"/>
+      <c r="BQ84" s="11"/>
+    </row>
+    <row r="85" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D85" s="10"/>
       <c r="E85" s="9"/>
-      <c r="BO85" s="11"/>
-      <c r="BR85" s="11"/>
-    </row>
-    <row r="86" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN85" s="11"/>
+      <c r="BQ85" s="11"/>
+    </row>
+    <row r="86" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D86" s="10"/>
       <c r="E86" s="9"/>
-      <c r="BO86" s="11"/>
-      <c r="BR86" s="11"/>
-    </row>
-    <row r="87" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN86" s="11"/>
+      <c r="BQ86" s="11"/>
+    </row>
+    <row r="87" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D87" s="10"/>
       <c r="E87" s="9"/>
-      <c r="BO87" s="11"/>
-      <c r="BR87" s="11"/>
-    </row>
-    <row r="88" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN87" s="11"/>
+      <c r="BQ87" s="11"/>
+    </row>
+    <row r="88" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D88" s="10"/>
       <c r="E88" s="9"/>
-      <c r="BO88" s="11"/>
-      <c r="BR88" s="11"/>
-    </row>
-    <row r="89" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN88" s="11"/>
+      <c r="BQ88" s="11"/>
+    </row>
+    <row r="89" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D89" s="10"/>
       <c r="E89" s="9"/>
-      <c r="BO89" s="11"/>
-      <c r="BR89" s="11"/>
-    </row>
-    <row r="90" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN89" s="11"/>
+      <c r="BQ89" s="11"/>
+    </row>
+    <row r="90" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D90" s="10"/>
       <c r="E90" s="9"/>
-      <c r="BO90" s="11"/>
-      <c r="BR90" s="11"/>
-    </row>
-    <row r="91" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN90" s="11"/>
+      <c r="BQ90" s="11"/>
+    </row>
+    <row r="91" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D91" s="10"/>
       <c r="E91" s="9"/>
-      <c r="BO91" s="11"/>
-      <c r="BR91" s="11"/>
-    </row>
-    <row r="92" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN91" s="11"/>
+      <c r="BQ91" s="11"/>
+    </row>
+    <row r="92" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D92" s="10"/>
       <c r="E92" s="9"/>
-      <c r="BO92" s="11"/>
-      <c r="BR92" s="11"/>
-    </row>
-    <row r="93" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN92" s="11"/>
+      <c r="BQ92" s="11"/>
+    </row>
+    <row r="93" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D93" s="10"/>
       <c r="E93" s="9"/>
-      <c r="BO93" s="11"/>
-      <c r="BR93" s="11"/>
-    </row>
-    <row r="94" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN93" s="11"/>
+      <c r="BQ93" s="11"/>
+    </row>
+    <row r="94" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D94" s="10"/>
       <c r="E94" s="9"/>
-      <c r="BO94" s="11"/>
-      <c r="BR94" s="11"/>
-    </row>
-    <row r="95" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN94" s="11"/>
+      <c r="BQ94" s="11"/>
+    </row>
+    <row r="95" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D95" s="10"/>
       <c r="E95" s="9"/>
-      <c r="BO95" s="11"/>
-      <c r="BR95" s="11"/>
-    </row>
-    <row r="96" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN95" s="11"/>
+      <c r="BQ95" s="11"/>
+    </row>
+    <row r="96" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D96" s="10"/>
       <c r="E96" s="9"/>
-      <c r="BO96" s="11"/>
-      <c r="BR96" s="11"/>
-    </row>
-    <row r="97" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN96" s="11"/>
+      <c r="BQ96" s="11"/>
+    </row>
+    <row r="97" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D97" s="10"/>
       <c r="E97" s="9"/>
-      <c r="BO97" s="11"/>
-      <c r="BR97" s="11"/>
-    </row>
-    <row r="98" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN97" s="11"/>
+      <c r="BQ97" s="11"/>
+    </row>
+    <row r="98" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D98" s="10"/>
       <c r="E98" s="9"/>
-      <c r="BO98" s="11"/>
-      <c r="BR98" s="11"/>
-    </row>
-    <row r="99" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN98" s="11"/>
+      <c r="BQ98" s="11"/>
+    </row>
+    <row r="99" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D99" s="10"/>
       <c r="E99" s="9"/>
-      <c r="BO99" s="11"/>
-      <c r="BR99" s="11"/>
-    </row>
-    <row r="100" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN99" s="11"/>
+      <c r="BQ99" s="11"/>
+    </row>
+    <row r="100" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D100" s="10"/>
       <c r="E100" s="9"/>
-      <c r="BO100" s="11"/>
-      <c r="BR100" s="11"/>
-    </row>
-    <row r="101" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN100" s="11"/>
+      <c r="BQ100" s="11"/>
+    </row>
+    <row r="101" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D101" s="10"/>
       <c r="E101" s="9"/>
-      <c r="BO101" s="11"/>
-      <c r="BR101" s="11"/>
-    </row>
-    <row r="102" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN101" s="11"/>
+      <c r="BQ101" s="11"/>
+    </row>
+    <row r="102" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D102" s="10"/>
       <c r="E102" s="9"/>
-      <c r="BO102" s="11"/>
-      <c r="BR102" s="11"/>
-    </row>
-    <row r="103" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN102" s="11"/>
+      <c r="BQ102" s="11"/>
+    </row>
+    <row r="103" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D103" s="10"/>
       <c r="E103" s="9"/>
-      <c r="BO103" s="11"/>
-      <c r="BR103" s="11"/>
-    </row>
-    <row r="104" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN103" s="11"/>
+      <c r="BQ103" s="11"/>
+    </row>
+    <row r="104" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D104" s="10"/>
       <c r="E104" s="9"/>
-      <c r="BO104" s="11"/>
-      <c r="BR104" s="11"/>
-    </row>
-    <row r="105" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN104" s="11"/>
+      <c r="BQ104" s="11"/>
+    </row>
+    <row r="105" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D105" s="10"/>
       <c r="E105" s="9"/>
-      <c r="BO105" s="11"/>
-      <c r="BR105" s="11"/>
-    </row>
-    <row r="106" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN105" s="11"/>
+      <c r="BQ105" s="11"/>
+    </row>
+    <row r="106" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D106" s="10"/>
       <c r="E106" s="9"/>
-      <c r="BO106" s="11"/>
-      <c r="BR106" s="11"/>
-    </row>
-    <row r="107" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN106" s="11"/>
+      <c r="BQ106" s="11"/>
+    </row>
+    <row r="107" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D107" s="10"/>
       <c r="E107" s="9"/>
-      <c r="BO107" s="11"/>
-      <c r="BR107" s="11"/>
-    </row>
-    <row r="108" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN107" s="11"/>
+      <c r="BQ107" s="11"/>
+    </row>
+    <row r="108" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D108" s="10"/>
       <c r="E108" s="9"/>
-      <c r="BO108" s="11"/>
-      <c r="BR108" s="11"/>
-    </row>
-    <row r="109" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN108" s="11"/>
+      <c r="BQ108" s="11"/>
+    </row>
+    <row r="109" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D109" s="10"/>
       <c r="E109" s="9"/>
-      <c r="BO109" s="11"/>
-      <c r="BR109" s="11"/>
-    </row>
-    <row r="110" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN109" s="11"/>
+      <c r="BQ109" s="11"/>
+    </row>
+    <row r="110" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
       <c r="E110" s="9"/>
-      <c r="BO110" s="11"/>
-      <c r="BR110" s="11"/>
-    </row>
-    <row r="111" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN110" s="11"/>
+      <c r="BQ110" s="11"/>
+    </row>
+    <row r="111" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D111" s="10"/>
       <c r="E111" s="9"/>
-      <c r="BO111" s="11"/>
-      <c r="BR111" s="11"/>
-    </row>
-    <row r="112" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN111" s="11"/>
+      <c r="BQ111" s="11"/>
+    </row>
+    <row r="112" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D112" s="10"/>
       <c r="E112" s="9"/>
-      <c r="BO112" s="11"/>
-      <c r="BR112" s="11"/>
-    </row>
-    <row r="113" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN112" s="11"/>
+      <c r="BQ112" s="11"/>
+    </row>
+    <row r="113" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D113" s="10"/>
       <c r="E113" s="9"/>
-      <c r="BO113" s="11"/>
-      <c r="BR113" s="11"/>
-    </row>
-    <row r="114" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN113" s="11"/>
+      <c r="BQ113" s="11"/>
+    </row>
+    <row r="114" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D114" s="10"/>
       <c r="E114" s="9"/>
-      <c r="BO114" s="11"/>
-      <c r="BR114" s="11"/>
-    </row>
-    <row r="115" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN114" s="11"/>
+      <c r="BQ114" s="11"/>
+    </row>
+    <row r="115" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D115" s="10"/>
       <c r="E115" s="9"/>
-      <c r="BO115" s="11"/>
-      <c r="BR115" s="11"/>
-    </row>
-    <row r="116" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN115" s="11"/>
+      <c r="BQ115" s="11"/>
+    </row>
+    <row r="116" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D116" s="10"/>
       <c r="E116" s="9"/>
-      <c r="BO116" s="11"/>
-      <c r="BR116" s="11"/>
-    </row>
-    <row r="117" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN116" s="11"/>
+      <c r="BQ116" s="11"/>
+    </row>
+    <row r="117" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D117" s="10"/>
       <c r="E117" s="9"/>
-      <c r="BO117" s="11"/>
-      <c r="BR117" s="11"/>
-    </row>
-    <row r="118" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN117" s="11"/>
+      <c r="BQ117" s="11"/>
+    </row>
+    <row r="118" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D118" s="10"/>
       <c r="E118" s="9"/>
-      <c r="BO118" s="11"/>
-      <c r="BR118" s="11"/>
-    </row>
-    <row r="119" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN118" s="11"/>
+      <c r="BQ118" s="11"/>
+    </row>
+    <row r="119" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D119" s="10"/>
       <c r="E119" s="9"/>
-      <c r="BO119" s="11"/>
-      <c r="BR119" s="11"/>
-    </row>
-    <row r="120" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN119" s="11"/>
+      <c r="BQ119" s="11"/>
+    </row>
+    <row r="120" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D120" s="10"/>
       <c r="E120" s="9"/>
-      <c r="BO120" s="11"/>
-      <c r="BR120" s="11"/>
-    </row>
-    <row r="121" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN120" s="11"/>
+      <c r="BQ120" s="11"/>
+    </row>
+    <row r="121" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D121" s="10"/>
       <c r="E121" s="9"/>
-      <c r="BO121" s="11"/>
-      <c r="BR121" s="11"/>
-    </row>
-    <row r="122" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN121" s="11"/>
+      <c r="BQ121" s="11"/>
+    </row>
+    <row r="122" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D122" s="10"/>
       <c r="E122" s="9"/>
-      <c r="BO122" s="11"/>
-      <c r="BR122" s="11"/>
-    </row>
-    <row r="123" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN122" s="11"/>
+      <c r="BQ122" s="11"/>
+    </row>
+    <row r="123" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D123" s="10"/>
       <c r="E123" s="9"/>
-      <c r="BO123" s="11"/>
-      <c r="BR123" s="11"/>
-    </row>
-    <row r="124" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN123" s="11"/>
+      <c r="BQ123" s="11"/>
+    </row>
+    <row r="124" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D124" s="10"/>
       <c r="E124" s="9"/>
-      <c r="BO124" s="11"/>
-      <c r="BR124" s="11"/>
-    </row>
-    <row r="125" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN124" s="11"/>
+      <c r="BQ124" s="11"/>
+    </row>
+    <row r="125" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D125" s="10"/>
       <c r="E125" s="9"/>
-      <c r="BO125" s="11"/>
-      <c r="BR125" s="11"/>
-    </row>
-    <row r="126" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN125" s="11"/>
+      <c r="BQ125" s="11"/>
+    </row>
+    <row r="126" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D126" s="10"/>
       <c r="E126" s="9"/>
-      <c r="BO126" s="11"/>
-      <c r="BR126" s="11"/>
-    </row>
-    <row r="127" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN126" s="11"/>
+      <c r="BQ126" s="11"/>
+    </row>
+    <row r="127" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D127" s="10"/>
       <c r="E127" s="9"/>
-      <c r="BO127" s="11"/>
-      <c r="BR127" s="11"/>
-    </row>
-    <row r="128" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN127" s="11"/>
+      <c r="BQ127" s="11"/>
+    </row>
+    <row r="128" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D128" s="10"/>
       <c r="E128" s="9"/>
-      <c r="BO128" s="11"/>
-      <c r="BR128" s="11"/>
-    </row>
-    <row r="129" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN128" s="11"/>
+      <c r="BQ128" s="11"/>
+    </row>
+    <row r="129" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D129" s="10"/>
       <c r="E129" s="9"/>
-      <c r="BO129" s="11"/>
-      <c r="BR129" s="11"/>
-    </row>
-    <row r="130" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN129" s="11"/>
+      <c r="BQ129" s="11"/>
+    </row>
+    <row r="130" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D130" s="10"/>
       <c r="E130" s="9"/>
-      <c r="BO130" s="11"/>
-      <c r="BR130" s="11"/>
-    </row>
-    <row r="131" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN130" s="11"/>
+      <c r="BQ130" s="11"/>
+    </row>
+    <row r="131" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D131" s="10"/>
       <c r="E131" s="9"/>
-      <c r="BO131" s="11"/>
-      <c r="BR131" s="11"/>
-    </row>
-    <row r="132" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN131" s="11"/>
+      <c r="BQ131" s="11"/>
+    </row>
+    <row r="132" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D132" s="10"/>
       <c r="E132" s="9"/>
-      <c r="BO132" s="11"/>
-      <c r="BR132" s="11"/>
-    </row>
-    <row r="133" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN132" s="11"/>
+      <c r="BQ132" s="11"/>
+    </row>
+    <row r="133" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D133" s="10"/>
       <c r="E133" s="9"/>
-      <c r="BO133" s="11"/>
-      <c r="BR133" s="11"/>
-    </row>
-    <row r="134" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN133" s="11"/>
+      <c r="BQ133" s="11"/>
+    </row>
+    <row r="134" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D134" s="10"/>
       <c r="E134" s="9"/>
-      <c r="BO134" s="11"/>
-      <c r="BR134" s="11"/>
-    </row>
-    <row r="135" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN134" s="11"/>
+      <c r="BQ134" s="11"/>
+    </row>
+    <row r="135" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D135" s="10"/>
       <c r="E135" s="9"/>
-      <c r="BO135" s="11"/>
-      <c r="BR135" s="11"/>
-    </row>
-    <row r="136" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN135" s="11"/>
+      <c r="BQ135" s="11"/>
+    </row>
+    <row r="136" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D136" s="10"/>
       <c r="E136" s="9"/>
-      <c r="BO136" s="11"/>
-      <c r="BR136" s="11"/>
-    </row>
-    <row r="137" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN136" s="11"/>
+      <c r="BQ136" s="11"/>
+    </row>
+    <row r="137" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D137" s="10"/>
       <c r="E137" s="9"/>
-      <c r="BO137" s="11"/>
-      <c r="BR137" s="11"/>
-    </row>
-    <row r="138" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN137" s="11"/>
+      <c r="BQ137" s="11"/>
+    </row>
+    <row r="138" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D138" s="10"/>
       <c r="E138" s="9"/>
-      <c r="BO138" s="11"/>
-      <c r="BR138" s="11"/>
-    </row>
-    <row r="139" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN138" s="11"/>
+      <c r="BQ138" s="11"/>
+    </row>
+    <row r="139" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D139" s="10"/>
       <c r="E139" s="9"/>
-      <c r="BO139" s="11"/>
-      <c r="BR139" s="11"/>
-    </row>
-    <row r="140" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN139" s="11"/>
+      <c r="BQ139" s="11"/>
+    </row>
+    <row r="140" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D140" s="10"/>
       <c r="E140" s="9"/>
-      <c r="BO140" s="11"/>
-      <c r="BR140" s="11"/>
-    </row>
-    <row r="141" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN140" s="11"/>
+      <c r="BQ140" s="11"/>
+    </row>
+    <row r="141" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D141" s="10"/>
       <c r="E141" s="9"/>
-      <c r="BO141" s="11"/>
-      <c r="BR141" s="11"/>
-    </row>
-    <row r="142" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN141" s="11"/>
+      <c r="BQ141" s="11"/>
+    </row>
+    <row r="142" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D142" s="10"/>
       <c r="E142" s="9"/>
-      <c r="BO142" s="11"/>
-      <c r="BR142" s="11"/>
-    </row>
-    <row r="143" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN142" s="11"/>
+      <c r="BQ142" s="11"/>
+    </row>
+    <row r="143" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D143" s="10"/>
       <c r="E143" s="9"/>
-      <c r="BO143" s="11"/>
-      <c r="BR143" s="11"/>
-    </row>
-    <row r="144" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN143" s="11"/>
+      <c r="BQ143" s="11"/>
+    </row>
+    <row r="144" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D144" s="10"/>
       <c r="E144" s="9"/>
-      <c r="BO144" s="11"/>
-      <c r="BR144" s="11"/>
-    </row>
-    <row r="145" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN144" s="11"/>
+      <c r="BQ144" s="11"/>
+    </row>
+    <row r="145" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D145" s="10"/>
       <c r="E145" s="9"/>
-      <c r="BO145" s="11"/>
-      <c r="BR145" s="11"/>
-    </row>
-    <row r="146" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN145" s="11"/>
+      <c r="BQ145" s="11"/>
+    </row>
+    <row r="146" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D146" s="10"/>
       <c r="E146" s="9"/>
-      <c r="BO146" s="11"/>
-      <c r="BR146" s="11"/>
-    </row>
-    <row r="147" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN146" s="11"/>
+      <c r="BQ146" s="11"/>
+    </row>
+    <row r="147" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D147" s="10"/>
       <c r="E147" s="9"/>
-      <c r="BO147" s="11"/>
-      <c r="BR147" s="11"/>
-    </row>
-    <row r="148" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN147" s="11"/>
+      <c r="BQ147" s="11"/>
+    </row>
+    <row r="148" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D148" s="10"/>
       <c r="E148" s="9"/>
-      <c r="BO148" s="11"/>
-      <c r="BR148" s="11"/>
-    </row>
-    <row r="149" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN148" s="11"/>
+      <c r="BQ148" s="11"/>
+    </row>
+    <row r="149" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D149" s="10"/>
       <c r="E149" s="9"/>
-      <c r="BO149" s="11"/>
-      <c r="BR149" s="11"/>
-    </row>
-    <row r="150" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN149" s="11"/>
+      <c r="BQ149" s="11"/>
+    </row>
+    <row r="150" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D150" s="10"/>
       <c r="E150" s="9"/>
-      <c r="BO150" s="11"/>
-      <c r="BR150" s="11"/>
-    </row>
-    <row r="151" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN150" s="11"/>
+      <c r="BQ150" s="11"/>
+    </row>
+    <row r="151" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D151" s="10"/>
       <c r="E151" s="9"/>
-      <c r="BO151" s="11"/>
-      <c r="BR151" s="11"/>
-    </row>
-    <row r="152" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN151" s="11"/>
+      <c r="BQ151" s="11"/>
+    </row>
+    <row r="152" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D152" s="10"/>
       <c r="E152" s="9"/>
-      <c r="BO152" s="11"/>
-      <c r="BR152" s="11"/>
-    </row>
-    <row r="153" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN152" s="11"/>
+      <c r="BQ152" s="11"/>
+    </row>
+    <row r="153" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D153" s="10"/>
       <c r="E153" s="9"/>
-      <c r="BO153" s="11"/>
-      <c r="BR153" s="11"/>
-    </row>
-    <row r="154" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN153" s="11"/>
+      <c r="BQ153" s="11"/>
+    </row>
+    <row r="154" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D154" s="10"/>
       <c r="E154" s="9"/>
-      <c r="BO154" s="11"/>
-      <c r="BR154" s="11"/>
-    </row>
-    <row r="155" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN154" s="11"/>
+      <c r="BQ154" s="11"/>
+    </row>
+    <row r="155" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D155" s="10"/>
       <c r="E155" s="9"/>
-      <c r="BO155" s="11"/>
-      <c r="BR155" s="11"/>
-    </row>
-    <row r="156" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN155" s="11"/>
+      <c r="BQ155" s="11"/>
+    </row>
+    <row r="156" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D156" s="10"/>
       <c r="E156" s="9"/>
-      <c r="BO156" s="11"/>
-      <c r="BR156" s="11"/>
-    </row>
-    <row r="157" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN156" s="11"/>
+      <c r="BQ156" s="11"/>
+    </row>
+    <row r="157" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D157" s="10"/>
       <c r="E157" s="9"/>
-      <c r="BO157" s="11"/>
-      <c r="BR157" s="11"/>
-    </row>
-    <row r="158" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN157" s="11"/>
+      <c r="BQ157" s="11"/>
+    </row>
+    <row r="158" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D158" s="10"/>
       <c r="E158" s="9"/>
-      <c r="BO158" s="11"/>
-      <c r="BR158" s="11"/>
-    </row>
-    <row r="159" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN158" s="11"/>
+      <c r="BQ158" s="11"/>
+    </row>
+    <row r="159" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D159" s="10"/>
       <c r="E159" s="9"/>
-      <c r="BO159" s="11"/>
-      <c r="BR159" s="11"/>
-    </row>
-    <row r="160" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN159" s="11"/>
+      <c r="BQ159" s="11"/>
+    </row>
+    <row r="160" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D160" s="10"/>
       <c r="E160" s="9"/>
-      <c r="BO160" s="11"/>
-      <c r="BR160" s="11"/>
-    </row>
-    <row r="161" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN160" s="11"/>
+      <c r="BQ160" s="11"/>
+    </row>
+    <row r="161" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D161" s="10"/>
       <c r="E161" s="9"/>
-      <c r="BO161" s="11"/>
-      <c r="BR161" s="11"/>
-    </row>
-    <row r="162" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN161" s="11"/>
+      <c r="BQ161" s="11"/>
+    </row>
+    <row r="162" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D162" s="10"/>
       <c r="E162" s="9"/>
-      <c r="BO162" s="11"/>
-      <c r="BR162" s="11"/>
-    </row>
-    <row r="163" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN162" s="11"/>
+      <c r="BQ162" s="11"/>
+    </row>
+    <row r="163" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D163" s="10"/>
       <c r="E163" s="9"/>
-      <c r="BO163" s="11"/>
-      <c r="BR163" s="11"/>
-    </row>
-    <row r="164" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN163" s="11"/>
+      <c r="BQ163" s="11"/>
+    </row>
+    <row r="164" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D164" s="10"/>
       <c r="E164" s="9"/>
-      <c r="BO164" s="11"/>
-      <c r="BR164" s="11"/>
-    </row>
-    <row r="165" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN164" s="11"/>
+      <c r="BQ164" s="11"/>
+    </row>
+    <row r="165" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D165" s="10"/>
       <c r="E165" s="9"/>
-      <c r="BO165" s="11"/>
-      <c r="BR165" s="11"/>
-    </row>
-    <row r="166" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN165" s="11"/>
+      <c r="BQ165" s="11"/>
+    </row>
+    <row r="166" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D166" s="10"/>
       <c r="E166" s="9"/>
-      <c r="BO166" s="11"/>
-      <c r="BR166" s="11"/>
-    </row>
-    <row r="167" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN166" s="11"/>
+      <c r="BQ166" s="11"/>
+    </row>
+    <row r="167" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D167" s="10"/>
       <c r="E167" s="9"/>
-      <c r="BO167" s="11"/>
-      <c r="BR167" s="11"/>
-    </row>
-    <row r="168" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN167" s="11"/>
+      <c r="BQ167" s="11"/>
+    </row>
+    <row r="168" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D168" s="10"/>
       <c r="E168" s="9"/>
-      <c r="BO168" s="11"/>
-      <c r="BR168" s="11"/>
-    </row>
-    <row r="169" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN168" s="11"/>
+      <c r="BQ168" s="11"/>
+    </row>
+    <row r="169" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D169" s="10"/>
       <c r="E169" s="9"/>
-      <c r="BO169" s="11"/>
-      <c r="BR169" s="11"/>
-    </row>
-    <row r="170" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN169" s="11"/>
+      <c r="BQ169" s="11"/>
+    </row>
+    <row r="170" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D170" s="10"/>
       <c r="E170" s="9"/>
-      <c r="BO170" s="11"/>
-      <c r="BR170" s="11"/>
-    </row>
-    <row r="171" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN170" s="11"/>
+      <c r="BQ170" s="11"/>
+    </row>
+    <row r="171" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D171" s="10"/>
       <c r="E171" s="9"/>
-      <c r="BO171" s="11"/>
-      <c r="BR171" s="11"/>
-    </row>
-    <row r="172" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN171" s="11"/>
+      <c r="BQ171" s="11"/>
+    </row>
+    <row r="172" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D172" s="10"/>
       <c r="E172" s="9"/>
-      <c r="BO172" s="11"/>
-      <c r="BR172" s="11"/>
-    </row>
-    <row r="173" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN172" s="11"/>
+      <c r="BQ172" s="11"/>
+    </row>
+    <row r="173" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D173" s="10"/>
       <c r="E173" s="9"/>
-      <c r="BO173" s="11"/>
-      <c r="BR173" s="11"/>
-    </row>
-    <row r="174" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN173" s="11"/>
+      <c r="BQ173" s="11"/>
+    </row>
+    <row r="174" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D174" s="10"/>
       <c r="E174" s="9"/>
-      <c r="BO174" s="11"/>
-      <c r="BR174" s="11"/>
-    </row>
-    <row r="175" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN174" s="11"/>
+      <c r="BQ174" s="11"/>
+    </row>
+    <row r="175" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D175" s="10"/>
       <c r="E175" s="9"/>
-      <c r="BO175" s="11"/>
-      <c r="BR175" s="11"/>
-    </row>
-    <row r="176" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN175" s="11"/>
+      <c r="BQ175" s="11"/>
+    </row>
+    <row r="176" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D176" s="10"/>
       <c r="E176" s="9"/>
-      <c r="BO176" s="11"/>
-      <c r="BR176" s="11"/>
-    </row>
-    <row r="177" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN176" s="11"/>
+      <c r="BQ176" s="11"/>
+    </row>
+    <row r="177" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D177" s="10"/>
       <c r="E177" s="9"/>
-      <c r="BO177" s="11"/>
-      <c r="BR177" s="11"/>
-    </row>
-    <row r="178" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN177" s="11"/>
+      <c r="BQ177" s="11"/>
+    </row>
+    <row r="178" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D178" s="10"/>
       <c r="E178" s="9"/>
-      <c r="BO178" s="11"/>
-      <c r="BR178" s="11"/>
-    </row>
-    <row r="179" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN178" s="11"/>
+      <c r="BQ178" s="11"/>
+    </row>
+    <row r="179" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D179" s="10"/>
       <c r="E179" s="9"/>
-      <c r="BO179" s="11"/>
-      <c r="BR179" s="11"/>
-    </row>
-    <row r="180" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN179" s="11"/>
+      <c r="BQ179" s="11"/>
+    </row>
+    <row r="180" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D180" s="10"/>
       <c r="E180" s="9"/>
-      <c r="BO180" s="11"/>
-      <c r="BR180" s="11"/>
-    </row>
-    <row r="181" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN180" s="11"/>
+      <c r="BQ180" s="11"/>
+    </row>
+    <row r="181" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D181" s="10"/>
       <c r="E181" s="9"/>
-      <c r="BO181" s="11"/>
-      <c r="BR181" s="11"/>
-    </row>
-    <row r="182" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN181" s="11"/>
+      <c r="BQ181" s="11"/>
+    </row>
+    <row r="182" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D182" s="10"/>
       <c r="E182" s="9"/>
-      <c r="BO182" s="11"/>
-      <c r="BR182" s="11"/>
-    </row>
-    <row r="183" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN182" s="11"/>
+      <c r="BQ182" s="11"/>
+    </row>
+    <row r="183" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D183" s="10"/>
       <c r="E183" s="9"/>
-      <c r="BO183" s="11"/>
-      <c r="BR183" s="11"/>
-    </row>
-    <row r="184" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN183" s="11"/>
+      <c r="BQ183" s="11"/>
+    </row>
+    <row r="184" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D184" s="10"/>
       <c r="E184" s="9"/>
-      <c r="BO184" s="11"/>
-      <c r="BR184" s="11"/>
-    </row>
-    <row r="185" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN184" s="11"/>
+      <c r="BQ184" s="11"/>
+    </row>
+    <row r="185" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D185" s="10"/>
       <c r="E185" s="9"/>
-      <c r="BO185" s="11"/>
-      <c r="BR185" s="11"/>
-    </row>
-    <row r="186" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN185" s="11"/>
+      <c r="BQ185" s="11"/>
+    </row>
+    <row r="186" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D186" s="10"/>
       <c r="E186" s="9"/>
-      <c r="BO186" s="11"/>
-      <c r="BR186" s="11"/>
-    </row>
-    <row r="187" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN186" s="11"/>
+      <c r="BQ186" s="11"/>
+    </row>
+    <row r="187" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D187" s="10"/>
       <c r="E187" s="9"/>
-      <c r="BO187" s="11"/>
-      <c r="BR187" s="11"/>
-    </row>
-    <row r="188" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN187" s="11"/>
+      <c r="BQ187" s="11"/>
+    </row>
+    <row r="188" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D188" s="10"/>
       <c r="E188" s="9"/>
-      <c r="BO188" s="11"/>
-      <c r="BR188" s="11"/>
-    </row>
-    <row r="189" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN188" s="11"/>
+      <c r="BQ188" s="11"/>
+    </row>
+    <row r="189" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D189" s="10"/>
       <c r="E189" s="9"/>
-      <c r="BO189" s="11"/>
-      <c r="BR189" s="11"/>
-    </row>
-    <row r="190" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN189" s="11"/>
+      <c r="BQ189" s="11"/>
+    </row>
+    <row r="190" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D190" s="10"/>
       <c r="E190" s="9"/>
-      <c r="BO190" s="11"/>
-      <c r="BR190" s="11"/>
-    </row>
-    <row r="191" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN190" s="11"/>
+      <c r="BQ190" s="11"/>
+    </row>
+    <row r="191" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D191" s="10"/>
       <c r="E191" s="9"/>
-      <c r="BO191" s="11"/>
-      <c r="BR191" s="11"/>
-    </row>
-    <row r="192" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN191" s="11"/>
+      <c r="BQ191" s="11"/>
+    </row>
+    <row r="192" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D192" s="10"/>
       <c r="E192" s="9"/>
-      <c r="BO192" s="11"/>
-      <c r="BR192" s="11"/>
-    </row>
-    <row r="193" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN192" s="11"/>
+      <c r="BQ192" s="11"/>
+    </row>
+    <row r="193" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D193" s="10"/>
       <c r="E193" s="9"/>
-      <c r="BO193" s="11"/>
-      <c r="BR193" s="11"/>
-    </row>
-    <row r="194" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN193" s="11"/>
+      <c r="BQ193" s="11"/>
+    </row>
+    <row r="194" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D194" s="10"/>
       <c r="E194" s="9"/>
-      <c r="BO194" s="11"/>
-      <c r="BR194" s="11"/>
-    </row>
-    <row r="195" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN194" s="11"/>
+      <c r="BQ194" s="11"/>
+    </row>
+    <row r="195" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D195" s="10"/>
       <c r="E195" s="9"/>
-      <c r="BO195" s="11"/>
-      <c r="BR195" s="11"/>
-    </row>
-    <row r="196" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN195" s="11"/>
+      <c r="BQ195" s="11"/>
+    </row>
+    <row r="196" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D196" s="10"/>
       <c r="E196" s="9"/>
-      <c r="BO196" s="11"/>
-      <c r="BR196" s="11"/>
-    </row>
-    <row r="197" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN196" s="11"/>
+      <c r="BQ196" s="11"/>
+    </row>
+    <row r="197" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D197" s="10"/>
       <c r="E197" s="9"/>
-      <c r="BO197" s="11"/>
-      <c r="BR197" s="11"/>
-    </row>
-    <row r="198" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN197" s="11"/>
+      <c r="BQ197" s="11"/>
+    </row>
+    <row r="198" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D198" s="10"/>
       <c r="E198" s="9"/>
-      <c r="BO198" s="11"/>
-      <c r="BR198" s="11"/>
-    </row>
-    <row r="199" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN198" s="11"/>
+      <c r="BQ198" s="11"/>
+    </row>
+    <row r="199" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D199" s="10"/>
       <c r="E199" s="9"/>
-      <c r="BO199" s="11"/>
-      <c r="BR199" s="11"/>
-    </row>
-    <row r="200" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN199" s="11"/>
+      <c r="BQ199" s="11"/>
+    </row>
+    <row r="200" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D200" s="10"/>
       <c r="E200" s="9"/>
-      <c r="BO200" s="11"/>
-      <c r="BR200" s="11"/>
-    </row>
-    <row r="201" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN200" s="11"/>
+      <c r="BQ200" s="11"/>
+    </row>
+    <row r="201" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D201" s="10"/>
       <c r="E201" s="9"/>
-      <c r="BO201" s="11"/>
-      <c r="BR201" s="11"/>
-    </row>
-    <row r="202" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN201" s="11"/>
+      <c r="BQ201" s="11"/>
+    </row>
+    <row r="202" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D202" s="10"/>
       <c r="E202" s="9"/>
-      <c r="BO202" s="11"/>
-      <c r="BR202" s="11"/>
-    </row>
-    <row r="203" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN202" s="11"/>
+      <c r="BQ202" s="11"/>
+    </row>
+    <row r="203" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D203" s="10"/>
       <c r="E203" s="9"/>
-      <c r="BO203" s="11"/>
-      <c r="BR203" s="11"/>
-    </row>
-    <row r="204" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN203" s="11"/>
+      <c r="BQ203" s="11"/>
+    </row>
+    <row r="204" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D204" s="10"/>
       <c r="E204" s="9"/>
-      <c r="BO204" s="11"/>
-      <c r="BR204" s="11"/>
-    </row>
-    <row r="205" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN204" s="11"/>
+      <c r="BQ204" s="11"/>
+    </row>
+    <row r="205" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D205" s="10"/>
       <c r="E205" s="9"/>
-      <c r="BO205" s="11"/>
-      <c r="BR205" s="11"/>
-    </row>
-    <row r="206" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN205" s="11"/>
+      <c r="BQ205" s="11"/>
+    </row>
+    <row r="206" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D206" s="10"/>
       <c r="E206" s="9"/>
-      <c r="BO206" s="11"/>
-      <c r="BR206" s="11"/>
-    </row>
-    <row r="207" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN206" s="11"/>
+      <c r="BQ206" s="11"/>
+    </row>
+    <row r="207" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D207" s="10"/>
       <c r="E207" s="9"/>
-      <c r="BO207" s="11"/>
-      <c r="BR207" s="11"/>
-    </row>
-    <row r="208" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN207" s="11"/>
+      <c r="BQ207" s="11"/>
+    </row>
+    <row r="208" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D208" s="10"/>
       <c r="E208" s="9"/>
-      <c r="BO208" s="11"/>
-      <c r="BR208" s="11"/>
-    </row>
-    <row r="209" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN208" s="11"/>
+      <c r="BQ208" s="11"/>
+    </row>
+    <row r="209" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D209" s="10"/>
       <c r="E209" s="9"/>
-      <c r="BO209" s="11"/>
-      <c r="BR209" s="11"/>
-    </row>
-    <row r="210" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN209" s="11"/>
+      <c r="BQ209" s="11"/>
+    </row>
+    <row r="210" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D210" s="10"/>
       <c r="E210" s="9"/>
-      <c r="BO210" s="11"/>
-      <c r="BR210" s="11"/>
-    </row>
-    <row r="211" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN210" s="11"/>
+      <c r="BQ210" s="11"/>
+    </row>
+    <row r="211" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D211" s="10"/>
       <c r="E211" s="9"/>
-      <c r="BO211" s="11"/>
-      <c r="BR211" s="11"/>
-    </row>
-    <row r="212" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN211" s="11"/>
+      <c r="BQ211" s="11"/>
+    </row>
+    <row r="212" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D212" s="10"/>
       <c r="E212" s="9"/>
-      <c r="BO212" s="11"/>
-      <c r="BR212" s="11"/>
-    </row>
-    <row r="213" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN212" s="11"/>
+      <c r="BQ212" s="11"/>
+    </row>
+    <row r="213" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D213" s="10"/>
       <c r="E213" s="9"/>
-      <c r="BO213" s="11"/>
-      <c r="BR213" s="11"/>
-    </row>
-    <row r="214" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN213" s="11"/>
+      <c r="BQ213" s="11"/>
+    </row>
+    <row r="214" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D214" s="10"/>
       <c r="E214" s="9"/>
-      <c r="BO214" s="11"/>
-      <c r="BR214" s="11"/>
-    </row>
-    <row r="215" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN214" s="11"/>
+      <c r="BQ214" s="11"/>
+    </row>
+    <row r="215" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D215" s="10"/>
       <c r="E215" s="9"/>
-      <c r="BO215" s="11"/>
-      <c r="BR215" s="11"/>
-    </row>
-    <row r="216" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN215" s="11"/>
+      <c r="BQ215" s="11"/>
+    </row>
+    <row r="216" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D216" s="10"/>
       <c r="E216" s="9"/>
-      <c r="BR216" s="11"/>
-    </row>
-    <row r="217" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ216" s="11"/>
+    </row>
+    <row r="217" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D217" s="10"/>
       <c r="E217" s="9"/>
-      <c r="BO217" s="11"/>
-      <c r="BR217" s="11"/>
-    </row>
-    <row r="218" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN217" s="11"/>
+      <c r="BQ217" s="11"/>
+    </row>
+    <row r="218" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D218" s="10"/>
       <c r="E218" s="9"/>
-      <c r="BO218" s="11"/>
-      <c r="BR218" s="11"/>
-    </row>
-    <row r="219" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN218" s="11"/>
+      <c r="BQ218" s="11"/>
+    </row>
+    <row r="219" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D219" s="10"/>
       <c r="E219" s="9"/>
-      <c r="BO219" s="11"/>
-      <c r="BR219" s="11"/>
-    </row>
-    <row r="220" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN219" s="11"/>
+      <c r="BQ219" s="11"/>
+    </row>
+    <row r="220" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D220" s="10"/>
       <c r="E220" s="9"/>
-      <c r="BO220" s="11"/>
-      <c r="BR220" s="11"/>
-    </row>
-    <row r="221" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN220" s="11"/>
+      <c r="BQ220" s="11"/>
+    </row>
+    <row r="221" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D221" s="10"/>
       <c r="E221" s="9"/>
-      <c r="BO221" s="11"/>
-      <c r="BR221" s="11"/>
-    </row>
-    <row r="222" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN221" s="11"/>
+      <c r="BQ221" s="11"/>
+    </row>
+    <row r="222" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D222" s="10"/>
       <c r="E222" s="9"/>
-      <c r="BO222" s="11"/>
-      <c r="BR222" s="11"/>
-    </row>
-    <row r="223" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN222" s="11"/>
+      <c r="BQ222" s="11"/>
+    </row>
+    <row r="223" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D223" s="10"/>
       <c r="E223" s="9"/>
-      <c r="BO223" s="11"/>
-      <c r="BR223" s="11"/>
-    </row>
-    <row r="224" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN223" s="11"/>
+      <c r="BQ223" s="11"/>
+    </row>
+    <row r="224" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D224" s="10"/>
       <c r="E224" s="9"/>
-      <c r="BO224" s="11"/>
-      <c r="BR224" s="11"/>
-    </row>
-    <row r="225" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN224" s="11"/>
+      <c r="BQ224" s="11"/>
+    </row>
+    <row r="225" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D225" s="10"/>
       <c r="E225" s="9"/>
-      <c r="BO225" s="11"/>
-      <c r="BR225" s="11"/>
-    </row>
-    <row r="226" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN225" s="11"/>
+      <c r="BQ225" s="11"/>
+    </row>
+    <row r="226" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D226" s="10"/>
       <c r="E226" s="9"/>
-      <c r="BO226" s="11"/>
-      <c r="BR226" s="11"/>
-    </row>
-    <row r="227" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN226" s="11"/>
+      <c r="BQ226" s="11"/>
+    </row>
+    <row r="227" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D227" s="10"/>
       <c r="E227" s="9"/>
-      <c r="BO227" s="11"/>
-      <c r="BR227" s="11"/>
-    </row>
-    <row r="228" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN227" s="11"/>
+      <c r="BQ227" s="11"/>
+    </row>
+    <row r="228" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D228" s="10"/>
       <c r="E228" s="9"/>
-      <c r="BO228" s="11"/>
-      <c r="BR228" s="11"/>
-    </row>
-    <row r="229" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN228" s="11"/>
+      <c r="BQ228" s="11"/>
+    </row>
+    <row r="229" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D229" s="10"/>
       <c r="E229" s="9"/>
-      <c r="BO229" s="11"/>
-      <c r="BR229" s="11"/>
-    </row>
-    <row r="230" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN229" s="11"/>
+      <c r="BQ229" s="11"/>
+    </row>
+    <row r="230" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D230" s="10"/>
       <c r="E230" s="9"/>
-      <c r="BO230" s="11"/>
-      <c r="BR230" s="11"/>
-    </row>
-    <row r="231" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN230" s="11"/>
+      <c r="BQ230" s="11"/>
+    </row>
+    <row r="231" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D231" s="10"/>
       <c r="E231" s="9"/>
-      <c r="BO231" s="11"/>
-      <c r="BR231" s="11"/>
-    </row>
-    <row r="232" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN231" s="11"/>
+      <c r="BQ231" s="11"/>
+    </row>
+    <row r="232" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D232" s="10"/>
       <c r="E232" s="9"/>
-      <c r="BO232" s="11"/>
-      <c r="BR232" s="11"/>
-    </row>
-    <row r="233" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN232" s="11"/>
+      <c r="BQ232" s="11"/>
+    </row>
+    <row r="233" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D233" s="10"/>
       <c r="E233" s="9"/>
-      <c r="BO233" s="11"/>
-      <c r="BR233" s="11"/>
-    </row>
-    <row r="234" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN233" s="11"/>
+      <c r="BQ233" s="11"/>
+    </row>
+    <row r="234" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D234" s="10"/>
       <c r="E234" s="9"/>
-      <c r="BO234" s="11"/>
-      <c r="BR234" s="11"/>
-    </row>
-    <row r="235" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN234" s="11"/>
+      <c r="BQ234" s="11"/>
+    </row>
+    <row r="235" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D235" s="10"/>
       <c r="E235" s="9"/>
-      <c r="BO235" s="11"/>
-      <c r="BR235" s="11"/>
-    </row>
-    <row r="236" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN235" s="11"/>
+      <c r="BQ235" s="11"/>
+    </row>
+    <row r="236" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D236" s="10"/>
       <c r="E236" s="9"/>
-      <c r="BO236" s="11"/>
-      <c r="BR236" s="11"/>
-    </row>
-    <row r="237" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN236" s="11"/>
+      <c r="BQ236" s="11"/>
+    </row>
+    <row r="237" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D237" s="10"/>
       <c r="E237" s="9"/>
-      <c r="BO237" s="11"/>
-      <c r="BR237" s="11"/>
-    </row>
-    <row r="238" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN237" s="11"/>
+      <c r="BQ237" s="11"/>
+    </row>
+    <row r="238" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D238" s="10"/>
       <c r="E238" s="9"/>
-      <c r="BO238" s="11"/>
-      <c r="BR238" s="11"/>
-    </row>
-    <row r="239" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN238" s="11"/>
+      <c r="BQ238" s="11"/>
+    </row>
+    <row r="239" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D239" s="10"/>
       <c r="E239" s="9"/>
-      <c r="BO239" s="11"/>
-      <c r="BR239" s="11"/>
-    </row>
-    <row r="240" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN239" s="11"/>
+      <c r="BQ239" s="11"/>
+    </row>
+    <row r="240" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D240" s="10"/>
       <c r="E240" s="9"/>
-      <c r="BO240" s="11"/>
-      <c r="BR240" s="11"/>
-    </row>
-    <row r="241" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN240" s="11"/>
+      <c r="BQ240" s="11"/>
+    </row>
+    <row r="241" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D241" s="10"/>
       <c r="E241" s="9"/>
-      <c r="BO241" s="11"/>
-      <c r="BR241" s="11"/>
-    </row>
-    <row r="242" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN241" s="11"/>
+      <c r="BQ241" s="11"/>
+    </row>
+    <row r="242" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D242" s="10"/>
       <c r="E242" s="9"/>
-      <c r="BO242" s="11"/>
-      <c r="BR242" s="11"/>
-    </row>
-    <row r="243" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN242" s="11"/>
+      <c r="BQ242" s="11"/>
+    </row>
+    <row r="243" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D243" s="10"/>
       <c r="E243" s="9"/>
-      <c r="BO243" s="11"/>
-      <c r="BR243" s="11"/>
-    </row>
-    <row r="244" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN243" s="11"/>
+      <c r="BQ243" s="11"/>
+    </row>
+    <row r="244" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D244" s="10"/>
       <c r="E244" s="9"/>
-      <c r="BO244" s="11"/>
-      <c r="BR244" s="11"/>
-    </row>
-    <row r="245" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN244" s="11"/>
+      <c r="BQ244" s="11"/>
+    </row>
+    <row r="245" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D245" s="10"/>
       <c r="E245" s="9"/>
-      <c r="BO245" s="11"/>
-      <c r="BR245" s="11"/>
-    </row>
-    <row r="246" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN245" s="11"/>
+      <c r="BQ245" s="11"/>
+    </row>
+    <row r="246" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D246" s="10"/>
       <c r="E246" s="9"/>
-      <c r="BO246" s="11"/>
-      <c r="BR246" s="11"/>
-    </row>
-    <row r="247" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN246" s="11"/>
+      <c r="BQ246" s="11"/>
+    </row>
+    <row r="247" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D247" s="10"/>
       <c r="E247" s="9"/>
-      <c r="BO247" s="11"/>
-      <c r="BR247" s="11"/>
-    </row>
-    <row r="248" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN247" s="11"/>
+      <c r="BQ247" s="11"/>
+    </row>
+    <row r="248" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D248" s="10"/>
       <c r="E248" s="9"/>
-      <c r="BO248" s="11"/>
-      <c r="BR248" s="11"/>
-    </row>
-    <row r="249" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN248" s="11"/>
+      <c r="BQ248" s="11"/>
+    </row>
+    <row r="249" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D249" s="10"/>
       <c r="E249" s="9"/>
-      <c r="BO249" s="11"/>
-      <c r="BR249" s="11"/>
-    </row>
-    <row r="250" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN249" s="11"/>
+      <c r="BQ249" s="11"/>
+    </row>
+    <row r="250" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D250" s="10"/>
       <c r="E250" s="9"/>
-      <c r="BO250" s="11"/>
-      <c r="BR250" s="11"/>
-    </row>
-    <row r="251" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN250" s="11"/>
+      <c r="BQ250" s="11"/>
+    </row>
+    <row r="251" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D251" s="10"/>
       <c r="E251" s="9"/>
-      <c r="BO251" s="11"/>
-      <c r="BR251" s="11"/>
-    </row>
-    <row r="252" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN251" s="11"/>
+      <c r="BQ251" s="11"/>
+    </row>
+    <row r="252" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D252" s="10"/>
       <c r="E252" s="9"/>
-      <c r="BO252" s="11"/>
-      <c r="BR252" s="11"/>
-    </row>
-    <row r="253" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN252" s="11"/>
+      <c r="BQ252" s="11"/>
+    </row>
+    <row r="253" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D253" s="10"/>
       <c r="E253" s="9"/>
-      <c r="BO253" s="11"/>
-      <c r="BR253" s="11"/>
-    </row>
-    <row r="254" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN253" s="11"/>
+      <c r="BQ253" s="11"/>
+    </row>
+    <row r="254" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D254" s="10"/>
       <c r="E254" s="9"/>
-      <c r="BO254" s="11"/>
-      <c r="BR254" s="11"/>
-    </row>
-    <row r="255" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN254" s="11"/>
+      <c r="BQ254" s="11"/>
+    </row>
+    <row r="255" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D255" s="10"/>
       <c r="E255" s="9"/>
-      <c r="BO255" s="11"/>
-      <c r="BR255" s="11"/>
-    </row>
-    <row r="256" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN255" s="11"/>
+      <c r="BQ255" s="11"/>
+    </row>
+    <row r="256" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D256" s="10"/>
       <c r="E256" s="9"/>
-      <c r="BO256" s="11"/>
-      <c r="BR256" s="11"/>
-    </row>
-    <row r="257" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN256" s="11"/>
+      <c r="BQ256" s="11"/>
+    </row>
+    <row r="257" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D257" s="10"/>
       <c r="E257" s="9"/>
-      <c r="BO257" s="11"/>
-      <c r="BR257" s="11"/>
-    </row>
-    <row r="258" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN257" s="11"/>
+      <c r="BQ257" s="11"/>
+    </row>
+    <row r="258" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D258" s="10"/>
       <c r="E258" s="9"/>
-      <c r="BO258" s="11"/>
-      <c r="BR258" s="11"/>
-    </row>
-    <row r="259" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN258" s="11"/>
+      <c r="BQ258" s="11"/>
+    </row>
+    <row r="259" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D259" s="10"/>
       <c r="E259" s="9"/>
-      <c r="BR259" s="11"/>
-    </row>
-    <row r="260" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ259" s="11"/>
+    </row>
+    <row r="260" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D260" s="10"/>
       <c r="E260" s="9"/>
-      <c r="BO260" s="11"/>
-      <c r="BR260" s="11"/>
-    </row>
-    <row r="261" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN260" s="11"/>
+      <c r="BQ260" s="11"/>
+    </row>
+    <row r="261" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D261" s="10"/>
       <c r="E261" s="9"/>
-      <c r="BO261" s="11"/>
-      <c r="BR261" s="11"/>
-    </row>
-    <row r="262" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN261" s="11"/>
+      <c r="BQ261" s="11"/>
+    </row>
+    <row r="262" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D262" s="10"/>
       <c r="E262" s="9"/>
-      <c r="BO262" s="11"/>
-      <c r="BR262" s="11"/>
-    </row>
-    <row r="263" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN262" s="11"/>
+      <c r="BQ262" s="11"/>
+    </row>
+    <row r="263" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D263" s="10"/>
       <c r="E263" s="9"/>
-      <c r="BO263" s="11"/>
-      <c r="BR263" s="11"/>
-    </row>
-    <row r="264" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN263" s="11"/>
+      <c r="BQ263" s="11"/>
+    </row>
+    <row r="264" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D264" s="10"/>
       <c r="E264" s="9"/>
-      <c r="BO264" s="11"/>
-      <c r="BR264" s="11"/>
-    </row>
-    <row r="265" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN264" s="11"/>
+      <c r="BQ264" s="11"/>
+    </row>
+    <row r="265" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D265" s="10"/>
       <c r="E265" s="9"/>
-      <c r="BO265" s="11"/>
-      <c r="BR265" s="11"/>
-    </row>
-    <row r="266" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN265" s="11"/>
+      <c r="BQ265" s="11"/>
+    </row>
+    <row r="266" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D266" s="10"/>
       <c r="E266" s="9"/>
-      <c r="BO266" s="11"/>
-      <c r="BR266" s="11"/>
-    </row>
-    <row r="267" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN266" s="11"/>
+      <c r="BQ266" s="11"/>
+    </row>
+    <row r="267" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D267" s="10"/>
       <c r="E267" s="9"/>
-      <c r="BO267" s="11"/>
-      <c r="BR267" s="11"/>
-    </row>
-    <row r="268" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN267" s="11"/>
+      <c r="BQ267" s="11"/>
+    </row>
+    <row r="268" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D268" s="10"/>
       <c r="E268" s="9"/>
-      <c r="BO268" s="11"/>
-      <c r="BR268" s="11"/>
-    </row>
-    <row r="269" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN268" s="11"/>
+      <c r="BQ268" s="11"/>
+    </row>
+    <row r="269" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D269" s="10"/>
       <c r="E269" s="9"/>
-      <c r="BO269" s="11"/>
-      <c r="BR269" s="11"/>
-    </row>
-    <row r="270" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN269" s="11"/>
+      <c r="BQ269" s="11"/>
+    </row>
+    <row r="270" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D270" s="10"/>
       <c r="E270" s="9"/>
-      <c r="BO270" s="11"/>
-      <c r="BR270" s="11"/>
-    </row>
-    <row r="271" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN270" s="11"/>
+      <c r="BQ270" s="11"/>
+    </row>
+    <row r="271" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D271" s="10"/>
       <c r="E271" s="9"/>
-      <c r="BO271" s="11"/>
-      <c r="BR271" s="11"/>
-    </row>
-    <row r="272" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN271" s="11"/>
+      <c r="BQ271" s="11"/>
+    </row>
+    <row r="272" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D272" s="10"/>
       <c r="E272" s="9"/>
-      <c r="BO272" s="11"/>
-      <c r="BR272" s="11"/>
-    </row>
-    <row r="273" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN272" s="11"/>
+      <c r="BQ272" s="11"/>
+    </row>
+    <row r="273" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D273" s="10"/>
       <c r="E273" s="9"/>
-      <c r="BO273" s="11"/>
-      <c r="BR273" s="11"/>
-    </row>
-    <row r="274" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN273" s="11"/>
+      <c r="BQ273" s="11"/>
+    </row>
+    <row r="274" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D274" s="10"/>
       <c r="E274" s="9"/>
-      <c r="BO274" s="11"/>
-      <c r="BR274" s="11"/>
-    </row>
-    <row r="275" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN274" s="11"/>
+      <c r="BQ274" s="11"/>
+    </row>
+    <row r="275" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D275" s="10"/>
       <c r="E275" s="9"/>
-      <c r="BO275" s="11"/>
-      <c r="BR275" s="11"/>
-    </row>
-    <row r="276" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN275" s="11"/>
+      <c r="BQ275" s="11"/>
+    </row>
+    <row r="276" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D276" s="10"/>
       <c r="E276" s="9"/>
-      <c r="BO276" s="11"/>
-      <c r="BR276" s="11"/>
-    </row>
-    <row r="277" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN276" s="11"/>
+      <c r="BQ276" s="11"/>
+    </row>
+    <row r="277" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D277" s="10"/>
       <c r="E277" s="9"/>
-      <c r="BO277" s="11"/>
-      <c r="BR277" s="11"/>
-    </row>
-    <row r="278" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN277" s="11"/>
+      <c r="BQ277" s="11"/>
+    </row>
+    <row r="278" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D278" s="10"/>
       <c r="E278" s="9"/>
-      <c r="BO278" s="11"/>
-      <c r="BR278" s="11"/>
-    </row>
-    <row r="279" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN278" s="11"/>
+      <c r="BQ278" s="11"/>
+    </row>
+    <row r="279" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D279" s="10"/>
       <c r="E279" s="9"/>
-      <c r="BO279" s="11"/>
-      <c r="BR279" s="11"/>
-    </row>
-    <row r="280" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN279" s="11"/>
+      <c r="BQ279" s="11"/>
+    </row>
+    <row r="280" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D280" s="10"/>
       <c r="E280" s="9"/>
-      <c r="BO280" s="11"/>
-      <c r="BR280" s="11"/>
-    </row>
-    <row r="281" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN280" s="11"/>
+      <c r="BQ280" s="11"/>
+    </row>
+    <row r="281" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D281" s="10"/>
       <c r="E281" s="9"/>
-      <c r="BO281" s="11"/>
-      <c r="BR281" s="11"/>
-    </row>
-    <row r="282" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN281" s="11"/>
+      <c r="BQ281" s="11"/>
+    </row>
+    <row r="282" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D282" s="10"/>
       <c r="E282" s="9"/>
-      <c r="BO282" s="11"/>
-      <c r="BR282" s="11"/>
-    </row>
-    <row r="283" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN282" s="11"/>
+      <c r="BQ282" s="11"/>
+    </row>
+    <row r="283" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D283" s="10"/>
       <c r="E283" s="9"/>
-      <c r="BO283" s="11"/>
-      <c r="BR283" s="11"/>
-    </row>
-    <row r="284" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN283" s="11"/>
+      <c r="BQ283" s="11"/>
+    </row>
+    <row r="284" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D284" s="10"/>
       <c r="E284" s="9"/>
-      <c r="BO284" s="11"/>
-      <c r="BR284" s="11"/>
-    </row>
-    <row r="285" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN284" s="11"/>
+      <c r="BQ284" s="11"/>
+    </row>
+    <row r="285" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D285" s="10"/>
       <c r="E285" s="9"/>
-      <c r="BO285" s="11"/>
-      <c r="BR285" s="11"/>
-    </row>
-    <row r="286" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN285" s="11"/>
+      <c r="BQ285" s="11"/>
+    </row>
+    <row r="286" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D286" s="10"/>
       <c r="E286" s="9"/>
-      <c r="BO286" s="11"/>
-      <c r="BR286" s="11"/>
-    </row>
-    <row r="287" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN286" s="11"/>
+      <c r="BQ286" s="11"/>
+    </row>
+    <row r="287" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D287" s="10"/>
       <c r="E287" s="9"/>
-      <c r="BO287" s="11"/>
-      <c r="BR287" s="11"/>
-    </row>
-    <row r="288" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN287" s="11"/>
+      <c r="BQ287" s="11"/>
+    </row>
+    <row r="288" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D288" s="10"/>
       <c r="E288" s="9"/>
-      <c r="BO288" s="11"/>
-      <c r="BR288" s="11"/>
-    </row>
-    <row r="289" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN288" s="11"/>
+      <c r="BQ288" s="11"/>
+    </row>
+    <row r="289" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D289" s="10"/>
       <c r="E289" s="9"/>
-      <c r="BO289" s="11"/>
-      <c r="BR289" s="11"/>
-    </row>
-    <row r="290" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN289" s="11"/>
+      <c r="BQ289" s="11"/>
+    </row>
+    <row r="290" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D290" s="10"/>
       <c r="E290" s="9"/>
-      <c r="BO290" s="11"/>
-      <c r="BR290" s="11"/>
-    </row>
-    <row r="291" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN290" s="11"/>
+      <c r="BQ290" s="11"/>
+    </row>
+    <row r="291" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D291" s="10"/>
       <c r="E291" s="9"/>
-      <c r="BO291" s="11"/>
-      <c r="BR291" s="11"/>
-    </row>
-    <row r="292" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN291" s="11"/>
+      <c r="BQ291" s="11"/>
+    </row>
+    <row r="292" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D292" s="10"/>
       <c r="E292" s="9"/>
-      <c r="BO292" s="11"/>
-      <c r="BR292" s="11"/>
-    </row>
-    <row r="293" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN292" s="11"/>
+      <c r="BQ292" s="11"/>
+    </row>
+    <row r="293" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D293" s="10"/>
       <c r="E293" s="9"/>
-      <c r="BO293" s="11"/>
-      <c r="BR293" s="11"/>
-    </row>
-    <row r="294" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN293" s="11"/>
+      <c r="BQ293" s="11"/>
+    </row>
+    <row r="294" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D294" s="10"/>
       <c r="E294" s="9"/>
-      <c r="BO294" s="11"/>
-      <c r="BR294" s="11"/>
-    </row>
-    <row r="295" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN294" s="11"/>
+      <c r="BQ294" s="11"/>
+    </row>
+    <row r="295" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D295" s="10"/>
       <c r="E295" s="9"/>
-      <c r="BO295" s="11"/>
-      <c r="BR295" s="11"/>
-    </row>
-    <row r="296" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN295" s="11"/>
+      <c r="BQ295" s="11"/>
+    </row>
+    <row r="296" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D296" s="10"/>
       <c r="E296" s="9"/>
-      <c r="BO296" s="11"/>
-      <c r="BR296" s="11"/>
-    </row>
-    <row r="297" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN296" s="11"/>
+      <c r="BQ296" s="11"/>
+    </row>
+    <row r="297" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D297" s="10"/>
       <c r="E297" s="9"/>
-      <c r="BO297" s="11"/>
-      <c r="BR297" s="11"/>
-    </row>
-    <row r="298" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN297" s="11"/>
+      <c r="BQ297" s="11"/>
+    </row>
+    <row r="298" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D298" s="10"/>
       <c r="E298" s="9"/>
-      <c r="BO298" s="11"/>
-      <c r="BR298" s="11"/>
-    </row>
-    <row r="299" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN298" s="11"/>
+      <c r="BQ298" s="11"/>
+    </row>
+    <row r="299" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D299" s="10"/>
       <c r="E299" s="9"/>
-      <c r="BO299" s="11"/>
-      <c r="BR299" s="11"/>
-    </row>
-    <row r="300" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN299" s="11"/>
+      <c r="BQ299" s="11"/>
+    </row>
+    <row r="300" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D300" s="10"/>
       <c r="E300" s="9"/>
-      <c r="BO300" s="11"/>
-      <c r="BR300" s="11"/>
-    </row>
-    <row r="301" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN300" s="11"/>
+      <c r="BQ300" s="11"/>
+    </row>
+    <row r="301" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D301" s="10"/>
       <c r="E301" s="9"/>
-      <c r="BO301" s="11"/>
-      <c r="BR301" s="11"/>
-    </row>
-    <row r="302" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN301" s="11"/>
+      <c r="BQ301" s="11"/>
+    </row>
+    <row r="302" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D302" s="10"/>
       <c r="E302" s="9"/>
-      <c r="BO302" s="11"/>
-      <c r="BR302" s="11"/>
-    </row>
-    <row r="303" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN302" s="11"/>
+      <c r="BQ302" s="11"/>
+    </row>
+    <row r="303" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D303" s="10"/>
       <c r="E303" s="9"/>
-      <c r="BO303" s="11"/>
-      <c r="BR303" s="11"/>
-    </row>
-    <row r="304" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN303" s="11"/>
+      <c r="BQ303" s="11"/>
+    </row>
+    <row r="304" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D304" s="10"/>
       <c r="E304" s="9"/>
-      <c r="BO304" s="11"/>
-      <c r="BR304" s="11"/>
-    </row>
-    <row r="305" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN304" s="11"/>
+      <c r="BQ304" s="11"/>
+    </row>
+    <row r="305" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D305" s="10"/>
       <c r="E305" s="9"/>
-      <c r="BO305" s="11"/>
-      <c r="BR305" s="11"/>
-    </row>
-    <row r="306" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN305" s="11"/>
+      <c r="BQ305" s="11"/>
+    </row>
+    <row r="306" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D306" s="10"/>
       <c r="E306" s="9"/>
-      <c r="BO306" s="11"/>
-      <c r="BR306" s="11"/>
-    </row>
-    <row r="307" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN306" s="11"/>
+      <c r="BQ306" s="11"/>
+    </row>
+    <row r="307" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D307" s="10"/>
       <c r="E307" s="9"/>
-      <c r="BO307" s="11"/>
-      <c r="BR307" s="11"/>
-    </row>
-    <row r="308" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN307" s="11"/>
+      <c r="BQ307" s="11"/>
+    </row>
+    <row r="308" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D308" s="10"/>
       <c r="E308" s="9"/>
-      <c r="BO308" s="11"/>
-      <c r="BR308" s="11"/>
-    </row>
-    <row r="309" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN308" s="11"/>
+      <c r="BQ308" s="11"/>
+    </row>
+    <row r="309" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D309" s="10"/>
       <c r="E309" s="9"/>
-      <c r="BO309" s="11"/>
-      <c r="BR309" s="11"/>
-    </row>
-    <row r="310" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN309" s="11"/>
+      <c r="BQ309" s="11"/>
+    </row>
+    <row r="310" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D310" s="10"/>
       <c r="E310" s="9"/>
-      <c r="BO310" s="11"/>
-      <c r="BR310" s="11"/>
-    </row>
-    <row r="311" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN310" s="11"/>
+      <c r="BQ310" s="11"/>
+    </row>
+    <row r="311" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D311" s="10"/>
       <c r="E311" s="9"/>
-      <c r="BO311" s="11"/>
-      <c r="BR311" s="11"/>
-    </row>
-    <row r="312" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN311" s="11"/>
+      <c r="BQ311" s="11"/>
+    </row>
+    <row r="312" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D312" s="10"/>
       <c r="E312" s="9"/>
-      <c r="BO312" s="11"/>
-      <c r="BR312" s="11"/>
-    </row>
-    <row r="313" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN312" s="11"/>
+      <c r="BQ312" s="11"/>
+    </row>
+    <row r="313" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D313" s="10"/>
       <c r="E313" s="9"/>
-      <c r="BO313" s="11"/>
-      <c r="BR313" s="11"/>
-    </row>
-    <row r="314" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN313" s="11"/>
+      <c r="BQ313" s="11"/>
+    </row>
+    <row r="314" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D314" s="10"/>
       <c r="E314" s="9"/>
-      <c r="BO314" s="11"/>
-      <c r="BR314" s="11"/>
-    </row>
-    <row r="315" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN314" s="11"/>
+      <c r="BQ314" s="11"/>
+    </row>
+    <row r="315" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D315" s="10"/>
       <c r="E315" s="9"/>
-      <c r="BR315" s="11"/>
-    </row>
-    <row r="316" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ315" s="11"/>
+    </row>
+    <row r="316" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D316" s="10"/>
       <c r="E316" s="9"/>
-      <c r="BR316" s="11"/>
-    </row>
-    <row r="317" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ316" s="11"/>
+    </row>
+    <row r="317" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D317" s="10"/>
       <c r="E317" s="9"/>
-      <c r="BR317" s="11"/>
-    </row>
-    <row r="318" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ317" s="11"/>
+    </row>
+    <row r="318" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D318" s="10"/>
       <c r="E318" s="9"/>
-      <c r="BO318" s="11"/>
-      <c r="BR318" s="11"/>
-    </row>
-    <row r="319" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN318" s="11"/>
+      <c r="BQ318" s="11"/>
+    </row>
+    <row r="319" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D319" s="10"/>
       <c r="E319" s="9"/>
-      <c r="BO319" s="11"/>
-      <c r="BR319" s="11"/>
-    </row>
-    <row r="320" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN319" s="11"/>
+      <c r="BQ319" s="11"/>
+    </row>
+    <row r="320" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D320" s="10"/>
       <c r="E320" s="9"/>
-      <c r="BO320" s="11"/>
-      <c r="BR320" s="11"/>
-    </row>
-    <row r="321" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN320" s="11"/>
+      <c r="BQ320" s="11"/>
+    </row>
+    <row r="321" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D321" s="10"/>
       <c r="E321" s="9"/>
-      <c r="BO321" s="11"/>
-      <c r="BR321" s="11"/>
-    </row>
-    <row r="322" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN321" s="11"/>
+      <c r="BQ321" s="11"/>
+    </row>
+    <row r="322" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D322" s="10"/>
       <c r="E322" s="9"/>
-      <c r="BO322" s="11"/>
-      <c r="BR322" s="11"/>
-    </row>
-    <row r="323" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN322" s="11"/>
+      <c r="BQ322" s="11"/>
+    </row>
+    <row r="323" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D323" s="10"/>
       <c r="E323" s="9"/>
-      <c r="BO323" s="11"/>
-      <c r="BR323" s="11"/>
-    </row>
-    <row r="324" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN323" s="11"/>
+      <c r="BQ323" s="11"/>
+    </row>
+    <row r="324" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D324" s="10"/>
       <c r="E324" s="9"/>
-      <c r="BO324" s="11"/>
-      <c r="BR324" s="11"/>
-    </row>
-    <row r="325" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN324" s="11"/>
+      <c r="BQ324" s="11"/>
+    </row>
+    <row r="325" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D325" s="10"/>
       <c r="E325" s="9"/>
-      <c r="BO325" s="11"/>
-      <c r="BR325" s="11"/>
-    </row>
-    <row r="326" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN325" s="11"/>
+      <c r="BQ325" s="11"/>
+    </row>
+    <row r="326" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D326" s="10"/>
       <c r="E326" s="9"/>
-      <c r="BO326" s="11"/>
-      <c r="BR326" s="11"/>
-    </row>
-    <row r="327" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN326" s="11"/>
+      <c r="BQ326" s="11"/>
+    </row>
+    <row r="327" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D327" s="10"/>
       <c r="E327" s="9"/>
-      <c r="BO327" s="11"/>
-      <c r="BR327" s="11"/>
-    </row>
-    <row r="328" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN327" s="11"/>
+      <c r="BQ327" s="11"/>
+    </row>
+    <row r="328" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D328" s="10"/>
       <c r="E328" s="9"/>
-      <c r="BO328" s="11"/>
-      <c r="BR328" s="11"/>
-    </row>
-    <row r="329" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN328" s="11"/>
+      <c r="BQ328" s="11"/>
+    </row>
+    <row r="329" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D329" s="10"/>
       <c r="E329" s="9"/>
-      <c r="BO329" s="11"/>
-      <c r="BR329" s="11"/>
-    </row>
-    <row r="330" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN329" s="11"/>
+      <c r="BQ329" s="11"/>
+    </row>
+    <row r="330" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D330" s="10"/>
       <c r="E330" s="9"/>
-      <c r="BO330" s="11"/>
-      <c r="BR330" s="11"/>
-    </row>
-    <row r="331" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN330" s="11"/>
+      <c r="BQ330" s="11"/>
+    </row>
+    <row r="331" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D331" s="10"/>
       <c r="E331" s="9"/>
-      <c r="BO331" s="11"/>
-      <c r="BR331" s="11"/>
-    </row>
-    <row r="332" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN331" s="11"/>
+      <c r="BQ331" s="11"/>
+    </row>
+    <row r="332" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D332" s="10"/>
       <c r="E332" s="9"/>
-      <c r="BO332" s="11"/>
-      <c r="BR332" s="11"/>
-    </row>
-    <row r="333" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN332" s="11"/>
+      <c r="BQ332" s="11"/>
+    </row>
+    <row r="333" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D333" s="10"/>
       <c r="E333" s="9"/>
-      <c r="BO333" s="11"/>
-      <c r="BR333" s="11"/>
-    </row>
-    <row r="334" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN333" s="11"/>
+      <c r="BQ333" s="11"/>
+    </row>
+    <row r="334" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D334" s="10"/>
       <c r="E334" s="9"/>
-      <c r="BO334" s="11"/>
-      <c r="BR334" s="11"/>
-    </row>
-    <row r="335" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN334" s="11"/>
+      <c r="BQ334" s="11"/>
+    </row>
+    <row r="335" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D335" s="10"/>
       <c r="E335" s="9"/>
-      <c r="BO335" s="11"/>
-      <c r="BR335" s="11"/>
-    </row>
-    <row r="336" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN335" s="11"/>
+      <c r="BQ335" s="11"/>
+    </row>
+    <row r="336" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D336" s="10"/>
       <c r="E336" s="9"/>
-      <c r="BO336" s="11"/>
-      <c r="BR336" s="11"/>
-    </row>
-    <row r="337" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN336" s="11"/>
+      <c r="BQ336" s="11"/>
+    </row>
+    <row r="337" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D337" s="10"/>
       <c r="E337" s="9"/>
-      <c r="BO337" s="11"/>
-      <c r="BR337" s="11"/>
-    </row>
-    <row r="338" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN337" s="11"/>
+      <c r="BQ337" s="11"/>
+    </row>
+    <row r="338" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D338" s="10"/>
       <c r="E338" s="9"/>
-      <c r="BO338" s="11"/>
-      <c r="BR338" s="11"/>
-    </row>
-    <row r="339" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN338" s="11"/>
+      <c r="BQ338" s="11"/>
+    </row>
+    <row r="339" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D339" s="10"/>
       <c r="E339" s="9"/>
-      <c r="BO339" s="11"/>
-      <c r="BR339" s="11"/>
-    </row>
-    <row r="340" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN339" s="11"/>
+      <c r="BQ339" s="11"/>
+    </row>
+    <row r="340" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D340" s="10"/>
       <c r="E340" s="9"/>
-      <c r="BO340" s="11"/>
-      <c r="BR340" s="11"/>
-    </row>
-    <row r="341" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN340" s="11"/>
+      <c r="BQ340" s="11"/>
+    </row>
+    <row r="341" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D341" s="10"/>
       <c r="E341" s="9"/>
-      <c r="BO341" s="11"/>
-      <c r="BR341" s="11"/>
-    </row>
-    <row r="342" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN341" s="11"/>
+      <c r="BQ341" s="11"/>
+    </row>
+    <row r="342" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D342" s="10"/>
       <c r="E342" s="9"/>
-      <c r="BO342" s="11"/>
-      <c r="BR342" s="11"/>
-    </row>
-    <row r="343" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN342" s="11"/>
+      <c r="BQ342" s="11"/>
+    </row>
+    <row r="343" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D343" s="10"/>
       <c r="E343" s="9"/>
-      <c r="BO343" s="11"/>
-      <c r="BR343" s="11"/>
-    </row>
-    <row r="344" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN343" s="11"/>
+      <c r="BQ343" s="11"/>
+    </row>
+    <row r="344" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D344" s="10"/>
       <c r="E344" s="9"/>
-      <c r="BO344" s="11"/>
-      <c r="BR344" s="11"/>
-    </row>
-    <row r="345" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN344" s="11"/>
+      <c r="BQ344" s="11"/>
+    </row>
+    <row r="345" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D345" s="10"/>
       <c r="E345" s="9"/>
-      <c r="BO345" s="11"/>
-      <c r="BR345" s="11"/>
-    </row>
-    <row r="346" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN345" s="11"/>
+      <c r="BQ345" s="11"/>
+    </row>
+    <row r="346" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D346" s="10"/>
       <c r="E346" s="9"/>
-      <c r="BO346" s="11"/>
-      <c r="BR346" s="11"/>
-    </row>
-    <row r="347" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN346" s="11"/>
+      <c r="BQ346" s="11"/>
+    </row>
+    <row r="347" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D347" s="10"/>
       <c r="E347" s="9"/>
-      <c r="BO347" s="11"/>
-      <c r="BR347" s="11"/>
-    </row>
-    <row r="348" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN347" s="11"/>
+      <c r="BQ347" s="11"/>
+    </row>
+    <row r="348" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D348" s="10"/>
       <c r="E348" s="9"/>
-      <c r="BO348" s="11"/>
-      <c r="BR348" s="11"/>
-    </row>
-    <row r="349" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN348" s="11"/>
+      <c r="BQ348" s="11"/>
+    </row>
+    <row r="349" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D349" s="10"/>
       <c r="E349" s="9"/>
-      <c r="BO349" s="11"/>
-      <c r="BR349" s="11"/>
-    </row>
-    <row r="350" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN349" s="11"/>
+      <c r="BQ349" s="11"/>
+    </row>
+    <row r="350" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D350" s="10"/>
       <c r="E350" s="9"/>
-      <c r="BO350" s="11"/>
-      <c r="BR350" s="11"/>
-    </row>
-    <row r="351" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN350" s="11"/>
+      <c r="BQ350" s="11"/>
+    </row>
+    <row r="351" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D351" s="10"/>
       <c r="E351" s="9"/>
-      <c r="BO351" s="11"/>
-      <c r="BR351" s="11"/>
-    </row>
-    <row r="352" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN351" s="11"/>
+      <c r="BQ351" s="11"/>
+    </row>
+    <row r="352" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D352" s="10"/>
       <c r="E352" s="9"/>
-      <c r="BR352" s="11"/>
-    </row>
-    <row r="353" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ352" s="11"/>
+    </row>
+    <row r="353" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D353" s="10"/>
       <c r="E353" s="9"/>
-      <c r="BR353" s="11"/>
-    </row>
-    <row r="354" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ353" s="11"/>
+    </row>
+    <row r="354" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D354" s="10"/>
       <c r="E354" s="9"/>
-      <c r="BO354" s="11"/>
-      <c r="BR354" s="11"/>
-    </row>
-    <row r="355" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN354" s="11"/>
+      <c r="BQ354" s="11"/>
+    </row>
+    <row r="355" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D355" s="10"/>
       <c r="E355" s="9"/>
-      <c r="BO355" s="11"/>
-      <c r="BR355" s="11"/>
-    </row>
-    <row r="356" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN355" s="11"/>
+      <c r="BQ355" s="11"/>
+    </row>
+    <row r="356" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D356" s="10"/>
       <c r="E356" s="9"/>
-      <c r="BO356" s="11"/>
-      <c r="BR356" s="11"/>
-    </row>
-    <row r="357" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN356" s="11"/>
+      <c r="BQ356" s="11"/>
+    </row>
+    <row r="357" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D357" s="10"/>
       <c r="E357" s="9"/>
-      <c r="BO357" s="11"/>
-      <c r="BR357" s="11"/>
-    </row>
-    <row r="358" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN357" s="11"/>
+      <c r="BQ357" s="11"/>
+    </row>
+    <row r="358" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D358" s="10"/>
       <c r="E358" s="9"/>
-      <c r="BO358" s="11"/>
-      <c r="BR358" s="11"/>
-    </row>
-    <row r="359" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN358" s="11"/>
+      <c r="BQ358" s="11"/>
+    </row>
+    <row r="359" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D359" s="10"/>
       <c r="E359" s="9"/>
-      <c r="BO359" s="11"/>
-      <c r="BR359" s="11"/>
-    </row>
-    <row r="360" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN359" s="11"/>
+      <c r="BQ359" s="11"/>
+    </row>
+    <row r="360" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D360" s="10"/>
       <c r="E360" s="9"/>
-      <c r="BO360" s="11"/>
-      <c r="BR360" s="11"/>
-    </row>
-    <row r="361" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN360" s="11"/>
+      <c r="BQ360" s="11"/>
+    </row>
+    <row r="361" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D361" s="10"/>
       <c r="E361" s="9"/>
-      <c r="BO361" s="11"/>
-      <c r="BR361" s="11"/>
-    </row>
-    <row r="362" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN361" s="11"/>
+      <c r="BQ361" s="11"/>
+    </row>
+    <row r="362" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D362" s="10"/>
       <c r="E362" s="9"/>
-      <c r="BO362" s="11"/>
-      <c r="BR362" s="11"/>
-    </row>
-    <row r="363" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN362" s="11"/>
+      <c r="BQ362" s="11"/>
+    </row>
+    <row r="363" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D363" s="10"/>
       <c r="E363" s="9"/>
-      <c r="BO363" s="11"/>
-      <c r="BR363" s="11"/>
-    </row>
-    <row r="364" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN363" s="11"/>
+      <c r="BQ363" s="11"/>
+    </row>
+    <row r="364" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D364" s="10"/>
       <c r="E364" s="9"/>
-      <c r="BO364" s="11"/>
-      <c r="BR364" s="11"/>
-    </row>
-    <row r="365" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN364" s="11"/>
+      <c r="BQ364" s="11"/>
+    </row>
+    <row r="365" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D365" s="10"/>
       <c r="E365" s="9"/>
-      <c r="BO365" s="11"/>
-      <c r="BR365" s="11"/>
-    </row>
-    <row r="366" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN365" s="11"/>
+      <c r="BQ365" s="11"/>
+    </row>
+    <row r="366" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D366" s="10"/>
       <c r="E366" s="9"/>
-      <c r="BO366" s="11"/>
-      <c r="BR366" s="11"/>
-    </row>
-    <row r="367" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN366" s="11"/>
+      <c r="BQ366" s="11"/>
+    </row>
+    <row r="367" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D367" s="10"/>
       <c r="E367" s="9"/>
-      <c r="BO367" s="11"/>
-      <c r="BR367" s="11"/>
-    </row>
-    <row r="368" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN367" s="11"/>
+      <c r="BQ367" s="11"/>
+    </row>
+    <row r="368" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D368" s="10"/>
       <c r="E368" s="9"/>
-      <c r="BO368" s="11"/>
-      <c r="BR368" s="11"/>
-    </row>
-    <row r="369" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN368" s="11"/>
+      <c r="BQ368" s="11"/>
+    </row>
+    <row r="369" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D369" s="10"/>
       <c r="E369" s="9"/>
-      <c r="BO369" s="11"/>
-      <c r="BR369" s="11"/>
-    </row>
-    <row r="370" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN369" s="11"/>
+      <c r="BQ369" s="11"/>
+    </row>
+    <row r="370" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D370" s="10"/>
       <c r="E370" s="9"/>
-      <c r="BO370" s="11"/>
-      <c r="BR370" s="11"/>
-    </row>
-    <row r="371" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN370" s="11"/>
+      <c r="BQ370" s="11"/>
+    </row>
+    <row r="371" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D371" s="10"/>
       <c r="E371" s="9"/>
-      <c r="BO371" s="11"/>
-      <c r="BR371" s="11"/>
-    </row>
-    <row r="372" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN371" s="11"/>
+      <c r="BQ371" s="11"/>
+    </row>
+    <row r="372" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D372" s="10"/>
       <c r="E372" s="9"/>
-      <c r="BO372" s="11"/>
-      <c r="BR372" s="11"/>
-    </row>
-    <row r="373" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN372" s="11"/>
+      <c r="BQ372" s="11"/>
+    </row>
+    <row r="373" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D373" s="10"/>
       <c r="E373" s="9"/>
-      <c r="BO373" s="11"/>
-      <c r="BR373" s="11"/>
-    </row>
-    <row r="374" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN373" s="11"/>
+      <c r="BQ373" s="11"/>
+    </row>
+    <row r="374" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D374" s="10"/>
       <c r="E374" s="9"/>
-      <c r="BO374" s="11"/>
-      <c r="BR374" s="11"/>
-    </row>
-    <row r="375" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN374" s="11"/>
+      <c r="BQ374" s="11"/>
+    </row>
+    <row r="375" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D375" s="10"/>
       <c r="E375" s="9"/>
-      <c r="BO375" s="11"/>
-      <c r="BR375" s="11"/>
-    </row>
-    <row r="376" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN375" s="11"/>
+      <c r="BQ375" s="11"/>
+    </row>
+    <row r="376" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D376" s="10"/>
       <c r="E376" s="9"/>
-      <c r="BO376" s="11"/>
-      <c r="BR376" s="11"/>
-    </row>
-    <row r="377" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN376" s="11"/>
+      <c r="BQ376" s="11"/>
+    </row>
+    <row r="377" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D377" s="10"/>
       <c r="E377" s="9"/>
-      <c r="BR377" s="11"/>
-    </row>
-    <row r="378" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ377" s="11"/>
+    </row>
+    <row r="378" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D378" s="10"/>
       <c r="E378" s="9"/>
-      <c r="BR378" s="11"/>
-    </row>
-    <row r="379" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ378" s="11"/>
+    </row>
+    <row r="379" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D379" s="10"/>
       <c r="E379" s="9"/>
-      <c r="BO379" s="11"/>
-      <c r="BR379" s="11"/>
-    </row>
-    <row r="380" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN379" s="11"/>
+      <c r="BQ379" s="11"/>
+    </row>
+    <row r="380" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D380" s="10"/>
       <c r="E380" s="9"/>
-      <c r="BO380" s="11"/>
-      <c r="BR380" s="11"/>
-    </row>
-    <row r="381" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN380" s="11"/>
+      <c r="BQ380" s="11"/>
+    </row>
+    <row r="381" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D381" s="10"/>
       <c r="E381" s="9"/>
-      <c r="BR381" s="11"/>
-    </row>
-    <row r="382" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ381" s="11"/>
+    </row>
+    <row r="382" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D382" s="10"/>
       <c r="E382" s="9"/>
-      <c r="BR382" s="11"/>
-    </row>
-    <row r="383" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ382" s="11"/>
+    </row>
+    <row r="383" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D383" s="10"/>
       <c r="E383" s="9"/>
-      <c r="BO383" s="11"/>
-      <c r="BR383" s="11"/>
-    </row>
-    <row r="384" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN383" s="11"/>
+      <c r="BQ383" s="11"/>
+    </row>
+    <row r="384" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D384" s="10"/>
       <c r="E384" s="9"/>
-      <c r="BO384" s="11"/>
-      <c r="BR384" s="11"/>
-    </row>
-    <row r="385" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN384" s="11"/>
+      <c r="BQ384" s="11"/>
+    </row>
+    <row r="385" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D385" s="10"/>
       <c r="E385" s="9"/>
-      <c r="BO385" s="11"/>
-      <c r="BR385" s="11"/>
-    </row>
-    <row r="386" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN385" s="11"/>
+      <c r="BQ385" s="11"/>
+    </row>
+    <row r="386" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D386" s="10"/>
       <c r="E386" s="9"/>
-      <c r="BO386" s="11"/>
-      <c r="BR386" s="11"/>
-    </row>
-    <row r="387" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN386" s="11"/>
+      <c r="BQ386" s="11"/>
+    </row>
+    <row r="387" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D387" s="10"/>
       <c r="E387" s="9"/>
-      <c r="BO387" s="11"/>
-      <c r="BR387" s="11"/>
-    </row>
-    <row r="388" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN387" s="11"/>
+      <c r="BQ387" s="11"/>
+    </row>
+    <row r="388" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D388" s="10"/>
       <c r="E388" s="9"/>
-      <c r="BO388" s="11"/>
-      <c r="BR388" s="11"/>
-    </row>
-    <row r="389" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN388" s="11"/>
+      <c r="BQ388" s="11"/>
+    </row>
+    <row r="389" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D389" s="10"/>
       <c r="E389" s="9"/>
-      <c r="BO389" s="11"/>
-      <c r="BR389" s="11"/>
-    </row>
-    <row r="390" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN389" s="11"/>
+      <c r="BQ389" s="11"/>
+    </row>
+    <row r="390" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D390" s="10"/>
       <c r="E390" s="9"/>
-      <c r="BO390" s="11"/>
-      <c r="BR390" s="11"/>
-    </row>
-    <row r="391" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN390" s="11"/>
+      <c r="BQ390" s="11"/>
+    </row>
+    <row r="391" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D391" s="10"/>
       <c r="E391" s="9"/>
-      <c r="BO391" s="11"/>
-      <c r="BR391" s="11"/>
-    </row>
-    <row r="392" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN391" s="11"/>
+      <c r="BQ391" s="11"/>
+    </row>
+    <row r="392" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D392" s="10"/>
       <c r="E392" s="9"/>
-      <c r="BO392" s="11"/>
-      <c r="BR392" s="11"/>
-    </row>
-    <row r="393" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN392" s="11"/>
+      <c r="BQ392" s="11"/>
+    </row>
+    <row r="393" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D393" s="10"/>
       <c r="E393" s="9"/>
-      <c r="BO393" s="11"/>
-      <c r="BR393" s="11"/>
-    </row>
-    <row r="394" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN393" s="11"/>
+      <c r="BQ393" s="11"/>
+    </row>
+    <row r="394" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D394" s="10"/>
       <c r="E394" s="9"/>
-      <c r="BO394" s="11"/>
-      <c r="BR394" s="11"/>
-    </row>
-    <row r="395" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN394" s="11"/>
+      <c r="BQ394" s="11"/>
+    </row>
+    <row r="395" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D395" s="10"/>
       <c r="E395" s="9"/>
-      <c r="BO395" s="11"/>
-      <c r="BR395" s="11"/>
-    </row>
-    <row r="396" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN395" s="11"/>
+      <c r="BQ395" s="11"/>
+    </row>
+    <row r="396" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D396" s="10"/>
       <c r="E396" s="9"/>
-      <c r="BO396" s="11"/>
-      <c r="BR396" s="11"/>
-    </row>
-    <row r="397" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN396" s="11"/>
+      <c r="BQ396" s="11"/>
+    </row>
+    <row r="397" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D397" s="10"/>
       <c r="E397" s="9"/>
-      <c r="BO397" s="11"/>
-      <c r="BR397" s="11"/>
-    </row>
-    <row r="398" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN397" s="11"/>
+      <c r="BQ397" s="11"/>
+    </row>
+    <row r="398" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D398" s="10"/>
       <c r="E398" s="9"/>
-      <c r="BO398" s="11"/>
-      <c r="BR398" s="11"/>
-    </row>
-    <row r="399" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN398" s="11"/>
+      <c r="BQ398" s="11"/>
+    </row>
+    <row r="399" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D399" s="10"/>
       <c r="E399" s="9"/>
-      <c r="BO399" s="11"/>
-    </row>
-    <row r="400" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN399" s="11"/>
+    </row>
+    <row r="400" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D400" s="10"/>
       <c r="E400" s="9"/>
     </row>
@@ -5978,334 +5979,334 @@
   <sheetData>
     <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1" t="s">
         <v>141</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>142</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>143</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>144</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="U1" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="V1" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="Y1" t="s">
         <v>158</v>
       </c>
-      <c r="U1" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="V1" s="4" t="s">
+      <c r="Z1" t="s">
         <v>159</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="AB1" t="s">
         <v>161</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AC1" t="s">
         <v>162</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AD1" t="s">
         <v>163</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AE1" t="s">
         <v>164</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AF1" t="s">
         <v>165</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AG1" t="s">
         <v>166</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AH1" t="s">
         <v>167</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AI1" t="s">
         <v>168</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AJ1" t="s">
         <v>169</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AK1" t="s">
         <v>170</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AL1" t="s">
         <v>171</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AM1" t="s">
         <v>172</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AN1" t="s">
         <v>173</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AO1" t="s">
         <v>174</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AP1" t="s">
         <v>175</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AQ1" t="s">
         <v>176</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AR1" s="13" t="s">
+        <v>516</v>
+      </c>
+      <c r="AS1" s="13" t="s">
+        <v>517</v>
+      </c>
+      <c r="AT1" t="s">
         <v>177</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AU1" t="s">
         <v>178</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AV1" t="s">
         <v>179</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AW1" t="s">
         <v>180</v>
       </c>
-      <c r="AR1" s="13" t="s">
-        <v>520</v>
-      </c>
-      <c r="AS1" s="13" t="s">
-        <v>521</v>
-      </c>
-      <c r="AT1" t="s">
+      <c r="AX1" t="s">
         <v>181</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AY1" t="s">
         <v>182</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AZ1" t="s">
         <v>183</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="BA1" t="s">
         <v>184</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BB1" t="s">
         <v>185</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BC1" t="s">
         <v>186</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BD1" t="s">
         <v>187</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BE1" t="s">
         <v>188</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BF1" t="s">
         <v>189</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BG1" t="s">
         <v>190</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BH1" t="s">
         <v>191</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BJ1" t="s">
+        <v>191</v>
+      </c>
+      <c r="BK1" t="s">
         <v>192</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BL1" t="s">
         <v>193</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BM1" t="s">
         <v>194</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BN1" t="s">
         <v>195</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>195</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="BO1" t="s">
         <v>196</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BP1" t="s">
         <v>197</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BQ1" t="s">
         <v>198</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BR1" t="s">
         <v>199</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BS1" t="s">
         <v>200</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BT1" t="s">
         <v>201</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BU1" t="s">
         <v>202</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BV1" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BW1" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BX1" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BY1" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="BV1" s="5" t="s">
+      <c r="BZ1" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="BW1" s="5" t="s">
+      <c r="CA1" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="BX1" s="5" t="s">
+      <c r="CB1" t="s">
         <v>209</v>
       </c>
-      <c r="BY1" s="5" t="s">
+      <c r="CC1" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="BZ1" s="5" t="s">
+      <c r="CD1" t="s">
         <v>211</v>
       </c>
-      <c r="CA1" s="5" t="s">
+      <c r="CE1" t="s">
         <v>212</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CF1" t="s">
         <v>213</v>
       </c>
-      <c r="CC1" s="5" t="s">
+      <c r="CG1" t="s">
         <v>214</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CH1" t="s">
         <v>215</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CI1" t="s">
         <v>216</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CJ1" t="s">
         <v>217</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CK1" t="s">
         <v>218</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CL1" t="s">
         <v>219</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CM1" t="s">
         <v>220</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CN1" t="s">
         <v>221</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CO1" t="s">
         <v>222</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CP1" t="s">
         <v>223</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CQ1" t="s">
         <v>224</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CR1" t="s">
+        <v>201</v>
+      </c>
+      <c r="CS1" t="s">
         <v>225</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CT1" t="s">
         <v>226</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CU1" t="s">
         <v>227</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CV1" t="s">
         <v>228</v>
       </c>
-      <c r="CR1" t="s">
-        <v>205</v>
-      </c>
-      <c r="CS1" t="s">
+      <c r="CW1" t="s">
         <v>229</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CX1" t="s">
         <v>230</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CY1" t="s">
         <v>231</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CZ1" t="s">
+        <v>230</v>
+      </c>
+      <c r="DA1" t="s">
         <v>232</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="DB1" t="s">
         <v>233</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="DC1" t="s">
         <v>234</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="DD1" t="s">
         <v>235</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>234</v>
-      </c>
-      <c r="DA1" t="s">
+      <c r="DE1" t="s">
         <v>236</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DF1" t="s">
         <v>237</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DG1" t="s">
         <v>238</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DH1" t="s">
         <v>239</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DI1" t="s">
         <v>240</v>
-      </c>
-      <c r="DF1" t="s">
-        <v>241</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>242</v>
-      </c>
-      <c r="DH1" t="s">
-        <v>243</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:113" x14ac:dyDescent="0.25">
@@ -6313,337 +6314,337 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" t="s">
+        <v>243</v>
+      </c>
+      <c r="I2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J2" t="s">
+        <v>245</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>260</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>261</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>263</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>264</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>265</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>267</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>268</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>269</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>270</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>271</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>272</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>273</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>274</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>275</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>276</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>277</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>278</v>
+      </c>
+      <c r="AR2" s="13" t="s">
+        <v>518</v>
+      </c>
+      <c r="AS2" s="13" t="s">
+        <v>519</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>279</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>281</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>282</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>283</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>284</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>285</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>286</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>287</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>288</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>289</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>290</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>292</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>293</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>294</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>295</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>296</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>297</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>298</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>299</v>
+      </c>
+      <c r="BO2" t="s">
         <v>77</v>
       </c>
-      <c r="E2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F2" t="s">
-        <v>246</v>
-      </c>
-      <c r="G2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" t="s">
-        <v>247</v>
-      </c>
-      <c r="I2" t="s">
-        <v>248</v>
-      </c>
-      <c r="J2" t="s">
-        <v>249</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>264</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>265</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>267</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>268</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>269</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>270</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>271</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>272</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>273</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>274</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>275</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>276</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>277</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>278</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>280</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>281</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>282</v>
-      </c>
-      <c r="AR2" s="13" t="s">
-        <v>522</v>
-      </c>
-      <c r="AS2" s="13" t="s">
-        <v>523</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>283</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>284</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>285</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>286</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>287</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>288</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>289</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>290</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>292</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>293</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>294</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>295</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>296</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>297</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>298</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>299</v>
-      </c>
-      <c r="BK2" t="s">
+      <c r="BP2" t="s">
         <v>300</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BQ2" t="s">
         <v>301</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BR2" t="s">
         <v>302</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BS2" t="s">
         <v>303</v>
       </c>
-      <c r="BO2" t="s">
-        <v>79</v>
-      </c>
-      <c r="BP2" t="s">
+      <c r="BT2" t="s">
         <v>304</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BU2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV2" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BW2" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BX2" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BY2" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="BU2" t="s">
-        <v>95</v>
-      </c>
-      <c r="BV2" s="5" t="s">
+      <c r="BZ2" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="BW2" s="5" t="s">
+      <c r="CA2" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="BX2" s="5" t="s">
+      <c r="CB2" t="s">
         <v>311</v>
       </c>
-      <c r="BY2" s="5" t="s">
+      <c r="CC2" t="s">
         <v>312</v>
       </c>
-      <c r="BZ2" s="5" t="s">
+      <c r="CD2" t="s">
         <v>313</v>
       </c>
-      <c r="CA2" s="5" t="s">
+      <c r="CE2" t="s">
         <v>314</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CF2" t="s">
         <v>315</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CG2" t="s">
         <v>316</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CH2" t="s">
         <v>317</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CI2" t="s">
         <v>318</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CJ2" t="s">
         <v>319</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CK2" t="s">
         <v>320</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CL2" t="s">
         <v>321</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CM2" t="s">
         <v>322</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CN2" t="s">
         <v>323</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CO2" t="s">
         <v>324</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CP2" t="s">
         <v>325</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CQ2" t="s">
         <v>326</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CR2" t="s">
         <v>327</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CS2" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CT2" t="s">
         <v>329</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CU2" t="s">
         <v>330</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CV2" t="s">
         <v>331</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CW2" t="s">
         <v>332</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CX2" t="s">
         <v>333</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CY2" t="s">
         <v>334</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CZ2" t="s">
         <v>335</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="DA2" t="s">
         <v>336</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="DB2" t="s">
         <v>337</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DC2" t="s">
         <v>338</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DD2" t="s">
         <v>339</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DE2" t="s">
         <v>340</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DF2" t="s">
         <v>341</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DG2" t="s">
         <v>342</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DH2" t="s">
         <v>343</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DI2" t="s">
         <v>344</v>
-      </c>
-      <c r="DF2" t="s">
-        <v>345</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>346</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>347</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -6663,350 +6664,350 @@
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" t="s">
+        <v>345</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="O3" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="J3" t="s">
-        <v>349</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="M3" s="4" t="s">
+      <c r="P3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>348</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI3" t="s">
         <v>118</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>352</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>122</v>
       </c>
       <c r="AJ3" t="s">
         <v>3</v>
       </c>
       <c r="AK3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AL3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AM3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AN3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AO3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="AP3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
       <c r="AR3" s="13" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="AS3" s="13" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="AT3" t="s">
+        <v>351</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>352</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>351</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>353</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>354</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BV3" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="BW3" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="BX3" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="BY3" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="AU3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX3" t="s">
+      <c r="BZ3" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="CA3" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CC3" t="s">
         <v>356</v>
       </c>
-      <c r="AY3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>355</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BQ3" t="s">
+      <c r="CD3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CG3" t="s">
         <v>357</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="CH3" t="s">
         <v>358</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BV3" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW3" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="BX3" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="BY3" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="BZ3" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="CA3" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>360</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>361</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>362</v>
       </c>
       <c r="CI3" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="CK3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="CL3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="CM3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="CN3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="CO3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CP3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CQ3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CR3" t="s">
+        <v>356</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>119</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>112</v>
+      </c>
+      <c r="CU3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CV3" t="s">
         <v>360</v>
       </c>
-      <c r="CS3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>116</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>125</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>364</v>
-      </c>
       <c r="CW3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="CX3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="CY3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="CZ3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="DA3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="DB3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="DC3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="DD3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DE3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DF3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DG3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DH3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DI3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:113" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AC5">
         <v>2</v>
       </c>
       <c r="AO5" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AT5" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AX5" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="AZ5">
         <v>1</v>
@@ -7015,42 +7016,42 @@
         <v>1</v>
       </c>
       <c r="CB5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="CG5" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="CY5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C6" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AC6">
         <v>1</v>
       </c>
       <c r="AG6" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BD6">
         <v>1</v>
       </c>
       <c r="BO6" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="BS6">
         <v>0.1</v>
       </c>
       <c r="CN6" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="CO6" s="12" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="CR6">
         <v>0.2</v>
@@ -7058,31 +7059,31 @@
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C7" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AC7">
         <v>2</v>
       </c>
       <c r="AO7" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AT7" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="BD7">
         <v>99</v>
       </c>
       <c r="BO7" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="BS7">
         <v>0.1</v>
       </c>
       <c r="CN7" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="CR7">
         <v>0.2</v>
@@ -7090,25 +7091,25 @@
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C8" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="Q8" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="AC8">
         <v>2</v>
       </c>
       <c r="AO8" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AV8">
         <v>99</v>
       </c>
       <c r="AX8" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AZ8">
         <v>0.4</v>
@@ -7120,7 +7121,7 @@
         <v>1</v>
       </c>
       <c r="CL8" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9" spans="1:113" x14ac:dyDescent="0.25">
@@ -7128,40 +7129,40 @@
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D10" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E10" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="F10" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="J10" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AC10">
         <v>1</v>
       </c>
       <c r="AG10" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BD10">
         <v>1</v>
       </c>
       <c r="BO10" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BT10">
         <v>30</v>
@@ -7176,14 +7177,14 @@
         <v>1</v>
       </c>
       <c r="BY10" s="5" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="CB10" s="6"/>
       <c r="CG10" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="CN10" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="CO10">
         <v>0.7</v>
@@ -7197,23 +7198,23 @@
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C11" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AC11">
         <v>1</v>
       </c>
       <c r="AG11" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BD11">
         <v>1</v>
       </c>
       <c r="CB11" s="6"/>
       <c r="CN11" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="CO11">
         <v>1</v>
@@ -7224,25 +7225,25 @@
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="AC12">
         <v>2</v>
       </c>
       <c r="AO12" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AT12" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AX12" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="AZ12">
         <v>1</v>
@@ -7251,35 +7252,35 @@
         <v>1</v>
       </c>
       <c r="CB12" s="6" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="CG12" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="CY12" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C13" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I13">
         <v>1</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="M13"/>
       <c r="N13"/>
       <c r="O13" s="4" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
@@ -7296,10 +7297,10 @@
         <v>1</v>
       </c>
       <c r="CL13" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="CY13" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="DD13">
         <v>1</v>
@@ -7310,46 +7311,46 @@
     </row>
     <row r="15" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C15" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D15" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="E15" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F15" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="G15">
         <v>3</v>
       </c>
       <c r="J15" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AC15">
         <v>1</v>
       </c>
       <c r="AG15" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="AT15" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BD15">
         <v>1</v>
       </c>
       <c r="BO15" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BP15" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="BT15">
         <v>20</v>
@@ -7364,16 +7365,16 @@
         <v>1</v>
       </c>
       <c r="BY15" s="5" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="CB15" s="6" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="CG15" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="CN15" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="CO15">
         <v>1.6</v>
@@ -7388,33 +7389,33 @@
         <v>20</v>
       </c>
       <c r="CW15" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C16" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="AC16">
         <v>2</v>
       </c>
       <c r="AO16" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AP16" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="AT16" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="AX16" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AZ16">
         <v>1</v>
@@ -7423,30 +7424,30 @@
         <v>99</v>
       </c>
       <c r="CU16" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C17" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="AC17">
         <v>2</v>
       </c>
       <c r="AO17" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AT17" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AX17" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AZ17">
         <v>1</v>
@@ -7455,54 +7456,54 @@
         <v>1</v>
       </c>
       <c r="CB17" s="6" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="CG17" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="CY17" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C19" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D19" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="E19" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="F19" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="G19">
         <v>3</v>
       </c>
       <c r="J19" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AC19">
         <v>1</v>
       </c>
       <c r="AG19" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BD19">
         <v>1</v>
       </c>
       <c r="BO19" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="BP19" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="BT19">
         <v>45</v>
@@ -7517,14 +7518,14 @@
         <v>1</v>
       </c>
       <c r="BY19" s="5" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="CB19" s="6"/>
       <c r="CG19" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="CN19" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="CO19">
         <v>1.1000000000000001</v>
@@ -7541,28 +7542,28 @@
     </row>
     <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C20" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="AC20">
         <v>2</v>
       </c>
       <c r="AO20" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AX20" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="AZ20">
         <v>0</v>
@@ -7574,36 +7575,36 @@
         <v>1</v>
       </c>
       <c r="CL20" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="CU20" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="CY20" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="21" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C21" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="AC21">
         <v>2</v>
       </c>
       <c r="AO21" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AT21" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AX21" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="AZ21">
         <v>1</v>
@@ -7612,27 +7613,27 @@
         <v>1</v>
       </c>
       <c r="CB21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="CG21" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="CY21" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C22" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I22">
         <v>1</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="M22"/>
       <c r="N22"/>
@@ -7641,7 +7642,7 @@
         <v>1</v>
       </c>
       <c r="AG22" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BD22">
         <v>1</v>
@@ -7650,10 +7651,10 @@
         <v>1.6</v>
       </c>
       <c r="CB22" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="CG22" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="DD22">
         <v>1</v>
@@ -7667,19 +7668,19 @@
     </row>
     <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C23" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I23">
         <v>1</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="M23"/>
       <c r="N23"/>
@@ -7688,7 +7689,7 @@
         <v>1</v>
       </c>
       <c r="AG23" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BD23">
         <v>1</v>
@@ -7697,10 +7698,10 @@
         <v>0.16669999999999999</v>
       </c>
       <c r="CB23" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="CG23" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="DD23">
         <v>1</v>
@@ -8841,37 +8842,37 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>430</v>
+      </c>
+      <c r="F1" t="s">
+        <v>431</v>
+      </c>
+      <c r="G1" t="s">
+        <v>432</v>
+      </c>
+      <c r="H1" t="s">
+        <v>433</v>
+      </c>
+      <c r="I1" t="s">
         <v>434</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>435</v>
       </c>
-      <c r="G1" t="s">
+      <c r="L1" t="s">
         <v>436</v>
       </c>
-      <c r="H1" t="s">
+      <c r="M1" t="s">
         <v>437</v>
       </c>
-      <c r="I1" t="s">
+      <c r="N1" t="s">
         <v>438</v>
       </c>
-      <c r="J1" t="s">
+      <c r="O1" t="s">
         <v>439</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>440</v>
-      </c>
-      <c r="M1" t="s">
-        <v>441</v>
-      </c>
-      <c r="N1" t="s">
-        <v>442</v>
-      </c>
-      <c r="O1" t="s">
-        <v>443</v>
-      </c>
-      <c r="P1" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -8879,49 +8880,49 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
+        <v>441</v>
+      </c>
+      <c r="F2" t="s">
+        <v>442</v>
+      </c>
+      <c r="G2" t="s">
+        <v>443</v>
+      </c>
+      <c r="H2" t="s">
+        <v>444</v>
+      </c>
+      <c r="I2" t="s">
         <v>445</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>446</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K2" t="s">
         <v>447</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2" t="s">
         <v>448</v>
       </c>
-      <c r="I2" t="s">
+      <c r="N2" t="s">
         <v>449</v>
       </c>
-      <c r="J2" t="s">
+      <c r="O2" t="s">
         <v>450</v>
       </c>
-      <c r="K2" t="s">
+      <c r="P2" t="s">
         <v>451</v>
       </c>
-      <c r="L2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M2" t="s">
-        <v>452</v>
-      </c>
-      <c r="N2" t="s">
-        <v>453</v>
-      </c>
-      <c r="O2" t="s">
-        <v>454</v>
-      </c>
-      <c r="P2" t="s">
-        <v>455</v>
-      </c>
       <c r="Q2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -8935,65 +8936,65 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="K3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="N3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="O3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="P3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="Q3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C4" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="Q4" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C5" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -9001,27 +9002,27 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C7" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="Q7" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C9" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="278" spans="16:16" x14ac:dyDescent="0.25">
@@ -9056,7 +9057,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -9064,13 +9065,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="D2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -9081,10 +9082,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -9107,7 +9108,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -9115,31 +9116,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
       <c r="D2" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="G2" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="H2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="I2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="J2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -9156,22 +9157,22 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="J3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -9198,34 +9199,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D1" t="s">
+        <v>466</v>
+      </c>
+      <c r="E1" t="s">
+        <v>467</v>
+      </c>
+      <c r="F1" t="s">
         <v>468</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>469</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
         <v>470</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
         <v>471</v>
       </c>
-      <c r="F1" t="s">
+      <c r="K1" t="s">
         <v>472</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>473</v>
-      </c>
-      <c r="I1" t="s">
-        <v>474</v>
-      </c>
-      <c r="J1" t="s">
-        <v>475</v>
-      </c>
-      <c r="K1" t="s">
-        <v>476</v>
-      </c>
-      <c r="L1" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -9233,37 +9234,37 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E2" t="s">
+        <v>477</v>
+      </c>
+      <c r="F2" t="s">
         <v>478</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>479</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>480</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
         <v>481</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>482</v>
       </c>
-      <c r="G2" t="s">
-        <v>483</v>
-      </c>
-      <c r="H2" t="s">
-        <v>484</v>
-      </c>
-      <c r="I2" t="s">
-        <v>485</v>
-      </c>
-      <c r="J2" t="s">
-        <v>486</v>
-      </c>
       <c r="K2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -9274,34 +9275,34 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -9331,31 +9332,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E2" t="s">
+        <v>485</v>
+      </c>
+      <c r="F2" t="s">
         <v>77</v>
       </c>
-      <c r="D2" t="s">
-        <v>488</v>
-      </c>
-      <c r="E2" t="s">
-        <v>489</v>
-      </c>
-      <c r="F2" t="s">
-        <v>79</v>
-      </c>
       <c r="G2" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="H2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="I2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="J2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -9372,22 +9373,22 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -9416,28 +9417,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>496</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -9445,28 +9446,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -9474,10 +9475,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
@@ -9500,33 +9501,33 @@
     </row>
     <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>511</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -9535,13 +9536,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/一方通行/余.xlsx
+++ b/Excel/一方通行/余.xlsx
@@ -23,7 +23,7 @@
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="529">
   <si>
     <t>Id</t>
   </si>
@@ -313,6 +313,9 @@
     <t>UnitData[]</t>
   </si>
   <si>
+    <t>余</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
@@ -370,6 +373,9 @@
     <t>部署策略</t>
   </si>
   <si>
+    <t>可部署上限</t>
+  </si>
+  <si>
     <t>仇恨等级</t>
   </si>
   <si>
@@ -526,6 +532,9 @@
     <t>RedeployPolicy</t>
   </si>
   <si>
+    <t>BuildCountLimit</t>
+  </si>
+  <si>
     <t>Hatred</t>
   </si>
   <si>
@@ -676,9 +685,6 @@
     <t>System.Collections.Generic.Dictionary&lt;string,object&gt;</t>
   </si>
   <si>
-    <t>余</t>
-  </si>
-  <si>
     <t>干员</t>
   </si>
   <si>
@@ -1798,6 +1804,9 @@
     <t>MapHp</t>
   </si>
   <si>
+    <t>UnitTypeEnum[]</t>
+  </si>
+  <si>
     <t>仅单面</t>
   </si>
   <si>
@@ -1877,20 +1886,14 @@
   </si>
   <si>
     <t>/Spine/本能的召唤/front/token_10054_phatm2_encdool.skel.bytes</t>
-  </si>
-  <si>
-    <t>UnitTypeEnum[]</t>
-  </si>
-  <si>
-    <t>余</t>
-    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1902,27 +1905,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1952,19 +1934,19 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2269,765 +2251,862 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1"/>
+    <col min="1" max="2" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B4" t="s">
-        <v>125</v>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BS4"/>
+  <dimension ref="A1:BT4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1"/>
-    <col min="2" max="3" width="9" customWidth="1"/>
-    <col min="4" max="5" width="8.58203125" customWidth="1"/>
-    <col min="6" max="6" width="19.58203125" customWidth="1"/>
-    <col min="7" max="7" width="8.25" customWidth="1"/>
-    <col min="8" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="5.5" customWidth="1"/>
-    <col min="13" max="13" width="5.58203125" customWidth="1"/>
-    <col min="14" max="14" width="4" customWidth="1"/>
-    <col min="15" max="15" width="7.75" customWidth="1"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1"/>
-    <col min="17" max="18" width="3.83203125" customWidth="1"/>
-    <col min="19" max="20" width="3.58203125" customWidth="1"/>
-    <col min="21" max="21" width="10.25" customWidth="1"/>
-    <col min="22" max="22" width="9.58203125" customWidth="1"/>
-    <col min="23" max="23" width="10.75" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1"/>
-    <col min="25" max="25" width="13.08203125" customWidth="1"/>
-    <col min="26" max="26" width="10.75" customWidth="1"/>
-    <col min="27" max="28" width="9" customWidth="1"/>
-    <col min="29" max="29" width="8" customWidth="1"/>
-    <col min="30" max="30" width="17.08203125" customWidth="1"/>
-    <col min="31" max="31" width="9" customWidth="1"/>
-    <col min="32" max="32" width="9.75" customWidth="1"/>
-    <col min="33" max="33" width="7.83203125" customWidth="1"/>
-    <col min="34" max="34" width="15.83203125" customWidth="1"/>
-    <col min="35" max="35" width="13.83203125" customWidth="1"/>
-    <col min="36" max="36" width="34.5" customWidth="1"/>
-    <col min="37" max="38" width="9.83203125" customWidth="1"/>
-    <col min="39" max="42" width="9" customWidth="1"/>
-    <col min="43" max="43" width="12.5" customWidth="1"/>
-    <col min="44" max="49" width="9" customWidth="1"/>
-    <col min="50" max="50" width="24.33203125" customWidth="1"/>
-    <col min="51" max="51" width="9" customWidth="1"/>
-    <col min="52" max="52" width="17.75" customWidth="1"/>
-    <col min="53" max="53" width="7.83203125" customWidth="1"/>
-    <col min="54" max="55" width="9" customWidth="1"/>
-    <col min="56" max="56" width="24.25" customWidth="1"/>
-    <col min="57" max="57" width="13.25" customWidth="1"/>
-    <col min="58" max="58" width="16.08203125" customWidth="1"/>
-    <col min="59" max="59" width="8" customWidth="1"/>
-    <col min="60" max="63" width="9" customWidth="1"/>
-    <col min="64" max="64" width="39.58203125" customWidth="1"/>
-    <col min="65" max="65" width="14" customWidth="1"/>
-    <col min="66" max="66" width="14.83203125" customWidth="1"/>
-    <col min="67" max="70" width="14" customWidth="1"/>
-    <col min="71" max="71" width="19.1640625" customWidth="1"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="9" customWidth="1" style="2"/>
+    <col min="3" max="3" width="9" customWidth="1" style="2"/>
+    <col min="4" max="4" width="8.58203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="8.58203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1" style="2"/>
+    <col min="7" max="7" width="8.25" customWidth="1" style="2"/>
+    <col min="8" max="8" width="9" customWidth="1" style="2"/>
+    <col min="9" max="9" width="9" customWidth="1" style="2"/>
+    <col min="10" max="10" width="9" customWidth="1" style="2"/>
+    <col min="11" max="11" width="6" customWidth="1" style="2"/>
+    <col min="12" max="12" width="5.5" customWidth="1" style="2"/>
+    <col min="13" max="13" width="5.58203125" customWidth="1" style="2"/>
+    <col min="14" max="14" width="4" customWidth="1" style="2"/>
+    <col min="15" max="15" width="7.75" customWidth="1" style="2"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1" style="2"/>
+    <col min="17" max="17" width="3.83203125" customWidth="1" style="2"/>
+    <col min="18" max="18" width="3.83203125" customWidth="1" style="2"/>
+    <col min="19" max="19" width="3.58203125" customWidth="1" style="2"/>
+    <col min="20" max="20" width="3.58203125" customWidth="1" style="2"/>
+    <col min="21" max="21" width="10.25" customWidth="1" style="2"/>
+    <col min="22" max="22" width="9.58203125" customWidth="1" style="2"/>
+    <col min="23" max="23" width="10.75" customWidth="1" style="2"/>
+    <col min="24" max="24" width="12.83203125" customWidth="1" style="2"/>
+    <col min="25" max="25" width="13.08203125" customWidth="1" style="2"/>
+    <col min="26" max="26" width="10.75" customWidth="1" style="2"/>
+    <col min="27" max="27" width="9" customWidth="1" style="2"/>
+    <col min="28" max="28" width="9" customWidth="1" style="2"/>
+    <col min="29" max="29" width="8" customWidth="1" style="2"/>
+    <col min="30" max="30" width="17.08203125" customWidth="1" style="2"/>
+    <col min="31" max="31" width="9" customWidth="1" style="2"/>
+    <col min="32" max="32" width="9" customWidth="1" style="2"/>
+    <col min="33" max="33" width="9.75" customWidth="1" style="2"/>
+    <col min="34" max="34" width="7.83203125" customWidth="1" style="2"/>
+    <col min="35" max="35" width="15.83203125" customWidth="1" style="2"/>
+    <col min="36" max="36" width="13.83203125" customWidth="1" style="2"/>
+    <col min="37" max="37" width="34.5" customWidth="1" style="2"/>
+    <col min="38" max="38" width="9.83203125" customWidth="1" style="2"/>
+    <col min="39" max="39" width="9.83203125" customWidth="1" style="2"/>
+    <col min="40" max="40" width="9" customWidth="1" style="2"/>
+    <col min="41" max="41" width="9" customWidth="1" style="2"/>
+    <col min="42" max="42" width="9" customWidth="1" style="2"/>
+    <col min="43" max="43" width="9" customWidth="1" style="2"/>
+    <col min="44" max="44" width="12.5" customWidth="1" style="2"/>
+    <col min="45" max="45" width="9" customWidth="1" style="2"/>
+    <col min="46" max="46" width="9" customWidth="1" style="2"/>
+    <col min="47" max="47" width="9" customWidth="1" style="2"/>
+    <col min="48" max="48" width="9" customWidth="1" style="2"/>
+    <col min="49" max="49" width="9" customWidth="1" style="2"/>
+    <col min="50" max="50" width="9" customWidth="1" style="2"/>
+    <col min="51" max="51" width="24.33203125" customWidth="1" style="2"/>
+    <col min="52" max="52" width="9" customWidth="1" style="2"/>
+    <col min="53" max="53" width="17.75" customWidth="1" style="2"/>
+    <col min="54" max="54" width="7.83203125" customWidth="1" style="2"/>
+    <col min="55" max="55" width="9" customWidth="1" style="2"/>
+    <col min="56" max="56" width="9" customWidth="1" style="2"/>
+    <col min="57" max="57" width="24.25" customWidth="1" style="2"/>
+    <col min="58" max="58" width="13.25" customWidth="1" style="2"/>
+    <col min="59" max="59" width="16.08203125" customWidth="1" style="2"/>
+    <col min="60" max="60" width="8" customWidth="1" style="2"/>
+    <col min="61" max="61" width="9" customWidth="1" style="2"/>
+    <col min="62" max="62" width="9" customWidth="1" style="2"/>
+    <col min="63" max="63" width="9" customWidth="1" style="2"/>
+    <col min="64" max="64" width="9" customWidth="1" style="2"/>
+    <col min="65" max="65" width="39.58203125" customWidth="1" style="2"/>
+    <col min="66" max="66" width="14" customWidth="1" style="2"/>
+    <col min="67" max="67" width="14.83203125" customWidth="1" style="2"/>
+    <col min="68" max="68" width="14" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="71" max="71" width="14" customWidth="1" style="2"/>
+    <col min="72" max="72" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="D1" t="s">
+    <row r="1">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AO1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AP1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AS1" s="2"/>
+      <c r="AT1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AU1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AW1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AX1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AY1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AZ1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="BA1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="BB1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="BC1" s="2"/>
+      <c r="BD1" s="2"/>
+      <c r="BE1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="BF1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="BG1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="BH1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="BI1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="BJ1" s="2"/>
+      <c r="BK1" s="2"/>
+      <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
+      <c r="BN1" s="2"/>
+      <c r="BO1" s="2"/>
+      <c r="BP1" s="2"/>
+      <c r="BQ1" s="2"/>
+      <c r="BR1" s="2"/>
+      <c r="BS1" s="2"/>
+      <c r="BT1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AT2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AU2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AX2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AY2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="BA2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BB2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="BC2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="BD2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BE2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BF2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BG2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BH2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BI2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BJ2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BK2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BL2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BM2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BN2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BO2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BP2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BQ2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="BR2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BS2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BT2" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AS3" s="2"/>
+      <c r="AT3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B4" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2">
+        <v>2</v>
+      </c>
+      <c r="J4" s="2">
+        <v>90</v>
+      </c>
+      <c r="K4" s="2">
+        <v>3903</v>
+      </c>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2">
+        <v>715</v>
+      </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2">
+        <v>607</v>
+      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2">
+        <v>10</v>
+      </c>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2">
+        <v>24</v>
+      </c>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="V4" s="2">
+        <v>70</v>
+      </c>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="AJ4" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AK4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AL4" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AM4" s="2"/>
+      <c r="AN4" s="2"/>
+      <c r="AO4" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AP4" s="2">
+        <v>3</v>
+      </c>
+      <c r="AQ4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AR4" s="2"/>
+      <c r="AS4" s="2"/>
+      <c r="AT4" s="2"/>
+      <c r="AU4" s="2"/>
+      <c r="AV4" s="2"/>
+      <c r="AW4" s="2"/>
+      <c r="AX4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="AY4" s="2"/>
+      <c r="AZ4" s="2"/>
+      <c r="BA4" s="2"/>
+      <c r="BB4" s="2"/>
+      <c r="BC4" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BD4" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BE4" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="BF4" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="BG4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BH4" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="BI4" s="2">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>11</v>
-      </c>
-      <c r="S1" t="s">
-        <v>12</v>
-      </c>
-      <c r="U1" t="s">
-        <v>13</v>
-      </c>
-      <c r="V1" t="s">
-        <v>14</v>
-      </c>
-      <c r="X1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>40</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>41</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>42</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>43</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>44</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>45</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K2" t="s">
-        <v>54</v>
-      </c>
-      <c r="L2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M2" t="s">
-        <v>56</v>
-      </c>
-      <c r="N2" t="s">
-        <v>57</v>
-      </c>
-      <c r="O2" t="s">
-        <v>58</v>
-      </c>
-      <c r="P2" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>60</v>
-      </c>
-      <c r="R2" t="s">
-        <v>61</v>
-      </c>
-      <c r="S2" t="s">
-        <v>62</v>
-      </c>
-      <c r="T2" t="s">
-        <v>63</v>
-      </c>
-      <c r="U2" t="s">
-        <v>64</v>
-      </c>
-      <c r="V2" t="s">
-        <v>65</v>
-      </c>
-      <c r="W2" t="s">
-        <v>66</v>
-      </c>
-      <c r="X2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>95</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>96</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>97</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>98</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>99</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>100</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>102</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>103</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>104</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>106</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>107</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>109</v>
-      </c>
-      <c r="BO2" t="s">
-        <v>110</v>
-      </c>
-      <c r="BP2" t="s">
-        <v>111</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J3" t="s">
-        <v>117</v>
-      </c>
-      <c r="K3" t="s">
-        <v>117</v>
-      </c>
-      <c r="L3" t="s">
-        <v>117</v>
-      </c>
-      <c r="M3" t="s">
-        <v>117</v>
-      </c>
-      <c r="N3" t="s">
-        <v>117</v>
-      </c>
-      <c r="O3" t="s">
-        <v>117</v>
-      </c>
-      <c r="P3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>117</v>
-      </c>
-      <c r="R3" t="s">
-        <v>117</v>
-      </c>
-      <c r="S3" t="s">
-        <v>117</v>
-      </c>
-      <c r="T3" t="s">
-        <v>117</v>
-      </c>
-      <c r="U3" t="s">
-        <v>116</v>
-      </c>
-      <c r="V3" t="s">
-        <v>117</v>
-      </c>
-      <c r="W3" t="s">
-        <v>117</v>
-      </c>
-      <c r="X3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>120</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>122</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>123</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="B4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>90</v>
-      </c>
-      <c r="K4">
-        <v>3903</v>
-      </c>
-      <c r="M4">
-        <v>715</v>
-      </c>
-      <c r="O4">
-        <v>607</v>
-      </c>
-      <c r="Q4">
-        <v>10</v>
-      </c>
-      <c r="S4">
-        <v>24</v>
-      </c>
-      <c r="U4">
-        <v>0.5</v>
-      </c>
-      <c r="V4">
-        <v>70</v>
-      </c>
-      <c r="Y4">
-        <v>0.05</v>
-      </c>
-      <c r="Z4">
-        <v>1.6</v>
-      </c>
-      <c r="AC4">
-        <v>1</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>129</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>130</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>132</v>
-      </c>
-      <c r="AO4">
-        <v>3</v>
-      </c>
-      <c r="AP4">
-        <v>0.5</v>
-      </c>
-      <c r="AW4">
-        <v>0.25</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>133</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>134</v>
-      </c>
-      <c r="BD4" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE4" t="s">
-        <v>136</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>127</v>
-      </c>
-      <c r="BG4" t="s">
-        <v>137</v>
-      </c>
-      <c r="BH4">
-        <v>6</v>
-      </c>
-      <c r="BI4" t="s">
-        <v>138</v>
-      </c>
-      <c r="BJ4" t="s">
-        <v>139</v>
-      </c>
-      <c r="BK4" t="s">
+      <c r="BJ4" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BK4" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BL4" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="BP4" t="s">
+      <c r="BM4" s="2"/>
+      <c r="BN4" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="BQ4" t="s">
-        <v>143</v>
-      </c>
-      <c r="BS4">
+      <c r="BO4" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="BP4" s="2"/>
+      <c r="BQ4" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BR4" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BS4" s="2"/>
+      <c r="BT4" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3035,6 +3114,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3044,1862 +3124,1862 @@
   <dimension ref="A1:DI519"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1"/>
-    <col min="3" max="3" width="7.75" customWidth="1"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1"/>
-    <col min="9" max="9" width="7.33203125" customWidth="1"/>
-    <col min="10" max="10" width="15.75" customWidth="1"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1"/>
-    <col min="14" max="14" width="11.75" customWidth="1"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1"/>
-    <col min="17" max="17" width="21.5" customWidth="1"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1"/>
-    <col min="22" max="22" width="17.75" customWidth="1"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1"/>
-    <col min="24" max="24" width="18.5" customWidth="1"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1"/>
-    <col min="32" max="32" width="13.75" customWidth="1"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1"/>
-    <col min="36" max="36" width="12.5" customWidth="1"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1"/>
-    <col min="40" max="40" width="15" customWidth="1"/>
-    <col min="41" max="41" width="13.25" customWidth="1"/>
-    <col min="42" max="45" width="11.83203125" customWidth="1"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1"/>
-    <col min="47" max="47" width="12.25" customWidth="1"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1"/>
-    <col min="51" max="51" width="9" customWidth="1"/>
-    <col min="52" max="52" width="7" customWidth="1"/>
-    <col min="53" max="53" width="11.75" customWidth="1"/>
-    <col min="54" max="54" width="19.75" customWidth="1"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1"/>
-    <col min="56" max="56" width="8.5" customWidth="1"/>
-    <col min="57" max="57" width="13.5" customWidth="1"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1"/>
-    <col min="60" max="60" width="8.25" customWidth="1"/>
-    <col min="61" max="67" width="8.33203125" customWidth="1"/>
-    <col min="68" max="70" width="11.25" customWidth="1"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1"/>
-    <col min="72" max="73" width="8" customWidth="1"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1"/>
-    <col min="75" max="76" width="8.5" customWidth="1"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1"/>
-    <col min="80" max="80" width="13.5" customWidth="1"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1"/>
-    <col min="82" max="82" width="15.75" customWidth="1"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1"/>
-    <col min="86" max="86" width="9" customWidth="1"/>
-    <col min="87" max="87" width="16" customWidth="1"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1"/>
-    <col min="92" max="92" width="17.08203125" customWidth="1"/>
-    <col min="93" max="93" width="9.5" customWidth="1"/>
-    <col min="94" max="98" width="9" customWidth="1"/>
-    <col min="99" max="99" width="14" customWidth="1"/>
-    <col min="100" max="100" width="8" customWidth="1"/>
-    <col min="101" max="101" width="9" customWidth="1"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1"/>
-    <col min="103" max="103" width="13.75" customWidth="1"/>
-    <col min="104" max="104" width="9.5" customWidth="1"/>
-    <col min="105" max="106" width="9" customWidth="1"/>
-    <col min="107" max="108" width="9.5" customWidth="1"/>
-    <col min="109" max="109" width="9" customWidth="1"/>
-    <col min="110" max="110" width="15.5" customWidth="1"/>
-    <col min="111" max="111" width="9" customWidth="1"/>
-    <col min="112" max="113" width="9.5" customWidth="1"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1" style="2"/>
+    <col min="3" max="3" width="7.75" customWidth="1" style="2"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1" style="2"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1" style="2"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1" style="2"/>
+    <col min="9" max="9" width="7.33203125" customWidth="1" style="2"/>
+    <col min="10" max="10" width="15.75" customWidth="1" style="2"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1" style="2"/>
+    <col min="14" max="14" width="11.75" customWidth="1" style="2"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1" style="2"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1" style="2"/>
+    <col min="17" max="17" width="21.5" customWidth="1" style="2"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1" style="2"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1" style="2"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1" style="2"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1" style="2"/>
+    <col min="22" max="22" width="17.75" customWidth="1" style="2"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1" style="2"/>
+    <col min="24" max="24" width="18.5" customWidth="1" style="2"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1" style="2"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1" style="2"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1" style="2"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1" style="2"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1" style="2"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1" style="2"/>
+    <col min="32" max="32" width="13.75" customWidth="1" style="2"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1" style="2"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1" style="2"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1" style="2"/>
+    <col min="36" max="36" width="12.5" customWidth="1" style="2"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1" style="2"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1" style="2"/>
+    <col min="40" max="40" width="15" customWidth="1" style="2"/>
+    <col min="41" max="41" width="13.25" customWidth="1" style="2"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1" style="2"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1" style="2"/>
+    <col min="47" max="47" width="12.25" customWidth="1" style="2"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1" style="2"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1" style="2"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1" style="2"/>
+    <col min="51" max="51" width="9" customWidth="1" style="2"/>
+    <col min="52" max="52" width="7" customWidth="1" style="2"/>
+    <col min="53" max="53" width="11.75" customWidth="1" style="2"/>
+    <col min="54" max="54" width="19.75" customWidth="1" style="2"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1" style="2"/>
+    <col min="56" max="56" width="8.5" customWidth="1" style="2"/>
+    <col min="57" max="57" width="13.5" customWidth="1" style="2"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1" style="2"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1" style="2"/>
+    <col min="60" max="60" width="8.25" customWidth="1" style="2"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1" style="2"/>
+    <col min="68" max="70" width="11.25" customWidth="1" style="2"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1" style="2"/>
+    <col min="72" max="73" width="8" customWidth="1" style="2"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1" style="2"/>
+    <col min="75" max="76" width="8.5" customWidth="1" style="2"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1" style="2"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1" style="2"/>
+    <col min="80" max="80" width="13.5" customWidth="1" style="2"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1" style="2"/>
+    <col min="82" max="82" width="15.75" customWidth="1" style="2"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1" style="2"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1" style="2"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1" style="2"/>
+    <col min="86" max="86" width="9" customWidth="1" style="2"/>
+    <col min="87" max="87" width="16" customWidth="1" style="2"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1" style="2"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1" style="2"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1" style="2"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1" style="2"/>
+    <col min="93" max="93" width="9.5" customWidth="1" style="2"/>
+    <col min="94" max="98" width="9" customWidth="1" style="2"/>
+    <col min="99" max="99" width="14" customWidth="1" style="2"/>
+    <col min="100" max="100" width="8" customWidth="1" style="2"/>
+    <col min="101" max="101" width="9" customWidth="1" style="2"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1" style="2"/>
+    <col min="103" max="103" width="13.75" customWidth="1" style="2"/>
+    <col min="104" max="104" width="9.5" customWidth="1" style="2"/>
+    <col min="105" max="106" width="9" customWidth="1" style="2"/>
+    <col min="107" max="108" width="9.5" customWidth="1" style="2"/>
+    <col min="109" max="109" width="9" customWidth="1" style="2"/>
+    <col min="110" max="110" width="15.5" customWidth="1" style="2"/>
+    <col min="111" max="111" width="9" customWidth="1" style="2"/>
+    <col min="112" max="113" width="9.5" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E1" t="s">
+    <row r="1">
+      <c r="B1" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D1" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="G1" t="s">
+      <c r="E1" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="H1" t="s">
+      <c r="F1" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="I1" t="s">
+      <c r="G1" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="J1" t="s">
+      <c r="H1" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K1" t="s">
+      <c r="I1" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L1" t="s">
+      <c r="J1" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="M1" t="s">
+      <c r="K1" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="N1" t="s">
+      <c r="L1" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="O1" t="s">
+      <c r="M1" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="P1" t="s">
+      <c r="N1" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="O1" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="R1" t="s">
+      <c r="P1" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="S1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="T1" t="s">
+      <c r="R1" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="U1" t="s">
-        <v>161</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="S1" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="W1" t="s">
+      <c r="T1" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="X1" t="s">
+      <c r="U1" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="V1" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="W1" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="X1" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AN1" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AU1" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AV1" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="AX1" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BA1" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BD1" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BE1" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BF1" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>200</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="BG1" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BH1" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BJ1" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="BK1" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BL1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BM1" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BN1" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BO1" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BP1" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BQ1" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BR1" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BS1" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BT1" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BU1" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BV1" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BW1" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="BX1" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="BY1" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="BZ1" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CA1" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CB1" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CC1" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CD1" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CE1" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CF1" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CG1" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CH1" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CI1" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CJ1" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CK1" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CL1" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CM1" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CN1" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CO1" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="CR1" t="s">
-        <v>210</v>
-      </c>
-      <c r="CS1" t="s">
+      <c r="CP1" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CQ1" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CR1" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="CS1" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CT1" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CU1" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CV1" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="CW1" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>239</v>
-      </c>
-      <c r="DA1" t="s">
+      <c r="CX1" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="CY1" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="CZ1" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="DA1" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DB1" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DC1" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DD1" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DE1" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="DF1" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="DI1" t="s">
+      <c r="DG1" s="2" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="DH1" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="DI1" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F2" t="s">
-        <v>251</v>
-      </c>
-      <c r="G2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="I2" t="s">
+      <c r="F2" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="J2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="K2" t="s">
+      <c r="I2" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="L2" t="s">
+      <c r="J2" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="M2" t="s">
+      <c r="K2" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="N2" t="s">
+      <c r="L2" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="O2" t="s">
+      <c r="M2" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="P2" t="s">
+      <c r="N2" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="O2" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="R2" t="s">
+      <c r="P2" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="S2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="T2" t="s">
+      <c r="R2" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="U2" t="s">
+      <c r="S2" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="V2" t="s">
+      <c r="T2" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="W2" t="s">
+      <c r="U2" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="X2" t="s">
+      <c r="V2" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="W2" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="X2" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AK2" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AL2" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AM2" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AN2" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AO2" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AP2" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AR2" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AS2" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AT2" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AU2" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AV2" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AW2" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="AX2" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="AY2" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="AZ2" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BA2" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BB2" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BC2" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BD2" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BE2" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BF2" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BG2" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BH2" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BI2" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BJ2" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BK2" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BL2" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="BO2" t="s">
-        <v>79</v>
-      </c>
-      <c r="BP2" t="s">
+      <c r="BM2" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BN2" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BO2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="BP2" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BQ2" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BR2" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="BU2" t="s">
-        <v>94</v>
-      </c>
-      <c r="BV2" t="s">
+      <c r="BS2" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="BW2" t="s">
+      <c r="BT2" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="BX2" t="s">
+      <c r="BU2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="BV2" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="BY2" t="s">
+      <c r="BW2" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="BX2" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="BY2" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="BZ2" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CA2" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CB2" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CC2" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CD2" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CE2" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CF2" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CG2" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CH2" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CI2" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CJ2" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CK2" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CL2" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CM2" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CN2" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CO2" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CP2" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CQ2" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CR2" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CS2" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CT2" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CU2" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CV2" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="CW2" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="CX2" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="CY2" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="CZ2" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DA2" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DB2" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DC2" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DD2" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="DE2" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="DH2" t="s">
+      <c r="DF2" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="DI2" t="s">
+      <c r="DG2" s="2" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="DH2" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="K3" t="s">
+      <c r="DI2" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="L3" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="M3" t="s">
-        <v>117</v>
-      </c>
-      <c r="N3" t="s">
-        <v>117</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="K3" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="P3" t="s">
+      <c r="N3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="O3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="R3" t="s">
+      <c r="AD3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="S3" t="s">
-        <v>115</v>
-      </c>
-      <c r="T3" t="s">
-        <v>116</v>
-      </c>
-      <c r="U3" t="s">
-        <v>116</v>
-      </c>
-      <c r="V3" t="s">
-        <v>116</v>
-      </c>
-      <c r="W3" t="s">
-        <v>115</v>
-      </c>
-      <c r="X3" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>359</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AI3" t="s">
+      <c r="AL3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BX3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BY3" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="BZ3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="CA3" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="CB3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="CC3" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="CD3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="CE3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="CF3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="CG3" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="CH3" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="CI3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="CK3" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="CL3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="CN3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="CO3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CP3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CQ3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CR3" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="CS3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="CT3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="CU3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="CV3" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="CW3" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="CX3" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="CY3" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="CZ3" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="DA3" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="DB3" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="DC3" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="DD3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="DE3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="DF3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="DG3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="DH3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="DI3" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO5" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="AT5" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="AX5" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="AZ5" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD5" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="CG5" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="CY5" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="BD6" s="2">
+        <v>1</v>
+      </c>
+      <c r="BO6" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="BS6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="CN6" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="CO6" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="CR6" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO7" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="AT7" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="BD7" s="2">
+        <v>99</v>
+      </c>
+      <c r="BO7" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="BS7" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="CN7" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="CR7" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO8" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="AV8" s="2">
+        <v>99</v>
+      </c>
+      <c r="AX8" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="AZ8" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="BD8" s="2">
+        <v>99</v>
+      </c>
+      <c r="BS8" s="2">
+        <v>1</v>
+      </c>
+      <c r="CL8" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="G10" s="2">
         <v>3</v>
       </c>
-      <c r="AK3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>360</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>361</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>362</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>363</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>362</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>364</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>365</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BW3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BY3" t="s">
-        <v>366</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>115</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>366</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>119</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>367</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>119</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>119</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>119</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>368</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>369</v>
-      </c>
-      <c r="CI3" t="s">
-        <v>2</v>
-      </c>
-      <c r="CJ3" t="s">
-        <v>370</v>
-      </c>
-      <c r="CK3" t="s">
-        <v>370</v>
-      </c>
-      <c r="CL3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>120</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>120</v>
-      </c>
-      <c r="CO3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CP3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CQ3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CR3" t="s">
-        <v>367</v>
-      </c>
-      <c r="CS3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>115</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>371</v>
-      </c>
-      <c r="CW3" t="s">
-        <v>372</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>372</v>
-      </c>
-      <c r="CY3" t="s">
-        <v>371</v>
-      </c>
-      <c r="CZ3" t="s">
-        <v>371</v>
-      </c>
-      <c r="DA3" t="s">
-        <v>371</v>
-      </c>
-      <c r="DB3" t="s">
-        <v>371</v>
-      </c>
-      <c r="DC3" t="s">
-        <v>371</v>
-      </c>
-      <c r="DD3" t="s">
-        <v>115</v>
-      </c>
-      <c r="DE3" t="s">
-        <v>115</v>
-      </c>
-      <c r="DF3" t="s">
-        <v>115</v>
-      </c>
-      <c r="DG3" t="s">
-        <v>115</v>
-      </c>
-      <c r="DH3" t="s">
-        <v>115</v>
-      </c>
-      <c r="DI3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="5" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>374</v>
-      </c>
-      <c r="C5" t="s">
-        <v>139</v>
-      </c>
-      <c r="AC5">
-        <v>2</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>375</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>376</v>
-      </c>
-      <c r="AX5" t="s">
+      <c r="J10" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="BD10" s="2">
+        <v>1</v>
+      </c>
+      <c r="BO10" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="BT10" s="2">
+        <v>30</v>
+      </c>
+      <c r="BV10" s="2">
+        <v>0</v>
+      </c>
+      <c r="BW10" s="2">
+        <v>16</v>
+      </c>
+      <c r="BX10" s="2">
+        <v>1</v>
+      </c>
+      <c r="BY10" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="CG10" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="CN10" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="CO10" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="CP10" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="CR10" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="BD11" s="2">
+        <v>1</v>
+      </c>
+      <c r="CN11" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="CO11" s="2">
+        <v>1</v>
+      </c>
+      <c r="CR11" s="2">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="AC12" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO12" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="AZ5">
+      <c r="AT12" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="AX12" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="AZ12" s="2">
         <v>1</v>
       </c>
-      <c r="BD5">
+      <c r="BD12" s="2">
         <v>1</v>
       </c>
-      <c r="CB5" t="s">
-        <v>56</v>
-      </c>
-      <c r="CG5" t="s">
+      <c r="CB12" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="CG12" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="CY12" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="AC13" s="2">
+        <v>2</v>
+      </c>
+      <c r="AD13" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD13" s="2">
+        <v>1</v>
+      </c>
+      <c r="CL13" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="CY13" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="DD13" s="2">
+        <v>1</v>
+      </c>
+      <c r="DH13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="G15" s="2">
+        <v>3</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="AT15" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="BD15" s="2">
+        <v>1</v>
+      </c>
+      <c r="BO15" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="BP15" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="BT15" s="2">
+        <v>20</v>
+      </c>
+      <c r="BV15" s="2">
+        <v>20</v>
+      </c>
+      <c r="BW15" s="2">
+        <v>26</v>
+      </c>
+      <c r="BX15" s="2">
+        <v>1</v>
+      </c>
+      <c r="BY15" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="CB15" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="CG15" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="CN15" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="CO15" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="CP15" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="CQ15" s="2">
+        <v>2</v>
+      </c>
+      <c r="CR15" s="2">
+        <v>20</v>
+      </c>
+      <c r="CW15" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO16" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="AP16" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="AT16" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="AX16" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="AZ16" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD16" s="2">
+        <v>99</v>
+      </c>
+      <c r="CU16" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO17" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="AT17" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="CY5" t="s">
+      <c r="AX17" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="AZ17" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD17" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB17" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="CG17" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="CY17" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="G19" s="2">
+        <v>3</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="AC19" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="BD19" s="2">
+        <v>1</v>
+      </c>
+      <c r="BO19" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="BP19" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="BT19" s="2">
+        <v>45</v>
+      </c>
+      <c r="BV19" s="2">
+        <v>42</v>
+      </c>
+      <c r="BW19" s="2">
+        <v>55</v>
+      </c>
+      <c r="BX19" s="2">
+        <v>1</v>
+      </c>
+      <c r="BY19" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="CG19" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="CN19" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="CO19" s="2">
+        <v>1.1</v>
+      </c>
+      <c r="CP19" s="2">
+        <v>1.1</v>
+      </c>
+      <c r="CQ19" s="2">
+        <v>1.1</v>
+      </c>
+      <c r="CR19" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="AC20" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO20" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="AX20" s="2" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="AZ20" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB20" s="2">
+        <v>2</v>
+      </c>
+      <c r="BD20" s="2">
+        <v>1</v>
+      </c>
+      <c r="CL20" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="CU20" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="CY20" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="AC21" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO21" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="AT21" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="AX21" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="AZ21" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD21" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB21" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="CG21" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C6" t="s">
+      <c r="CY21" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="AC6">
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I22" s="2">
         <v>1</v>
       </c>
-      <c r="AG6" t="s">
-        <v>382</v>
-      </c>
-      <c r="BD6">
+      <c r="K22" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="AC22" s="2">
         <v>1</v>
       </c>
-      <c r="BO6" t="s">
+      <c r="AG22" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="BD22" s="2">
+        <v>1</v>
+      </c>
+      <c r="BS22" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="CB22" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="CG22" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="DD22" s="2">
+        <v>1</v>
+      </c>
+      <c r="DG22" s="2">
+        <v>1</v>
+      </c>
+      <c r="DH22" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="BS6">
+      <c r="I23" s="2">
+        <v>1</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC23" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG23" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="BD23" s="2">
+        <v>1</v>
+      </c>
+      <c r="BS23" s="2">
+        <v>0.1667</v>
+      </c>
+      <c r="CB23" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="CG23" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="DD23" s="2">
+        <v>1</v>
+      </c>
+      <c r="DG23" s="2">
+        <v>1</v>
+      </c>
+      <c r="DH23" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="CL499" s="2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="CL501" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="CL502" s="2">
         <v>0.1</v>
       </c>
-      <c r="CN6" t="s">
-        <v>384</v>
-      </c>
-      <c r="CO6" t="s">
-        <v>385</v>
-      </c>
-      <c r="CR6">
+    </row>
+    <row r="504">
+      <c r="CL504" s="2">
         <v>0.2</v>
       </c>
     </row>
-    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>383</v>
-      </c>
-      <c r="C7" t="s">
-        <v>381</v>
-      </c>
-      <c r="AC7">
-        <v>2</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>375</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>376</v>
-      </c>
-      <c r="BD7">
-        <v>99</v>
-      </c>
-      <c r="BO7" t="s">
-        <v>386</v>
-      </c>
-      <c r="BS7">
-        <v>0.1</v>
-      </c>
-      <c r="CN7" t="s">
-        <v>383</v>
-      </c>
-      <c r="CR7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>386</v>
-      </c>
-      <c r="C8" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>383</v>
-      </c>
-      <c r="AC8">
-        <v>2</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>375</v>
-      </c>
-      <c r="AV8">
-        <v>99</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>387</v>
-      </c>
-      <c r="AZ8">
+    <row r="511">
+      <c r="CL511" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="CL513" s="2">
         <v>0.4</v>
       </c>
-      <c r="BD8">
-        <v>99</v>
-      </c>
-      <c r="BS8">
-        <v>1</v>
-      </c>
-      <c r="CL8" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>389</v>
-      </c>
-      <c r="C10" t="s">
-        <v>381</v>
-      </c>
-      <c r="D10" t="s">
-        <v>390</v>
-      </c>
-      <c r="E10" t="s">
-        <v>391</v>
-      </c>
-      <c r="F10" t="s">
-        <v>392</v>
-      </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
-      <c r="J10" t="s">
-        <v>393</v>
-      </c>
-      <c r="K10" t="s">
-        <v>394</v>
-      </c>
-      <c r="AC10">
-        <v>1</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>382</v>
-      </c>
-      <c r="BD10">
-        <v>1</v>
-      </c>
-      <c r="BO10" t="s">
-        <v>395</v>
-      </c>
-      <c r="BT10">
-        <v>30</v>
-      </c>
-      <c r="BV10">
-        <v>0</v>
-      </c>
-      <c r="BW10">
-        <v>16</v>
-      </c>
-      <c r="BX10">
-        <v>1</v>
-      </c>
-      <c r="BY10" t="s">
-        <v>396</v>
-      </c>
-      <c r="CG10" t="s">
-        <v>378</v>
-      </c>
-      <c r="CN10" t="s">
-        <v>397</v>
-      </c>
-      <c r="CO10">
-        <v>0.7</v>
-      </c>
-      <c r="CP10">
-        <v>0.7</v>
-      </c>
-      <c r="CR10">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>398</v>
-      </c>
-      <c r="C11" t="s">
-        <v>381</v>
-      </c>
-      <c r="AC11">
-        <v>1</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>382</v>
-      </c>
-      <c r="BD11">
-        <v>1</v>
-      </c>
-      <c r="CN11" t="s">
-        <v>399</v>
-      </c>
-      <c r="CO11">
-        <v>1</v>
-      </c>
-      <c r="CR11">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>400</v>
-      </c>
-      <c r="C12" t="s">
-        <v>139</v>
-      </c>
-      <c r="O12" t="s">
-        <v>401</v>
-      </c>
-      <c r="AC12">
-        <v>2</v>
-      </c>
-      <c r="AO12" t="s">
-        <v>375</v>
-      </c>
-      <c r="AT12" t="s">
-        <v>376</v>
-      </c>
-      <c r="AX12" t="s">
-        <v>377</v>
-      </c>
-      <c r="AZ12">
-        <v>1</v>
-      </c>
-      <c r="BD12">
-        <v>1</v>
-      </c>
-      <c r="CB12" t="s">
-        <v>402</v>
-      </c>
-      <c r="CG12" t="s">
-        <v>378</v>
-      </c>
-      <c r="CY12" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>403</v>
-      </c>
-      <c r="C13" t="s">
-        <v>381</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="K13" t="s">
-        <v>404</v>
-      </c>
-      <c r="L13" t="s">
-        <v>405</v>
-      </c>
-      <c r="O13" t="s">
-        <v>401</v>
-      </c>
-      <c r="AC13">
-        <v>2</v>
-      </c>
-      <c r="AD13">
-        <v>1</v>
-      </c>
-      <c r="AE13">
-        <v>1</v>
-      </c>
-      <c r="BD13">
-        <v>1</v>
-      </c>
-      <c r="CL13" t="s">
-        <v>406</v>
-      </c>
-      <c r="CY13" t="s">
-        <v>407</v>
-      </c>
-      <c r="DD13">
-        <v>1</v>
-      </c>
-      <c r="DH13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>408</v>
-      </c>
-      <c r="C15" t="s">
-        <v>381</v>
-      </c>
-      <c r="D15" t="s">
-        <v>409</v>
-      </c>
-      <c r="E15" t="s">
-        <v>410</v>
-      </c>
-      <c r="F15" t="s">
-        <v>411</v>
-      </c>
-      <c r="G15">
-        <v>3</v>
-      </c>
-      <c r="J15" t="s">
-        <v>393</v>
-      </c>
-      <c r="K15" t="s">
-        <v>394</v>
-      </c>
-      <c r="AC15">
-        <v>1</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>382</v>
-      </c>
-      <c r="AT15" t="s">
-        <v>412</v>
-      </c>
-      <c r="BD15">
-        <v>1</v>
-      </c>
-      <c r="BO15" t="s">
-        <v>413</v>
-      </c>
-      <c r="BP15" t="s">
-        <v>414</v>
-      </c>
-      <c r="BT15">
-        <v>20</v>
-      </c>
-      <c r="BV15">
-        <v>20</v>
-      </c>
-      <c r="BW15">
-        <v>26</v>
-      </c>
-      <c r="BX15">
-        <v>1</v>
-      </c>
-      <c r="BY15" t="s">
-        <v>415</v>
-      </c>
-      <c r="CB15" t="s">
-        <v>416</v>
-      </c>
-      <c r="CG15" t="s">
-        <v>378</v>
-      </c>
-      <c r="CN15" t="s">
-        <v>417</v>
-      </c>
-      <c r="CO15">
-        <v>1.6</v>
-      </c>
-      <c r="CP15">
-        <v>2.9</v>
-      </c>
-      <c r="CQ15">
-        <v>2</v>
-      </c>
-      <c r="CR15">
-        <v>20</v>
-      </c>
-      <c r="CW15" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>414</v>
-      </c>
-      <c r="C16" t="s">
-        <v>419</v>
-      </c>
-      <c r="K16" t="s">
-        <v>404</v>
-      </c>
-      <c r="AC16">
-        <v>2</v>
-      </c>
-      <c r="AO16" t="s">
-        <v>375</v>
-      </c>
-      <c r="AP16" t="s">
-        <v>420</v>
-      </c>
-      <c r="AT16" t="s">
-        <v>412</v>
-      </c>
-      <c r="AX16" t="s">
-        <v>387</v>
-      </c>
-      <c r="AZ16">
-        <v>1</v>
-      </c>
-      <c r="BD16">
-        <v>99</v>
-      </c>
-      <c r="CU16" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="17" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>413</v>
-      </c>
-      <c r="C17" t="s">
-        <v>139</v>
-      </c>
-      <c r="O17" t="s">
-        <v>422</v>
-      </c>
-      <c r="AC17">
-        <v>2</v>
-      </c>
-      <c r="AO17" t="s">
-        <v>375</v>
-      </c>
-      <c r="AT17" t="s">
-        <v>376</v>
-      </c>
-      <c r="AX17" t="s">
-        <v>387</v>
-      </c>
-      <c r="AZ17">
-        <v>1</v>
-      </c>
-      <c r="BD17">
-        <v>1</v>
-      </c>
-      <c r="CB17" t="s">
-        <v>416</v>
-      </c>
-      <c r="CG17" t="s">
-        <v>378</v>
-      </c>
-      <c r="CY17" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="19" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>423</v>
-      </c>
-      <c r="C19" t="s">
-        <v>381</v>
-      </c>
-      <c r="D19" t="s">
-        <v>424</v>
-      </c>
-      <c r="E19" t="s">
-        <v>425</v>
-      </c>
-      <c r="F19" t="s">
-        <v>426</v>
-      </c>
-      <c r="G19">
-        <v>3</v>
-      </c>
-      <c r="J19" t="s">
-        <v>393</v>
-      </c>
-      <c r="K19" t="s">
-        <v>394</v>
-      </c>
-      <c r="AC19">
-        <v>1</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>382</v>
-      </c>
-      <c r="BD19">
-        <v>1</v>
-      </c>
-      <c r="BO19" t="s">
-        <v>427</v>
-      </c>
-      <c r="BP19" t="s">
-        <v>428</v>
-      </c>
-      <c r="BT19">
-        <v>45</v>
-      </c>
-      <c r="BV19">
-        <v>42</v>
-      </c>
-      <c r="BW19">
-        <v>55</v>
-      </c>
-      <c r="BX19">
-        <v>1</v>
-      </c>
-      <c r="BY19" t="s">
-        <v>415</v>
-      </c>
-      <c r="CG19" t="s">
-        <v>378</v>
-      </c>
-      <c r="CN19" t="s">
-        <v>429</v>
-      </c>
-      <c r="CO19">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="CP19">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="CQ19">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="CR19">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>430</v>
-      </c>
-      <c r="C20" t="s">
-        <v>431</v>
-      </c>
-      <c r="K20" t="s">
-        <v>404</v>
-      </c>
-      <c r="L20" t="s">
-        <v>432</v>
-      </c>
-      <c r="O20" t="s">
-        <v>422</v>
-      </c>
-      <c r="AC20">
-        <v>2</v>
-      </c>
-      <c r="AO20" t="s">
-        <v>375</v>
-      </c>
-      <c r="AX20" t="s">
-        <v>377</v>
-      </c>
-      <c r="AZ20">
-        <v>0</v>
-      </c>
-      <c r="BB20">
-        <v>2</v>
-      </c>
-      <c r="BD20">
-        <v>1</v>
-      </c>
-      <c r="CL20" t="s">
-        <v>433</v>
-      </c>
-      <c r="CU20" t="s">
-        <v>434</v>
-      </c>
-      <c r="CY20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="21" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>435</v>
-      </c>
-      <c r="C21" t="s">
-        <v>139</v>
-      </c>
-      <c r="O21" t="s">
-        <v>422</v>
-      </c>
-      <c r="AC21">
-        <v>2</v>
-      </c>
-      <c r="AO21" t="s">
-        <v>375</v>
-      </c>
-      <c r="AT21" t="s">
-        <v>376</v>
-      </c>
-      <c r="AX21" t="s">
-        <v>377</v>
-      </c>
-      <c r="AZ21">
-        <v>1</v>
-      </c>
-      <c r="BD21">
-        <v>1</v>
-      </c>
-      <c r="CB21" t="s">
-        <v>436</v>
-      </c>
-      <c r="CG21" t="s">
-        <v>378</v>
-      </c>
-      <c r="CY21" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="22" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>428</v>
-      </c>
-      <c r="C22" t="s">
-        <v>381</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="K22" t="s">
-        <v>404</v>
-      </c>
-      <c r="AC22">
-        <v>1</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>382</v>
-      </c>
-      <c r="BD22">
-        <v>1</v>
-      </c>
-      <c r="BS22">
-        <v>1.6</v>
-      </c>
-      <c r="CB22" t="s">
-        <v>437</v>
-      </c>
-      <c r="CG22" t="s">
-        <v>378</v>
-      </c>
-      <c r="DD22">
-        <v>1</v>
-      </c>
-      <c r="DG22">
-        <v>1</v>
-      </c>
-      <c r="DH22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>438</v>
-      </c>
-      <c r="C23" t="s">
-        <v>381</v>
-      </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="K23" t="s">
-        <v>404</v>
-      </c>
-      <c r="L23" t="s">
-        <v>439</v>
-      </c>
-      <c r="AC23">
-        <v>1</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>382</v>
-      </c>
-      <c r="BD23">
-        <v>1</v>
-      </c>
-      <c r="BS23">
-        <v>0.16669999999999999</v>
-      </c>
-      <c r="CB23" t="s">
-        <v>440</v>
-      </c>
-      <c r="CG23" t="s">
-        <v>378</v>
-      </c>
-      <c r="DD23">
-        <v>1</v>
-      </c>
-      <c r="DG23">
-        <v>1</v>
-      </c>
-      <c r="DH23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="499" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL499">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="501" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL501">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="502" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL502">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="504" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL504">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="511" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL511">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="513" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL513">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="514" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL514">
+    </row>
+    <row r="514">
+      <c r="CL514" s="2">
         <v>0.6</v>
       </c>
     </row>
-    <row r="517" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL517">
+    <row r="517">
+      <c r="CL517" s="2">
         <v>0.5</v>
       </c>
     </row>
-    <row r="518" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL518">
-        <v>0.66700000000000004</v>
-      </c>
-    </row>
-    <row r="519" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL519">
+    <row r="518">
+      <c r="CL518" s="2">
+        <v>0.667</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="CL519" s="2">
         <v>0.2</v>
       </c>
     </row>
@@ -4907,6 +4987,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -4916,216 +4997,216 @@
   <dimension ref="A1:Q279"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="31.25" customWidth="1"/>
-    <col min="3" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="18.75" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="13" width="9" customWidth="1"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1"/>
-    <col min="15" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="22.1640625" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1" style="2"/>
+    <col min="2" max="2" width="31.25" customWidth="1" style="2"/>
+    <col min="3" max="6" width="9" customWidth="1" style="2"/>
+    <col min="7" max="7" width="18.75" customWidth="1" style="2"/>
+    <col min="8" max="8" width="15" customWidth="1" style="2"/>
+    <col min="9" max="13" width="9" customWidth="1" style="2"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1" style="2"/>
+    <col min="15" max="15" width="9.5" customWidth="1" style="2"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1" style="2"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>441</v>
-      </c>
-      <c r="F1" t="s">
-        <v>442</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="H1" t="s">
+      <c r="F1" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="I1" t="s">
+      <c r="G1" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J1" t="s">
+      <c r="H1" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="L1" t="s">
+      <c r="I1" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="M1" t="s">
+      <c r="J1" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="N1" t="s">
+      <c r="L1" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="O1" t="s">
+      <c r="M1" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="P1" t="s">
+      <c r="N1" s="2" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="O1" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" t="s">
-        <v>452</v>
-      </c>
-      <c r="F2" t="s">
-        <v>453</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="H2" t="s">
+      <c r="F2" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="I2" t="s">
+      <c r="G2" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="J2" t="s">
+      <c r="H2" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="K2" t="s">
+      <c r="I2" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L2" t="s">
-        <v>52</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="J2" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="N2" t="s">
+      <c r="K2" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="O2" t="s">
+      <c r="L2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="P2" t="s">
+      <c r="N2" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="Q2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H3" t="s">
-        <v>115</v>
-      </c>
-      <c r="I3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J3" t="s">
-        <v>371</v>
-      </c>
-      <c r="K3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L3" t="s">
-        <v>335</v>
-      </c>
-      <c r="M3" t="s">
-        <v>115</v>
-      </c>
-      <c r="N3" t="s">
-        <v>115</v>
-      </c>
-      <c r="O3" t="s">
-        <v>335</v>
-      </c>
-      <c r="P3" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>384</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="O2" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="F4">
+      <c r="P2" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="F4" s="2">
         <v>1</v>
       </c>
-      <c r="Q4" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>383</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="Q4" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="F5">
+      <c r="Q7" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H9" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>399</v>
-      </c>
-      <c r="C7" t="s">
-        <v>463</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>467</v>
-      </c>
-      <c r="C9" t="s">
-        <v>221</v>
-      </c>
-      <c r="H9">
+      <c r="Q9" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="P278" s="2">
         <v>1</v>
       </c>
-      <c r="Q9" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="278" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P278">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="279" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P279">
+    </row>
+    <row r="279">
+      <c r="P279" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5133,6 +5214,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5141,52 +5223,53 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.25" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="27.5" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="11.25" customWidth="1" style="2"/>
+    <col min="3" max="3" width="9" customWidth="1" style="2"/>
+    <col min="4" max="4" width="27.5" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C1" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" t="s">
-        <v>470</v>
-      </c>
-      <c r="D2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>335</v>
-      </c>
-      <c r="D3" t="s">
-        <v>124</v>
+      <c r="B2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5195,86 +5278,87 @@
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="27.25" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="10" width="9" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
+    <col min="2" max="2" width="9" customWidth="1" style="2"/>
+    <col min="3" max="3" width="27.25" customWidth="1" style="2"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1" style="2"/>
+    <col min="5" max="10" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="I1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="1">
+      <c r="I1" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D2" t="s">
-        <v>471</v>
-      </c>
-      <c r="E2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" t="s">
-        <v>472</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="H2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="I2" t="s">
-        <v>330</v>
-      </c>
-      <c r="J2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I3" t="s">
-        <v>370</v>
-      </c>
-      <c r="J3" t="s">
-        <v>124</v>
+      <c r="G2" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5283,129 +5367,130 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1"/>
-    <col min="5" max="10" width="11.25" customWidth="1"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
+    <col min="2" max="2" width="28" customWidth="1" style="2"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1" style="2"/>
+    <col min="5" max="10" width="11.25" customWidth="1" style="2"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1" style="2"/>
+    <col min="12" max="12" width="9" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C1" t="s">
-        <v>476</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="B1" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C1" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D1" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="H1" t="s">
+      <c r="E1" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="I1" t="s">
+      <c r="F1" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="J1" t="s">
+      <c r="H1" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="K1" t="s">
+      <c r="I1" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="L1" t="s">
+      <c r="J1" s="2" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="K1" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C2" t="s">
-        <v>486</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B2" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C2" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D2" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="G2" t="s">
+      <c r="E2" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="H2" t="s">
+      <c r="F2" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="I2" t="s">
+      <c r="G2" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="J2" t="s">
+      <c r="H2" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="K2" t="s">
-        <v>472</v>
-      </c>
-      <c r="L2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="I2" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="E3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J3" t="s">
-        <v>117</v>
-      </c>
-      <c r="K3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L3" t="s">
-        <v>116</v>
+      <c r="J2" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -5415,49 +5500,49 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1"/>
-    <col min="2" max="2" width="16.25" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.25" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="9" width="9" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="16.25" customWidth="1" style="2"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1" style="2"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="10.25" customWidth="1" style="2"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1" style="2"/>
+    <col min="7" max="9" width="9" customWidth="1" style="2"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" t="s">
-        <v>495</v>
-      </c>
-      <c r="E2" t="s">
-        <v>496</v>
-      </c>
-      <c r="F2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="H2" t="s">
-        <v>279</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="E2" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="J2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -5471,27 +5556,28 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>526</v>
+        <v>501</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5500,152 +5586,153 @@
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1"/>
-    <col min="3" max="3" width="21.9140625" customWidth="1"/>
-    <col min="4" max="4" width="16.25" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="7" width="15.1640625" customWidth="1"/>
-    <col min="8" max="8" width="12.9140625" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="1" max="1" width="7.5" customWidth="1" style="2"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1" style="2"/>
+    <col min="3" max="3" width="21.9140625" customWidth="1" style="2"/>
+    <col min="4" max="4" width="16.25" customWidth="1" style="2"/>
+    <col min="5" max="5" width="14" customWidth="1" style="2"/>
+    <col min="6" max="7" width="15.1640625" customWidth="1" style="2"/>
+    <col min="8" max="8" width="12.9140625" customWidth="1" style="2"/>
+    <col min="9" max="9" width="14" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>499</v>
-      </c>
-      <c r="C1" t="s">
-        <v>500</v>
-      </c>
-      <c r="D1" t="s">
-        <v>501</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="B1" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="F1" t="s">
+      <c r="C1" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="G1" t="s">
+      <c r="D1" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="H1" t="s">
+      <c r="E1" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="I1" t="s">
+      <c r="F1" s="2" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="G1" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>507</v>
-      </c>
-      <c r="C2" t="s">
-        <v>508</v>
-      </c>
-      <c r="D2" t="s">
-        <v>509</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="B2" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C2" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="G2" t="s">
+      <c r="D2" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="H2" t="s">
+      <c r="E2" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="I2" t="s">
+      <c r="F2" s="2" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="G2" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="C4">
+      <c r="H2" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
-        <v>516</v>
-      </c>
-      <c r="E4" t="s">
-        <v>517</v>
-      </c>
-      <c r="F4" t="s">
-        <v>518</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="D4" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="H4" t="s">
+      <c r="E4" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="I4" t="s">
+      <c r="F4" s="2" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="G4" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="B5">
+      <c r="H4" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
-        <v>523</v>
-      </c>
-      <c r="E5" t="s">
-        <v>524</v>
-      </c>
-      <c r="F5" t="s">
-        <v>525</v>
+      <c r="D5" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>528</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 

--- a/Excel/一方通行/余.xlsx
+++ b/Excel/一方通行/余.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C5EBEC-B63D-42F8-A783-C25FBE1D399B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0129357D-5F82-470F-A755-D7CFEAA6D6DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -47,6 +47,30 @@
   </authors>
   <commentList>
     <comment ref="AK1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>PC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0:干员 1:敌人 2:仅技能条 3:技能+血条</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AM1" authorId="0" shapeId="0" xr:uid="{8AD71D45-D2B4-4E68-8D71-0C91852B8E98}">
       <text>
         <r>
           <rPr>
@@ -299,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="534">
   <si>
     <t>Id</t>
   </si>
@@ -388,9 +412,6 @@
     <t>可选技能</t>
   </si>
   <si>
-    <t>血条类型</t>
-  </si>
-  <si>
     <t>高度</t>
   </si>
   <si>
@@ -1886,14 +1907,37 @@
   </si>
   <si>
     <t>/Spine/本能的召唤/front/token_10054_phatm2_encdool.skel.bytes</t>
+  </si>
+  <si>
+    <t>血条</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技力条</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpBarType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型:蓝</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型:绿</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1905,6 +1949,34 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1934,19 +2006,19 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2251,862 +2323,789 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1" style="2"/>
+    <col min="1" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BT4"/>
+  <dimension ref="A1:BU4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="8.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="8.58203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="19.58203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="8.25" customWidth="1" style="2"/>
-    <col min="8" max="8" width="9" customWidth="1" style="2"/>
-    <col min="9" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="9" customWidth="1" style="2"/>
-    <col min="11" max="11" width="6" customWidth="1" style="2"/>
-    <col min="12" max="12" width="5.5" customWidth="1" style="2"/>
-    <col min="13" max="13" width="5.58203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="4" customWidth="1" style="2"/>
-    <col min="15" max="15" width="7.75" customWidth="1" style="2"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1" style="2"/>
-    <col min="17" max="17" width="3.83203125" customWidth="1" style="2"/>
-    <col min="18" max="18" width="3.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="3.58203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="3.58203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="10.25" customWidth="1" style="2"/>
-    <col min="22" max="22" width="9.58203125" customWidth="1" style="2"/>
-    <col min="23" max="23" width="10.75" customWidth="1" style="2"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1" style="2"/>
-    <col min="25" max="25" width="13.08203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="10.75" customWidth="1" style="2"/>
-    <col min="27" max="27" width="9" customWidth="1" style="2"/>
-    <col min="28" max="28" width="9" customWidth="1" style="2"/>
-    <col min="29" max="29" width="8" customWidth="1" style="2"/>
-    <col min="30" max="30" width="17.08203125" customWidth="1" style="2"/>
-    <col min="31" max="31" width="9" customWidth="1" style="2"/>
-    <col min="32" max="32" width="9" customWidth="1" style="2"/>
-    <col min="33" max="33" width="9.75" customWidth="1" style="2"/>
-    <col min="34" max="34" width="7.83203125" customWidth="1" style="2"/>
-    <col min="35" max="35" width="15.83203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="13.83203125" customWidth="1" style="2"/>
-    <col min="37" max="37" width="34.5" customWidth="1" style="2"/>
-    <col min="38" max="38" width="9.83203125" customWidth="1" style="2"/>
-    <col min="39" max="39" width="9.83203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="9" customWidth="1" style="2"/>
-    <col min="41" max="41" width="9" customWidth="1" style="2"/>
-    <col min="42" max="42" width="9" customWidth="1" style="2"/>
-    <col min="43" max="43" width="9" customWidth="1" style="2"/>
-    <col min="44" max="44" width="12.5" customWidth="1" style="2"/>
-    <col min="45" max="45" width="9" customWidth="1" style="2"/>
-    <col min="46" max="46" width="9" customWidth="1" style="2"/>
-    <col min="47" max="47" width="9" customWidth="1" style="2"/>
-    <col min="48" max="48" width="9" customWidth="1" style="2"/>
-    <col min="49" max="49" width="9" customWidth="1" style="2"/>
-    <col min="50" max="50" width="9" customWidth="1" style="2"/>
-    <col min="51" max="51" width="24.33203125" customWidth="1" style="2"/>
-    <col min="52" max="52" width="9" customWidth="1" style="2"/>
-    <col min="53" max="53" width="17.75" customWidth="1" style="2"/>
-    <col min="54" max="54" width="7.83203125" customWidth="1" style="2"/>
-    <col min="55" max="55" width="9" customWidth="1" style="2"/>
-    <col min="56" max="56" width="9" customWidth="1" style="2"/>
-    <col min="57" max="57" width="24.25" customWidth="1" style="2"/>
-    <col min="58" max="58" width="13.25" customWidth="1" style="2"/>
-    <col min="59" max="59" width="16.08203125" customWidth="1" style="2"/>
-    <col min="60" max="60" width="8" customWidth="1" style="2"/>
-    <col min="61" max="61" width="9" customWidth="1" style="2"/>
-    <col min="62" max="62" width="9" customWidth="1" style="2"/>
-    <col min="63" max="63" width="9" customWidth="1" style="2"/>
-    <col min="64" max="64" width="9" customWidth="1" style="2"/>
-    <col min="65" max="65" width="39.58203125" customWidth="1" style="2"/>
-    <col min="66" max="66" width="14" customWidth="1" style="2"/>
-    <col min="67" max="67" width="14.83203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="14" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14" customWidth="1" style="2"/>
-    <col min="71" max="71" width="14" customWidth="1" style="2"/>
-    <col min="72" max="72" width="19.1640625" customWidth="1" style="2"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1"/>
+    <col min="2" max="3" width="9" customWidth="1"/>
+    <col min="4" max="5" width="8.58203125" customWidth="1"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1"/>
+    <col min="7" max="7" width="8.25" customWidth="1"/>
+    <col min="8" max="10" width="9" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="5.5" customWidth="1"/>
+    <col min="13" max="13" width="5.58203125" customWidth="1"/>
+    <col min="14" max="14" width="4" customWidth="1"/>
+    <col min="15" max="15" width="7.75" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1"/>
+    <col min="17" max="18" width="3.83203125" customWidth="1"/>
+    <col min="19" max="20" width="3.58203125" customWidth="1"/>
+    <col min="21" max="21" width="10.25" customWidth="1"/>
+    <col min="22" max="22" width="9.58203125" customWidth="1"/>
+    <col min="23" max="23" width="10.75" customWidth="1"/>
+    <col min="24" max="24" width="12.83203125" customWidth="1"/>
+    <col min="25" max="25" width="13.08203125" customWidth="1"/>
+    <col min="26" max="26" width="10.75" customWidth="1"/>
+    <col min="27" max="28" width="9" customWidth="1"/>
+    <col min="29" max="29" width="8" customWidth="1"/>
+    <col min="30" max="30" width="17.08203125" customWidth="1"/>
+    <col min="31" max="32" width="9" customWidth="1"/>
+    <col min="33" max="33" width="9.75" customWidth="1"/>
+    <col min="34" max="34" width="7.83203125" customWidth="1"/>
+    <col min="35" max="35" width="15.83203125" customWidth="1"/>
+    <col min="36" max="36" width="13.83203125" customWidth="1"/>
+    <col min="37" max="37" width="34.5" customWidth="1"/>
+    <col min="38" max="40" width="9.83203125" customWidth="1"/>
+    <col min="41" max="44" width="9" customWidth="1"/>
+    <col min="45" max="45" width="12.5" customWidth="1"/>
+    <col min="46" max="51" width="9" customWidth="1"/>
+    <col min="52" max="52" width="24.33203125" customWidth="1"/>
+    <col min="53" max="53" width="9" customWidth="1"/>
+    <col min="54" max="54" width="17.75" customWidth="1"/>
+    <col min="55" max="55" width="7.83203125" customWidth="1"/>
+    <col min="56" max="57" width="9" customWidth="1"/>
+    <col min="58" max="58" width="24.25" customWidth="1"/>
+    <col min="59" max="59" width="13.25" customWidth="1"/>
+    <col min="60" max="60" width="16.08203125" customWidth="1"/>
+    <col min="61" max="61" width="8" customWidth="1"/>
+    <col min="62" max="65" width="9" customWidth="1"/>
+    <col min="66" max="66" width="39.58203125" customWidth="1"/>
+    <col min="67" max="67" width="14" customWidth="1"/>
+    <col min="68" max="68" width="14.83203125" customWidth="1"/>
+    <col min="69" max="72" width="14" customWidth="1"/>
+    <col min="73" max="73" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2" t="s">
+      <c r="S1" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2" t="s">
+      <c r="U1" t="s">
         <v>14</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2" t="s">
+      <c r="X1" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" t="s">
         <v>19</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" t="s">
         <v>20</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" t="s">
         <v>22</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" t="s">
         <v>23</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" t="s">
         <v>24</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" t="s">
         <v>25</v>
       </c>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" t="s">
         <v>28</v>
       </c>
       <c r="AM1" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="AO1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AP1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AQ1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AR1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AS1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AU1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="2"/>
-      <c r="AT1" s="2" t="s">
+      <c r="AV1" t="s">
         <v>35</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AW1" t="s">
         <v>36</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AX1" t="s">
         <v>37</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AY1" t="s">
         <v>38</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AZ1" t="s">
         <v>39</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="BA1" t="s">
         <v>40</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="BB1" t="s">
         <v>41</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BC1" t="s">
         <v>42</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BF1" t="s">
         <v>43</v>
       </c>
-      <c r="BC1" s="2"/>
-      <c r="BD1" s="2"/>
-      <c r="BE1" s="2" t="s">
+      <c r="BG1" t="s">
         <v>44</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BH1" t="s">
         <v>45</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BI1" t="s">
         <v>46</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BJ1" t="s">
         <v>47</v>
       </c>
-      <c r="BI1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>48</v>
       </c>
-      <c r="BJ1" s="2"/>
-      <c r="BK1" s="2"/>
-      <c r="BL1" s="2"/>
-      <c r="BM1" s="2"/>
-      <c r="BN1" s="2"/>
-      <c r="BO1" s="2"/>
-      <c r="BP1" s="2"/>
-      <c r="BQ1" s="2"/>
-      <c r="BR1" s="2"/>
-      <c r="BS1" s="2"/>
-      <c r="BT1" s="2"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="F2" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="G2" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" t="s">
         <v>52</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" t="s">
         <v>53</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" t="s">
         <v>55</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" t="s">
         <v>56</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" t="s">
         <v>57</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" t="s">
         <v>58</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" t="s">
         <v>59</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" t="s">
         <v>60</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" t="s">
         <v>61</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" t="s">
         <v>62</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" t="s">
         <v>63</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" t="s">
         <v>64</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" t="s">
         <v>65</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="V2" t="s">
         <v>66</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W2" t="s">
         <v>67</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="X2" t="s">
         <v>68</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" t="s">
         <v>69</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" t="s">
         <v>70</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" t="s">
         <v>71</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AB2" t="s">
         <v>72</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" t="s">
         <v>73</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" t="s">
         <v>74</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" t="s">
         <v>75</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" t="s">
         <v>76</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AG2" t="s">
         <v>77</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AH2" t="s">
         <v>78</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AI2" t="s">
         <v>79</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AJ2" t="s">
         <v>80</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AK2" t="s">
         <v>81</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AL2" t="s">
         <v>82</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AM2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AN2" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="AO2" t="s">
         <v>84</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AP2" t="s">
         <v>85</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AQ2" t="s">
         <v>86</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AR2" t="s">
         <v>87</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AS2" t="s">
         <v>88</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AT2" t="s">
         <v>89</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AU2" t="s">
         <v>90</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AV2" t="s">
         <v>91</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AW2" t="s">
         <v>92</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AX2" t="s">
         <v>93</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="AY2" t="s">
         <v>94</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AZ2" t="s">
         <v>95</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="BA2" t="s">
         <v>96</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="BB2" t="s">
         <v>97</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="BC2" t="s">
         <v>98</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="BD2" t="s">
         <v>99</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BE2" t="s">
         <v>100</v>
       </c>
-      <c r="BD2" s="2" t="s">
+      <c r="BF2" t="s">
         <v>101</v>
       </c>
-      <c r="BE2" s="2" t="s">
+      <c r="BG2" t="s">
         <v>102</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BH2" t="s">
         <v>103</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BI2" t="s">
         <v>104</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BJ2" t="s">
         <v>105</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BK2" t="s">
         <v>106</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BL2" t="s">
         <v>107</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BM2" t="s">
         <v>108</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BN2" t="s">
         <v>109</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BO2" t="s">
         <v>110</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BP2" t="s">
         <v>111</v>
       </c>
-      <c r="BO2" s="2" t="s">
+      <c r="BQ2" t="s">
         <v>112</v>
       </c>
-      <c r="BP2" s="2" t="s">
+      <c r="BR2" t="s">
         <v>113</v>
       </c>
-      <c r="BQ2" s="2" t="s">
+      <c r="BS2" t="s">
         <v>114</v>
       </c>
-      <c r="BR2" s="2" t="s">
+      <c r="BT2" t="s">
         <v>115</v>
       </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BU2" t="s">
         <v>116</v>
       </c>
-      <c r="BT2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
         <v>119</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K3" t="s">
+        <v>119</v>
+      </c>
+      <c r="L3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M3" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" t="s">
+        <v>119</v>
+      </c>
+      <c r="O3" t="s">
+        <v>119</v>
+      </c>
+      <c r="P3" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>119</v>
+      </c>
+      <c r="R3" t="s">
+        <v>119</v>
+      </c>
+      <c r="S3" t="s">
+        <v>119</v>
+      </c>
+      <c r="T3" t="s">
+        <v>119</v>
+      </c>
+      <c r="U3" t="s">
+        <v>118</v>
+      </c>
+      <c r="V3" t="s">
+        <v>119</v>
+      </c>
+      <c r="W3" t="s">
+        <v>119</v>
+      </c>
+      <c r="X3" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK3" t="s">
         <v>120</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="AL3" t="s">
         <v>120</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="U3" s="2" t="s">
+      <c r="AM3" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>121</v>
+      </c>
+      <c r="AQ3" t="s">
         <v>119</v>
       </c>
-      <c r="V3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="X3" s="2" t="s">
+      <c r="AR3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AW3" t="s">
         <v>119</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="AX3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BJ3" t="s">
         <v>119</v>
       </c>
-      <c r="Z3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AD3" s="2" t="s">
+      <c r="BK3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BU3" t="s">
         <v>118</v>
       </c>
-      <c r="AE3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AI3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AS3" s="2"/>
-      <c r="AT3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AV3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AW3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AY3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BA3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BK3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BM3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>127</v>
       </c>
-      <c r="BN3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="D4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>90</v>
+      </c>
+      <c r="K4">
+        <v>3903</v>
+      </c>
+      <c r="M4">
+        <v>715</v>
+      </c>
+      <c r="O4">
+        <v>607</v>
+      </c>
+      <c r="Q4">
+        <v>10</v>
+      </c>
+      <c r="S4">
+        <v>24</v>
+      </c>
+      <c r="U4">
+        <v>0.5</v>
+      </c>
+      <c r="V4">
+        <v>70</v>
+      </c>
+      <c r="Y4">
+        <v>0.05</v>
+      </c>
+      <c r="Z4">
+        <v>1.6</v>
+      </c>
+      <c r="AC4">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="AJ4" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>131</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>132</v>
+      </c>
+      <c r="AM4" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="AN4" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>133</v>
+      </c>
+      <c r="AQ4">
+        <v>3</v>
+      </c>
+      <c r="AR4">
+        <v>0.5</v>
+      </c>
+      <c r="AY4">
+        <v>0.25</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>134</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>135</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>136</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>137</v>
+      </c>
+      <c r="BH4" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G4" s="2">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2">
-        <v>2</v>
-      </c>
-      <c r="J4" s="2">
-        <v>90</v>
-      </c>
-      <c r="K4" s="2">
-        <v>3903</v>
-      </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2">
-        <v>715</v>
-      </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2">
-        <v>607</v>
-      </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2">
-        <v>10</v>
-      </c>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2">
-        <v>24</v>
-      </c>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="V4" s="2">
-        <v>70</v>
-      </c>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="Z4" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="AA4" s="2"/>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="2"/>
-      <c r="AE4" s="2"/>
-      <c r="AF4" s="2"/>
-      <c r="AG4" s="2"/>
-      <c r="AH4" s="2"/>
-      <c r="AI4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ4" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="AK4" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL4" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AM4" s="2"/>
-      <c r="AN4" s="2"/>
-      <c r="AO4" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AP4" s="2">
-        <v>3</v>
-      </c>
-      <c r="AQ4" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="AR4" s="2"/>
-      <c r="AS4" s="2"/>
-      <c r="AT4" s="2"/>
-      <c r="AU4" s="2"/>
-      <c r="AV4" s="2"/>
-      <c r="AW4" s="2"/>
-      <c r="AX4" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="AY4" s="2"/>
-      <c r="AZ4" s="2"/>
-      <c r="BA4" s="2"/>
-      <c r="BB4" s="2"/>
-      <c r="BC4" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BD4" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="BE4" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="BF4" s="2" t="s">
+      <c r="BI4" t="s">
         <v>138</v>
       </c>
-      <c r="BG4" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="BH4" s="2" t="s">
+      <c r="BJ4">
+        <v>6</v>
+      </c>
+      <c r="BK4" t="s">
         <v>139</v>
       </c>
-      <c r="BI4" s="2">
-        <v>6</v>
-      </c>
-      <c r="BJ4" s="2" t="s">
+      <c r="BL4" t="s">
         <v>140</v>
       </c>
-      <c r="BK4" s="2" t="s">
+      <c r="BM4" t="s">
         <v>141</v>
       </c>
-      <c r="BL4" s="2" t="s">
+      <c r="BO4" t="s">
         <v>142</v>
       </c>
-      <c r="BM4" s="2"/>
-      <c r="BN4" s="2" t="s">
+      <c r="BP4" t="s">
         <v>143</v>
       </c>
-      <c r="BO4" s="2" t="s">
+      <c r="BR4" t="s">
         <v>144</v>
       </c>
-      <c r="BP4" s="2"/>
-      <c r="BQ4" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="BR4" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="BS4" s="2"/>
-      <c r="BT4" s="2">
+      <c r="BS4" t="s">
+        <v>144</v>
+      </c>
+      <c r="BU4">
         <v>1</v>
       </c>
     </row>
@@ -3114,7 +3113,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3124,1862 +3122,1862 @@
   <dimension ref="A1:DI519"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1" style="2"/>
-    <col min="3" max="3" width="7.75" customWidth="1" style="2"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1" style="2"/>
-    <col min="9" max="9" width="7.33203125" customWidth="1" style="2"/>
-    <col min="10" max="10" width="15.75" customWidth="1" style="2"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="11.75" customWidth="1" style="2"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1" style="2"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1" style="2"/>
-    <col min="17" max="17" width="21.5" customWidth="1" style="2"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1" style="2"/>
-    <col min="22" max="22" width="17.75" customWidth="1" style="2"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1" style="2"/>
-    <col min="24" max="24" width="18.5" customWidth="1" style="2"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1" style="2"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1" style="2"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1" style="2"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1" style="2"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1" style="2"/>
-    <col min="32" max="32" width="13.75" customWidth="1" style="2"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1" style="2"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1" style="2"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="12.5" customWidth="1" style="2"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1" style="2"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="15" customWidth="1" style="2"/>
-    <col min="41" max="41" width="13.25" customWidth="1" style="2"/>
-    <col min="42" max="45" width="11.83203125" customWidth="1" style="2"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1" style="2"/>
-    <col min="47" max="47" width="12.25" customWidth="1" style="2"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1" style="2"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1" style="2"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1" style="2"/>
-    <col min="51" max="51" width="9" customWidth="1" style="2"/>
-    <col min="52" max="52" width="7" customWidth="1" style="2"/>
-    <col min="53" max="53" width="11.75" customWidth="1" style="2"/>
-    <col min="54" max="54" width="19.75" customWidth="1" style="2"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1" style="2"/>
-    <col min="56" max="56" width="8.5" customWidth="1" style="2"/>
-    <col min="57" max="57" width="13.5" customWidth="1" style="2"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1" style="2"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1" style="2"/>
-    <col min="60" max="60" width="8.25" customWidth="1" style="2"/>
-    <col min="61" max="67" width="8.33203125" customWidth="1" style="2"/>
-    <col min="68" max="70" width="11.25" customWidth="1" style="2"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1" style="2"/>
-    <col min="72" max="73" width="8" customWidth="1" style="2"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1" style="2"/>
-    <col min="75" max="76" width="8.5" customWidth="1" style="2"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1" style="2"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1" style="2"/>
-    <col min="80" max="80" width="13.5" customWidth="1" style="2"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1" style="2"/>
-    <col min="82" max="82" width="15.75" customWidth="1" style="2"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1" style="2"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1" style="2"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1" style="2"/>
-    <col min="86" max="86" width="9" customWidth="1" style="2"/>
-    <col min="87" max="87" width="16" customWidth="1" style="2"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1" style="2"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1" style="2"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1" style="2"/>
-    <col min="92" max="92" width="17.08203125" customWidth="1" style="2"/>
-    <col min="93" max="93" width="9.5" customWidth="1" style="2"/>
-    <col min="94" max="98" width="9" customWidth="1" style="2"/>
-    <col min="99" max="99" width="14" customWidth="1" style="2"/>
-    <col min="100" max="100" width="8" customWidth="1" style="2"/>
-    <col min="101" max="101" width="9" customWidth="1" style="2"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1" style="2"/>
-    <col min="103" max="103" width="13.75" customWidth="1" style="2"/>
-    <col min="104" max="104" width="9.5" customWidth="1" style="2"/>
-    <col min="105" max="106" width="9" customWidth="1" style="2"/>
-    <col min="107" max="108" width="9.5" customWidth="1" style="2"/>
-    <col min="109" max="109" width="9" customWidth="1" style="2"/>
-    <col min="110" max="110" width="15.5" customWidth="1" style="2"/>
-    <col min="111" max="111" width="9" customWidth="1" style="2"/>
-    <col min="112" max="113" width="9.5" customWidth="1" style="2"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1"/>
+    <col min="3" max="3" width="7.75" customWidth="1"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" customWidth="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1"/>
+    <col min="14" max="14" width="11.75" customWidth="1"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1"/>
+    <col min="17" max="17" width="21.5" customWidth="1"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1"/>
+    <col min="22" max="22" width="17.75" customWidth="1"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1"/>
+    <col min="24" max="24" width="18.5" customWidth="1"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1"/>
+    <col min="32" max="32" width="13.75" customWidth="1"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1"/>
+    <col min="36" max="36" width="12.5" customWidth="1"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1"/>
+    <col min="40" max="40" width="15" customWidth="1"/>
+    <col min="41" max="41" width="13.25" customWidth="1"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1"/>
+    <col min="47" max="47" width="12.25" customWidth="1"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1"/>
+    <col min="51" max="51" width="9" customWidth="1"/>
+    <col min="52" max="52" width="7" customWidth="1"/>
+    <col min="53" max="53" width="11.75" customWidth="1"/>
+    <col min="54" max="54" width="19.75" customWidth="1"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1"/>
+    <col min="56" max="56" width="8.5" customWidth="1"/>
+    <col min="57" max="57" width="13.5" customWidth="1"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1"/>
+    <col min="60" max="60" width="8.25" customWidth="1"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1"/>
+    <col min="68" max="70" width="11.25" customWidth="1"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1"/>
+    <col min="72" max="73" width="8" customWidth="1"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1"/>
+    <col min="75" max="76" width="8.5" customWidth="1"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1"/>
+    <col min="80" max="80" width="13.5" customWidth="1"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1"/>
+    <col min="82" max="82" width="15.75" customWidth="1"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1"/>
+    <col min="86" max="86" width="9" customWidth="1"/>
+    <col min="87" max="87" width="16" customWidth="1"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1"/>
+    <col min="93" max="93" width="9.5" customWidth="1"/>
+    <col min="94" max="98" width="9" customWidth="1"/>
+    <col min="99" max="99" width="14" customWidth="1"/>
+    <col min="100" max="100" width="8" customWidth="1"/>
+    <col min="101" max="101" width="9" customWidth="1"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1"/>
+    <col min="103" max="103" width="13.75" customWidth="1"/>
+    <col min="104" max="104" width="9.5" customWidth="1"/>
+    <col min="105" max="106" width="9" customWidth="1"/>
+    <col min="107" max="108" width="9.5" customWidth="1"/>
+    <col min="109" max="109" width="9" customWidth="1"/>
+    <col min="110" max="110" width="15.5" customWidth="1"/>
+    <col min="111" max="111" width="9" customWidth="1"/>
+    <col min="112" max="113" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D1" t="s">
         <v>146</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" t="s">
         <v>147</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" t="s">
         <v>148</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" t="s">
         <v>149</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" t="s">
         <v>150</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" t="s">
         <v>151</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" t="s">
         <v>152</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" t="s">
         <v>153</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" t="s">
         <v>154</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" t="s">
         <v>155</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" t="s">
         <v>156</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" t="s">
         <v>157</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" t="s">
         <v>158</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" t="s">
         <v>159</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" t="s">
         <v>160</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" t="s">
         <v>161</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" t="s">
         <v>162</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" t="s">
+        <v>162</v>
+      </c>
+      <c r="V1" t="s">
         <v>163</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" t="s">
         <v>164</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" t="s">
         <v>165</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" t="s">
         <v>166</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" t="s">
         <v>167</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" t="s">
         <v>168</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" t="s">
         <v>169</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" t="s">
         <v>170</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" t="s">
         <v>171</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" t="s">
         <v>172</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" t="s">
         <v>173</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" t="s">
         <v>174</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AH1" t="s">
         <v>175</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" t="s">
         <v>176</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" t="s">
         <v>177</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" t="s">
         <v>178</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AL1" t="s">
         <v>179</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AM1" t="s">
         <v>180</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AN1" t="s">
         <v>181</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AO1" t="s">
         <v>182</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AP1" t="s">
         <v>183</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AQ1" t="s">
         <v>184</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AR1" t="s">
         <v>185</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AS1" t="s">
         <v>186</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AT1" t="s">
         <v>187</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AU1" t="s">
         <v>188</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AV1" t="s">
         <v>189</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AW1" t="s">
         <v>190</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AX1" t="s">
         <v>191</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AY1" t="s">
         <v>192</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AZ1" t="s">
         <v>193</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="BA1" t="s">
         <v>194</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BB1" t="s">
         <v>195</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BC1" t="s">
         <v>196</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BD1" t="s">
         <v>197</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BE1" t="s">
         <v>198</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BF1" t="s">
         <v>199</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BG1" t="s">
         <v>200</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BH1" t="s">
         <v>201</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BJ1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BK1" t="s">
         <v>202</v>
       </c>
-      <c r="BJ1" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BL1" t="s">
         <v>203</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BM1" t="s">
         <v>204</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BN1" t="s">
         <v>205</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BO1" t="s">
         <v>206</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BP1" t="s">
         <v>207</v>
       </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BQ1" t="s">
         <v>208</v>
       </c>
-      <c r="BQ1" s="2" t="s">
+      <c r="BR1" t="s">
         <v>209</v>
       </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BS1" t="s">
         <v>210</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BT1" t="s">
         <v>211</v>
       </c>
-      <c r="BT1" s="2" t="s">
+      <c r="BU1" t="s">
         <v>212</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BV1" t="s">
         <v>213</v>
       </c>
-      <c r="BV1" s="2" t="s">
+      <c r="BW1" t="s">
         <v>214</v>
       </c>
-      <c r="BW1" s="2" t="s">
+      <c r="BX1" t="s">
         <v>215</v>
       </c>
-      <c r="BX1" s="2" t="s">
+      <c r="BY1" t="s">
         <v>216</v>
       </c>
-      <c r="BY1" s="2" t="s">
+      <c r="BZ1" t="s">
         <v>217</v>
       </c>
-      <c r="BZ1" s="2" t="s">
+      <c r="CA1" t="s">
         <v>218</v>
       </c>
-      <c r="CA1" s="2" t="s">
+      <c r="CB1" t="s">
         <v>219</v>
       </c>
-      <c r="CB1" s="2" t="s">
+      <c r="CC1" t="s">
         <v>220</v>
       </c>
-      <c r="CC1" s="2" t="s">
+      <c r="CD1" t="s">
         <v>221</v>
       </c>
-      <c r="CD1" s="2" t="s">
+      <c r="CE1" t="s">
         <v>222</v>
       </c>
-      <c r="CE1" s="2" t="s">
+      <c r="CF1" t="s">
         <v>223</v>
       </c>
-      <c r="CF1" s="2" t="s">
+      <c r="CG1" t="s">
         <v>224</v>
       </c>
-      <c r="CG1" s="2" t="s">
+      <c r="CH1" t="s">
         <v>225</v>
       </c>
-      <c r="CH1" s="2" t="s">
+      <c r="CI1" t="s">
         <v>226</v>
       </c>
-      <c r="CI1" s="2" t="s">
+      <c r="CJ1" t="s">
         <v>227</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CK1" t="s">
         <v>228</v>
       </c>
-      <c r="CK1" s="2" t="s">
+      <c r="CL1" t="s">
         <v>229</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CM1" t="s">
         <v>230</v>
       </c>
-      <c r="CM1" s="2" t="s">
+      <c r="CN1" t="s">
         <v>231</v>
       </c>
-      <c r="CN1" s="2" t="s">
+      <c r="CO1" t="s">
         <v>232</v>
       </c>
-      <c r="CO1" s="2" t="s">
+      <c r="CP1" t="s">
         <v>233</v>
       </c>
-      <c r="CP1" s="2" t="s">
+      <c r="CQ1" t="s">
         <v>234</v>
       </c>
-      <c r="CQ1" s="2" t="s">
+      <c r="CR1" t="s">
+        <v>211</v>
+      </c>
+      <c r="CS1" t="s">
         <v>235</v>
       </c>
-      <c r="CR1" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="CS1" s="2" t="s">
+      <c r="CT1" t="s">
         <v>236</v>
       </c>
-      <c r="CT1" s="2" t="s">
+      <c r="CU1" t="s">
         <v>237</v>
       </c>
-      <c r="CU1" s="2" t="s">
+      <c r="CV1" t="s">
         <v>238</v>
       </c>
-      <c r="CV1" s="2" t="s">
+      <c r="CW1" t="s">
         <v>239</v>
       </c>
-      <c r="CW1" s="2" t="s">
+      <c r="CX1" t="s">
         <v>240</v>
       </c>
-      <c r="CX1" s="2" t="s">
+      <c r="CY1" t="s">
         <v>241</v>
       </c>
-      <c r="CY1" s="2" t="s">
+      <c r="CZ1" t="s">
+        <v>240</v>
+      </c>
+      <c r="DA1" t="s">
         <v>242</v>
       </c>
-      <c r="CZ1" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="DA1" s="2" t="s">
+      <c r="DB1" t="s">
         <v>243</v>
       </c>
-      <c r="DB1" s="2" t="s">
+      <c r="DC1" t="s">
         <v>244</v>
       </c>
-      <c r="DC1" s="2" t="s">
+      <c r="DD1" t="s">
         <v>245</v>
       </c>
-      <c r="DD1" s="2" t="s">
+      <c r="DE1" t="s">
         <v>246</v>
       </c>
-      <c r="DE1" s="2" t="s">
+      <c r="DF1" t="s">
         <v>247</v>
       </c>
-      <c r="DF1" s="2" t="s">
+      <c r="DG1" t="s">
         <v>248</v>
       </c>
-      <c r="DG1" s="2" t="s">
+      <c r="DH1" t="s">
         <v>249</v>
       </c>
-      <c r="DH1" s="2" t="s">
+      <c r="DI1" t="s">
         <v>250</v>
       </c>
-      <c r="DI1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="F2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J2" t="s">
+        <v>255</v>
+      </c>
+      <c r="K2" t="s">
+        <v>256</v>
+      </c>
+      <c r="L2" t="s">
+        <v>257</v>
+      </c>
+      <c r="M2" t="s">
+        <v>258</v>
+      </c>
+      <c r="N2" t="s">
+        <v>259</v>
+      </c>
+      <c r="O2" t="s">
+        <v>260</v>
+      </c>
+      <c r="P2" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>262</v>
+      </c>
+      <c r="R2" t="s">
+        <v>263</v>
+      </c>
+      <c r="S2" t="s">
+        <v>264</v>
+      </c>
+      <c r="T2" t="s">
+        <v>265</v>
+      </c>
+      <c r="U2" t="s">
+        <v>266</v>
+      </c>
+      <c r="V2" t="s">
+        <v>267</v>
+      </c>
+      <c r="W2" t="s">
+        <v>268</v>
+      </c>
+      <c r="X2" t="s">
+        <v>269</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>270</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>271</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>272</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>273</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>275</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>277</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>278</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>279</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>281</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>282</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>283</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>284</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>285</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>286</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>287</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>288</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>289</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>290</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>292</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>293</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>294</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>295</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>296</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>297</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>298</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>299</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>300</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>301</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>302</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>303</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>304</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>305</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>306</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>307</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>308</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>309</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>310</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>311</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>81</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>312</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>313</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>314</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>315</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>316</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>96</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>317</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>318</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>319</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>320</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>321</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>322</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>323</v>
+      </c>
+      <c r="CC2" t="s">
+        <v>324</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>325</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>326</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>327</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>328</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>329</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>330</v>
+      </c>
+      <c r="CJ2" t="s">
+        <v>331</v>
+      </c>
+      <c r="CK2" t="s">
+        <v>332</v>
+      </c>
+      <c r="CL2" t="s">
+        <v>333</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>334</v>
+      </c>
+      <c r="CN2" t="s">
+        <v>335</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>336</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>337</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>338</v>
+      </c>
+      <c r="CR2" t="s">
+        <v>339</v>
+      </c>
+      <c r="CS2" t="s">
+        <v>340</v>
+      </c>
+      <c r="CT2" t="s">
+        <v>341</v>
+      </c>
+      <c r="CU2" t="s">
+        <v>342</v>
+      </c>
+      <c r="CV2" t="s">
+        <v>343</v>
+      </c>
+      <c r="CW2" t="s">
+        <v>344</v>
+      </c>
+      <c r="CX2" t="s">
+        <v>345</v>
+      </c>
+      <c r="CY2" t="s">
+        <v>346</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>347</v>
+      </c>
+      <c r="DA2" t="s">
+        <v>348</v>
+      </c>
+      <c r="DB2" t="s">
+        <v>349</v>
+      </c>
+      <c r="DC2" t="s">
+        <v>350</v>
+      </c>
+      <c r="DD2" t="s">
+        <v>351</v>
+      </c>
+      <c r="DE2" t="s">
+        <v>352</v>
+      </c>
+      <c r="DF2" t="s">
+        <v>353</v>
+      </c>
+      <c r="DG2" t="s">
+        <v>354</v>
+      </c>
+      <c r="DH2" t="s">
+        <v>355</v>
+      </c>
+      <c r="DI2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J3" t="s">
+        <v>357</v>
+      </c>
+      <c r="K3" t="s">
+        <v>358</v>
+      </c>
+      <c r="L3" t="s">
+        <v>359</v>
+      </c>
+      <c r="M3" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" t="s">
+        <v>119</v>
+      </c>
+      <c r="O3" t="s">
+        <v>122</v>
+      </c>
+      <c r="P3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>122</v>
+      </c>
+      <c r="R3" t="s">
+        <v>122</v>
+      </c>
+      <c r="S3" t="s">
+        <v>117</v>
+      </c>
+      <c r="T3" t="s">
+        <v>118</v>
+      </c>
+      <c r="U3" t="s">
+        <v>118</v>
+      </c>
+      <c r="V3" t="s">
+        <v>118</v>
+      </c>
+      <c r="W3" t="s">
+        <v>117</v>
+      </c>
+      <c r="X3" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>360</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>362</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>363</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>364</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>363</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>365</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>366</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BY3" t="s">
+        <v>367</v>
+      </c>
+      <c r="BZ3" t="s">
+        <v>117</v>
+      </c>
+      <c r="CA3" t="s">
+        <v>367</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CC3" t="s">
+        <v>368</v>
+      </c>
+      <c r="CD3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CG3" t="s">
+        <v>369</v>
+      </c>
+      <c r="CH3" t="s">
+        <v>370</v>
+      </c>
+      <c r="CI3" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" t="s">
+        <v>371</v>
+      </c>
+      <c r="CK3" t="s">
+        <v>371</v>
+      </c>
+      <c r="CL3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CM3" t="s">
+        <v>122</v>
+      </c>
+      <c r="CN3" t="s">
+        <v>122</v>
+      </c>
+      <c r="CO3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CQ3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CR3" t="s">
+        <v>368</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>117</v>
+      </c>
+      <c r="CU3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CV3" t="s">
+        <v>372</v>
+      </c>
+      <c r="CW3" t="s">
+        <v>373</v>
+      </c>
+      <c r="CX3" t="s">
+        <v>373</v>
+      </c>
+      <c r="CY3" t="s">
+        <v>372</v>
+      </c>
+      <c r="CZ3" t="s">
+        <v>372</v>
+      </c>
+      <c r="DA3" t="s">
+        <v>372</v>
+      </c>
+      <c r="DB3" t="s">
+        <v>372</v>
+      </c>
+      <c r="DC3" t="s">
+        <v>372</v>
+      </c>
+      <c r="DD3" t="s">
+        <v>117</v>
+      </c>
+      <c r="DE3" t="s">
+        <v>117</v>
+      </c>
+      <c r="DF3" t="s">
+        <v>117</v>
+      </c>
+      <c r="DG3" t="s">
+        <v>117</v>
+      </c>
+      <c r="DH3" t="s">
+        <v>117</v>
+      </c>
+      <c r="DI3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="5" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C5" t="s">
+        <v>140</v>
+      </c>
+      <c r="AC5">
+        <v>2</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>376</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>377</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>378</v>
+      </c>
+      <c r="AZ5">
+        <v>1</v>
+      </c>
+      <c r="BD5">
+        <v>1</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>57</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>379</v>
+      </c>
+      <c r="CY5" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>381</v>
+      </c>
+      <c r="C6" t="s">
+        <v>382</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>383</v>
+      </c>
+      <c r="BD6">
+        <v>1</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>384</v>
+      </c>
+      <c r="BS6">
+        <v>0.1</v>
+      </c>
+      <c r="CN6" t="s">
+        <v>385</v>
+      </c>
+      <c r="CO6" t="s">
+        <v>386</v>
+      </c>
+      <c r="CR6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C7" t="s">
+        <v>382</v>
+      </c>
+      <c r="AC7">
+        <v>2</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>376</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>377</v>
+      </c>
+      <c r="BD7">
+        <v>99</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>387</v>
+      </c>
+      <c r="BS7">
+        <v>0.1</v>
+      </c>
+      <c r="CN7" t="s">
+        <v>384</v>
+      </c>
+      <c r="CR7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>387</v>
+      </c>
+      <c r="C8" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>384</v>
+      </c>
+      <c r="AC8">
+        <v>2</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV8">
+        <v>99</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>388</v>
+      </c>
+      <c r="AZ8">
+        <v>0.4</v>
+      </c>
+      <c r="BD8">
+        <v>99</v>
+      </c>
+      <c r="BS8">
+        <v>1</v>
+      </c>
+      <c r="CL8" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>390</v>
+      </c>
+      <c r="C10" t="s">
+        <v>382</v>
+      </c>
+      <c r="D10" t="s">
+        <v>391</v>
+      </c>
+      <c r="E10" t="s">
+        <v>392</v>
+      </c>
+      <c r="F10" t="s">
+        <v>393</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="J10" t="s">
+        <v>394</v>
+      </c>
+      <c r="K10" t="s">
+        <v>395</v>
+      </c>
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>383</v>
+      </c>
+      <c r="BD10">
+        <v>1</v>
+      </c>
+      <c r="BO10" t="s">
+        <v>396</v>
+      </c>
+      <c r="BT10">
+        <v>30</v>
+      </c>
+      <c r="BV10">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="AF2" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="AG2" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AH2" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="AI2" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="AK2" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="AL2" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="AM2" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="AN2" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="AO2" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="AP2" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="AQ2" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="AR2" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="AT2" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="AU2" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="AV2" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="AW2" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="AX2" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="AY2" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="AZ2" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="BA2" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="BB2" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="BC2" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="BD2" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="BE2" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="BF2" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="BG2" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="BH2" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="BI2" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="BJ2" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="BK2" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="BL2" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="BM2" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="BN2" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="BO2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="BP2" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="BQ2" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="BR2" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="BS2" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="BT2" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="BU2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="BV2" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="BW2" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="BX2" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="BY2" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="BZ2" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="CA2" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="CB2" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="CC2" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="CD2" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="CE2" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="CF2" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="CG2" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="CH2" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="CI2" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="CJ2" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="CK2" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="CL2" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="CM2" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="CN2" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="CO2" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="CP2" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="CQ2" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="CR2" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="CS2" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="CT2" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="CU2" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="CV2" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="CW2" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="CX2" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="CY2" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="CZ2" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="DA2" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="DB2" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="DC2" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="DD2" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="DE2" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="DF2" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="DG2" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="DH2" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="DI2" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AI3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="BW10">
+        <v>16</v>
+      </c>
+      <c r="BX10">
+        <v>1</v>
+      </c>
+      <c r="BY10" t="s">
+        <v>397</v>
+      </c>
+      <c r="CG10" t="s">
+        <v>379</v>
+      </c>
+      <c r="CN10" t="s">
+        <v>398</v>
+      </c>
+      <c r="CO10">
+        <v>0.7</v>
+      </c>
+      <c r="CP10">
+        <v>0.7</v>
+      </c>
+      <c r="CR10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>399</v>
+      </c>
+      <c r="C11" t="s">
+        <v>382</v>
+      </c>
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>383</v>
+      </c>
+      <c r="BD11">
+        <v>1</v>
+      </c>
+      <c r="CN11" t="s">
+        <v>400</v>
+      </c>
+      <c r="CO11">
+        <v>1</v>
+      </c>
+      <c r="CR11">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>401</v>
+      </c>
+      <c r="C12" t="s">
+        <v>140</v>
+      </c>
+      <c r="O12" t="s">
+        <v>402</v>
+      </c>
+      <c r="AC12">
+        <v>2</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>376</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>377</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>378</v>
+      </c>
+      <c r="AZ12">
+        <v>1</v>
+      </c>
+      <c r="BD12">
+        <v>1</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>403</v>
+      </c>
+      <c r="CG12" t="s">
+        <v>379</v>
+      </c>
+      <c r="CY12" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>404</v>
+      </c>
+      <c r="C13" t="s">
+        <v>382</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="K13" t="s">
+        <v>405</v>
+      </c>
+      <c r="L13" t="s">
+        <v>406</v>
+      </c>
+      <c r="O13" t="s">
+        <v>402</v>
+      </c>
+      <c r="AC13">
+        <v>2</v>
+      </c>
+      <c r="AD13">
+        <v>1</v>
+      </c>
+      <c r="AE13">
+        <v>1</v>
+      </c>
+      <c r="BD13">
+        <v>1</v>
+      </c>
+      <c r="CL13" t="s">
+        <v>407</v>
+      </c>
+      <c r="CY13" t="s">
+        <v>408</v>
+      </c>
+      <c r="DD13">
+        <v>1</v>
+      </c>
+      <c r="DH13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>409</v>
+      </c>
+      <c r="C15" t="s">
+        <v>382</v>
+      </c>
+      <c r="D15" t="s">
+        <v>410</v>
+      </c>
+      <c r="E15" t="s">
+        <v>411</v>
+      </c>
+      <c r="F15" t="s">
+        <v>412</v>
+      </c>
+      <c r="G15">
         <v>3</v>
       </c>
-      <c r="AK3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT3" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AV3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AW3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="AY3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BA3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BK3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BW3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BX3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BY3" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="BZ3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="CA3" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="CB3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CC3" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="CD3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CF3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CG3" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="CH3" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="CI3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="CJ3" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="CK3" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="CL3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CM3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="CN3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="CO3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="CP3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="CQ3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="CR3" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="CS3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="CT3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="CU3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CV3" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="CW3" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="CX3" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="CY3" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="CZ3" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="DA3" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="DB3" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="DC3" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="DD3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="DE3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="DF3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="DG3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="DH3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="DI3" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="J15" t="s">
+        <v>394</v>
+      </c>
+      <c r="K15" t="s">
+        <v>395</v>
+      </c>
+      <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>383</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>413</v>
+      </c>
+      <c r="BD15">
+        <v>1</v>
+      </c>
+      <c r="BO15" t="s">
+        <v>414</v>
+      </c>
+      <c r="BP15" t="s">
+        <v>415</v>
+      </c>
+      <c r="BT15">
+        <v>20</v>
+      </c>
+      <c r="BV15">
+        <v>20</v>
+      </c>
+      <c r="BW15">
+        <v>26</v>
+      </c>
+      <c r="BX15">
+        <v>1</v>
+      </c>
+      <c r="BY15" t="s">
+        <v>416</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>417</v>
+      </c>
+      <c r="CG15" t="s">
+        <v>379</v>
+      </c>
+      <c r="CN15" t="s">
+        <v>418</v>
+      </c>
+      <c r="CO15">
+        <v>1.6</v>
+      </c>
+      <c r="CP15">
+        <v>2.9</v>
+      </c>
+      <c r="CQ15">
+        <v>2</v>
+      </c>
+      <c r="CR15">
+        <v>20</v>
+      </c>
+      <c r="CW15" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>415</v>
+      </c>
+      <c r="C16" t="s">
+        <v>420</v>
+      </c>
+      <c r="K16" t="s">
+        <v>405</v>
+      </c>
+      <c r="AC16">
+        <v>2</v>
+      </c>
+      <c r="AO16" t="s">
         <v>376</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AC5" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO5" s="2" t="s">
+      <c r="AP16" t="s">
+        <v>421</v>
+      </c>
+      <c r="AT16" t="s">
+        <v>413</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>388</v>
+      </c>
+      <c r="AZ16">
+        <v>1</v>
+      </c>
+      <c r="BD16">
+        <v>99</v>
+      </c>
+      <c r="CU16" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="17" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>414</v>
+      </c>
+      <c r="C17" t="s">
+        <v>140</v>
+      </c>
+      <c r="O17" t="s">
+        <v>423</v>
+      </c>
+      <c r="AC17">
+        <v>2</v>
+      </c>
+      <c r="AO17" t="s">
+        <v>376</v>
+      </c>
+      <c r="AT17" t="s">
         <v>377</v>
       </c>
-      <c r="AT5" s="2" t="s">
+      <c r="AX17" t="s">
+        <v>388</v>
+      </c>
+      <c r="AZ17">
+        <v>1</v>
+      </c>
+      <c r="BD17">
+        <v>1</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>417</v>
+      </c>
+      <c r="CG17" t="s">
+        <v>379</v>
+      </c>
+      <c r="CY17" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="19" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>424</v>
+      </c>
+      <c r="C19" t="s">
+        <v>382</v>
+      </c>
+      <c r="D19" t="s">
+        <v>425</v>
+      </c>
+      <c r="E19" t="s">
+        <v>426</v>
+      </c>
+      <c r="F19" t="s">
+        <v>427</v>
+      </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
+      <c r="J19" t="s">
+        <v>394</v>
+      </c>
+      <c r="K19" t="s">
+        <v>395</v>
+      </c>
+      <c r="AC19">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>383</v>
+      </c>
+      <c r="BD19">
+        <v>1</v>
+      </c>
+      <c r="BO19" t="s">
+        <v>428</v>
+      </c>
+      <c r="BP19" t="s">
+        <v>429</v>
+      </c>
+      <c r="BT19">
+        <v>45</v>
+      </c>
+      <c r="BV19">
+        <v>42</v>
+      </c>
+      <c r="BW19">
+        <v>55</v>
+      </c>
+      <c r="BX19">
+        <v>1</v>
+      </c>
+      <c r="BY19" t="s">
+        <v>416</v>
+      </c>
+      <c r="CG19" t="s">
+        <v>379</v>
+      </c>
+      <c r="CN19" t="s">
+        <v>430</v>
+      </c>
+      <c r="CO19">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="CP19">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="CQ19">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="CR19">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>431</v>
+      </c>
+      <c r="C20" t="s">
+        <v>432</v>
+      </c>
+      <c r="K20" t="s">
+        <v>405</v>
+      </c>
+      <c r="L20" t="s">
+        <v>433</v>
+      </c>
+      <c r="O20" t="s">
+        <v>423</v>
+      </c>
+      <c r="AC20">
+        <v>2</v>
+      </c>
+      <c r="AO20" t="s">
+        <v>376</v>
+      </c>
+      <c r="AX20" t="s">
         <v>378</v>
       </c>
-      <c r="AX5" s="2" t="s">
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <v>2</v>
+      </c>
+      <c r="BD20">
+        <v>1</v>
+      </c>
+      <c r="CL20" t="s">
+        <v>434</v>
+      </c>
+      <c r="CU20" t="s">
+        <v>435</v>
+      </c>
+      <c r="CY20" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="21" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>436</v>
+      </c>
+      <c r="C21" t="s">
+        <v>140</v>
+      </c>
+      <c r="O21" t="s">
+        <v>423</v>
+      </c>
+      <c r="AC21">
+        <v>2</v>
+      </c>
+      <c r="AO21" t="s">
+        <v>376</v>
+      </c>
+      <c r="AT21" t="s">
+        <v>377</v>
+      </c>
+      <c r="AX21" t="s">
+        <v>378</v>
+      </c>
+      <c r="AZ21">
+        <v>1</v>
+      </c>
+      <c r="BD21">
+        <v>1</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>437</v>
+      </c>
+      <c r="CG21" t="s">
         <v>379</v>
       </c>
-      <c r="AZ5" s="2">
+      <c r="CY21" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="22" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>429</v>
+      </c>
+      <c r="C22" t="s">
+        <v>382</v>
+      </c>
+      <c r="I22">
         <v>1</v>
       </c>
-      <c r="BD5" s="2">
+      <c r="K22" t="s">
+        <v>405</v>
+      </c>
+      <c r="AC22">
         <v>1</v>
       </c>
-      <c r="CB5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="CG5" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="CY5" s="2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="AG22" t="s">
+        <v>383</v>
+      </c>
+      <c r="BD22">
+        <v>1</v>
+      </c>
+      <c r="BS22">
+        <v>1.6</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>438</v>
+      </c>
+      <c r="CG22" t="s">
+        <v>379</v>
+      </c>
+      <c r="DD22">
+        <v>1</v>
+      </c>
+      <c r="DG22">
+        <v>1</v>
+      </c>
+      <c r="DH22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>439</v>
+      </c>
+      <c r="C23" t="s">
         <v>382</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="K23" t="s">
+        <v>405</v>
+      </c>
+      <c r="L23" t="s">
+        <v>440</v>
+      </c>
+      <c r="AC23">
+        <v>1</v>
+      </c>
+      <c r="AG23" t="s">
         <v>383</v>
       </c>
-      <c r="AC6" s="2">
+      <c r="BD23">
         <v>1</v>
       </c>
-      <c r="AG6" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="BD6" s="2">
+      <c r="BS23">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>441</v>
+      </c>
+      <c r="CG23" t="s">
+        <v>379</v>
+      </c>
+      <c r="DD23">
         <v>1</v>
       </c>
-      <c r="BO6" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="BS6" s="2">
+      <c r="DG23">
+        <v>1</v>
+      </c>
+      <c r="DH23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="499" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL499">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="501" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL501">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="502" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL502">
         <v>0.1</v>
       </c>
-      <c r="CN6" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="CO6" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="CR6" s="2">
+    </row>
+    <row r="504" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL504">
         <v>0.2</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="AC7" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO7" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="AT7" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="BD7" s="2">
-        <v>99</v>
-      </c>
-      <c r="BO7" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="BS7" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CN7" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="CR7" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="AC8" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO8" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="AV8" s="2">
-        <v>99</v>
-      </c>
-      <c r="AX8" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="AZ8" s="2">
+    <row r="511" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL511">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="513" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL513">
         <v>0.4</v>
       </c>
-      <c r="BD8" s="2">
-        <v>99</v>
-      </c>
-      <c r="BS8" s="2">
-        <v>1</v>
-      </c>
-      <c r="CL8" s="2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="G10" s="2">
-        <v>3</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="AC10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="BD10" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO10" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="BT10" s="2">
-        <v>30</v>
-      </c>
-      <c r="BV10" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW10" s="2">
-        <v>16</v>
-      </c>
-      <c r="BX10" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY10" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="CG10" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="CN10" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="CO10" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="CP10" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="CR10" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="AC11" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="BD11" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN11" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="CO11" s="2">
-        <v>1</v>
-      </c>
-      <c r="CR11" s="2">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="AC12" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO12" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="AT12" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="AX12" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="AZ12" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD12" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB12" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="CG12" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="CY12" s="2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="AC13" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD13" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE13" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD13" s="2">
-        <v>1</v>
-      </c>
-      <c r="CL13" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="CY13" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="DD13" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH13" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="G15" s="2">
-        <v>3</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="AC15" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG15" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="AT15" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="BD15" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO15" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="BP15" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="BT15" s="2">
-        <v>20</v>
-      </c>
-      <c r="BV15" s="2">
-        <v>20</v>
-      </c>
-      <c r="BW15" s="2">
-        <v>26</v>
-      </c>
-      <c r="BX15" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY15" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="CB15" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="CG15" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="CN15" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="CO15" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="CP15" s="2">
-        <v>2.9</v>
-      </c>
-      <c r="CQ15" s="2">
-        <v>2</v>
-      </c>
-      <c r="CR15" s="2">
-        <v>20</v>
-      </c>
-      <c r="CW15" s="2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="AC16" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO16" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="AP16" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="AT16" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="AX16" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="AZ16" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD16" s="2">
-        <v>99</v>
-      </c>
-      <c r="CU16" s="2" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="AC17" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO17" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="AT17" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="AX17" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="AZ17" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD17" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB17" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="CG17" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="CY17" s="2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="G19" s="2">
-        <v>3</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="AC19" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG19" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="BD19" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO19" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="BP19" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="BT19" s="2">
-        <v>45</v>
-      </c>
-      <c r="BV19" s="2">
-        <v>42</v>
-      </c>
-      <c r="BW19" s="2">
-        <v>55</v>
-      </c>
-      <c r="BX19" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY19" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="CG19" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="CN19" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="CO19" s="2">
-        <v>1.1</v>
-      </c>
-      <c r="CP19" s="2">
-        <v>1.1</v>
-      </c>
-      <c r="CQ19" s="2">
-        <v>1.1</v>
-      </c>
-      <c r="CR19" s="2">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="AC20" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO20" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="AX20" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="AZ20" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB20" s="2">
-        <v>2</v>
-      </c>
-      <c r="BD20" s="2">
-        <v>1</v>
-      </c>
-      <c r="CL20" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="CU20" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="CY20" s="2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="AC21" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO21" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="AT21" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="AX21" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="AZ21" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD21" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB21" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="CG21" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="CY21" s="2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="I22" s="2">
-        <v>1</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="AC22" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG22" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="BD22" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS22" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="CB22" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="CG22" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="DD22" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG22" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH22" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="I23" s="2">
-        <v>1</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="AC23" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG23" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="BD23" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS23" s="2">
-        <v>0.1667</v>
-      </c>
-      <c r="CB23" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="CG23" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="DD23" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG23" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH23" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="499">
-      <c r="CL499" s="2">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="501">
-      <c r="CL501" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="502">
-      <c r="CL502" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="504">
-      <c r="CL504" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="511">
-      <c r="CL511" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="513">
-      <c r="CL513" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="514">
-      <c r="CL514" s="2">
+    </row>
+    <row r="514" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL514">
         <v>0.6</v>
       </c>
     </row>
-    <row r="517">
-      <c r="CL517" s="2">
+    <row r="517" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL517">
         <v>0.5</v>
       </c>
     </row>
-    <row r="518">
-      <c r="CL518" s="2">
-        <v>0.667</v>
-      </c>
-    </row>
-    <row r="519">
-      <c r="CL519" s="2">
+    <row r="518" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL518">
+        <v>0.66700000000000004</v>
+      </c>
+    </row>
+    <row r="519" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL519">
         <v>0.2</v>
       </c>
     </row>
@@ -4987,7 +4985,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -4997,216 +4994,216 @@
   <dimension ref="A1:Q279"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1" style="2"/>
-    <col min="2" max="2" width="31.25" customWidth="1" style="2"/>
-    <col min="3" max="6" width="9" customWidth="1" style="2"/>
-    <col min="7" max="7" width="18.75" customWidth="1" style="2"/>
-    <col min="8" max="8" width="15" customWidth="1" style="2"/>
-    <col min="9" max="13" width="9" customWidth="1" style="2"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1" style="2"/>
-    <col min="15" max="15" width="9.5" customWidth="1" style="2"/>
-    <col min="16" max="16" width="22.1640625" customWidth="1" style="2"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="31.25" customWidth="1"/>
+    <col min="3" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
+        <v>442</v>
+      </c>
+      <c r="F1" t="s">
         <v>443</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" t="s">
         <v>444</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" t="s">
         <v>445</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" t="s">
         <v>446</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" t="s">
         <v>447</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" t="s">
         <v>448</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" t="s">
         <v>449</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" t="s">
         <v>450</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" t="s">
         <v>451</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" t="s">
         <v>452</v>
       </c>
-      <c r="P1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" t="s">
         <v>454</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" t="s">
         <v>455</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" t="s">
         <v>456</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" t="s">
         <v>457</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" t="s">
         <v>458</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" t="s">
         <v>459</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M2" t="s">
         <v>460</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" t="s">
         <v>461</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" t="s">
         <v>462</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" t="s">
         <v>463</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J3" t="s">
+        <v>372</v>
+      </c>
+      <c r="K3" t="s">
+        <v>118</v>
+      </c>
+      <c r="L3" t="s">
+        <v>336</v>
+      </c>
+      <c r="M3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N3" t="s">
+        <v>117</v>
+      </c>
+      <c r="O3" t="s">
+        <v>336</v>
+      </c>
+      <c r="P3" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C4" t="s">
         <v>464</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="s">
         <v>465</v>
       </c>
-      <c r="F4" s="2">
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C5" t="s">
+        <v>466</v>
+      </c>
+      <c r="F5">
         <v>1</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>400</v>
+      </c>
+      <c r="C7" t="s">
+        <v>464</v>
+      </c>
+      <c r="Q7" t="s">
         <v>467</v>
       </c>
-      <c r="F5" s="2">
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>468</v>
+      </c>
+      <c r="C9" t="s">
+        <v>222</v>
+      </c>
+      <c r="H9">
         <v>1</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
+      <c r="Q9" t="s">
         <v>469</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="H9" s="2">
+    </row>
+    <row r="278" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P278">
         <v>1</v>
       </c>
-      <c r="Q9" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="P278" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="P279" s="2">
+    </row>
+    <row r="279" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P279">
         <v>1</v>
       </c>
     </row>
@@ -5214,7 +5211,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5223,53 +5219,52 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="11.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="27.5" customWidth="1" style="2"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>127</v>
+      <c r="D2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D3" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5278,87 +5273,86 @@
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="27.25" customWidth="1" style="2"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="27.25" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="I1" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" t="s">
+        <v>472</v>
+      </c>
+      <c r="E2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" t="s">
         <v>473</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" t="s">
         <v>474</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" t="s">
         <v>475</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="I2" t="s">
+        <v>331</v>
+      </c>
+      <c r="J2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>127</v>
+      <c r="G3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I3" t="s">
+        <v>371</v>
+      </c>
+      <c r="J3" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5367,130 +5361,129 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28" customWidth="1" style="2"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="11.25" customWidth="1" style="2"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1" style="2"/>
-    <col min="12" max="12" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1"/>
+    <col min="5" max="10" width="11.25" customWidth="1"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C1" t="s">
         <v>477</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" t="s">
         <v>478</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" t="s">
         <v>479</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" t="s">
         <v>480</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" t="s">
         <v>481</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" t="s">
         <v>482</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" t="s">
         <v>483</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" t="s">
         <v>484</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" t="s">
         <v>485</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" t="s">
         <v>487</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" t="s">
         <v>488</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" t="s">
         <v>489</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" t="s">
         <v>490</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" t="s">
         <v>491</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" t="s">
         <v>492</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" t="s">
         <v>493</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" t="s">
         <v>494</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" t="s">
+        <v>473</v>
+      </c>
+      <c r="L2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" t="s">
         <v>495</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K3" t="s">
         <v>118</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="L3" t="s">
         <v>118</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -5500,84 +5493,83 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="16.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1" style="2"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="10.25" customWidth="1" style="2"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1" style="2"/>
-    <col min="7" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.25" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E2" t="s">
         <v>497</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" t="s">
         <v>498</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2" t="s">
         <v>499</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>501</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -5586,153 +5578,152 @@
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5" customWidth="1" style="2"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1" style="2"/>
-    <col min="3" max="3" width="21.9140625" customWidth="1" style="2"/>
-    <col min="4" max="4" width="16.25" customWidth="1" style="2"/>
-    <col min="5" max="5" width="14" customWidth="1" style="2"/>
-    <col min="6" max="7" width="15.1640625" customWidth="1" style="2"/>
-    <col min="8" max="8" width="12.9140625" customWidth="1" style="2"/>
-    <col min="9" max="9" width="14" customWidth="1" style="2"/>
+    <col min="1" max="1" width="7.5" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.9140625" customWidth="1"/>
+    <col min="4" max="4" width="16.25" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="7" width="15.1640625" customWidth="1"/>
+    <col min="8" max="8" width="12.9140625" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C1" t="s">
         <v>502</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" t="s">
         <v>503</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" t="s">
         <v>504</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" t="s">
         <v>505</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" t="s">
         <v>506</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" t="s">
         <v>507</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" t="s">
         <v>508</v>
       </c>
-      <c r="I1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" t="s">
         <v>510</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" t="s">
         <v>511</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" t="s">
         <v>512</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" t="s">
         <v>513</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" t="s">
         <v>514</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" t="s">
         <v>515</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" t="s">
         <v>516</v>
       </c>
-      <c r="I2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>518</v>
       </c>
-      <c r="C4" s="2">
+      <c r="E4" t="s">
+        <v>519</v>
+      </c>
+      <c r="F4" t="s">
+        <v>520</v>
+      </c>
+      <c r="G4" t="s">
+        <v>521</v>
+      </c>
+      <c r="H4" t="s">
+        <v>522</v>
+      </c>
+      <c r="I4" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>524</v>
+      </c>
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>525</v>
       </c>
-      <c r="B5" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" t="s">
         <v>526</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" t="s">
         <v>527</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>528</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 

--- a/Excel/一方通行/余.xlsx
+++ b/Excel/一方通行/余.xlsx
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="537">
   <si>
     <t>Id</t>
   </si>
@@ -670,6 +670,9 @@
     <t>Ablititys</t>
   </si>
   <si>
+    <t>StartAnimation</t>
+  </si>
+  <si>
     <t>DefaultAnimation</t>
   </si>
   <si>
@@ -686,6 +689,9 @@
   </si>
   <si>
     <t>ForwardAnimation</t>
+  </si>
+  <si>
+    <t>DieAnimation</t>
   </si>
   <si>
     <t>MaxAnimationScale</t>
@@ -1975,11 +1981,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
@@ -2293,30 +2302,30 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1" style="2"/>
+    <col min="1" max="2" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2329,7 +2338,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BV4"/>
+  <dimension ref="A1:BX4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
@@ -2399,13 +2408,15 @@
     <col min="65" max="65" width="9" customWidth="1" style="2"/>
     <col min="66" max="66" width="9" customWidth="1" style="2"/>
     <col min="67" max="67" width="39.58203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="14" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14.83203125" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="68" max="68" width="9" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14.83203125" customWidth="1" style="2"/>
     <col min="71" max="71" width="14" customWidth="1" style="2"/>
     <col min="72" max="72" width="14" customWidth="1" style="2"/>
     <col min="73" max="73" width="14" customWidth="1" style="2"/>
-    <col min="74" max="74" width="19.1640625" customWidth="1" style="2"/>
+    <col min="74" max="74" width="14" customWidth="1" style="2"/>
+    <col min="75" max="75" width="9" customWidth="1" style="2"/>
+    <col min="76" max="76" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2577,6 +2588,8 @@
       <c r="BT1" s="2"/>
       <c r="BU1" s="2"/>
       <c r="BV1" s="2"/>
+      <c r="BW1" s="2"/>
+      <c r="BX1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
@@ -2797,6 +2810,12 @@
       <c r="BV2" s="2" t="s">
         <v>121</v>
       </c>
+      <c r="BW2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BX2" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
@@ -2806,7 +2825,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2814,206 +2833,212 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AE3" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="AF3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="AQ3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AS3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="AT3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AW3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AX3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AY3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="BA3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BM3" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="BB3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="BK3" s="2" t="s">
+      <c r="BN3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BX3" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="4">
@@ -3021,17 +3046,17 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
@@ -3092,23 +3117,23 @@
         <v>4</v>
       </c>
       <c r="AK4" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AL4" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AM4" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AN4" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AO4" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AP4" s="2"/>
       <c r="AQ4" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AR4" s="2">
         <v>3</v>
@@ -3130,51 +3155,53 @@
       <c r="BC4" s="2"/>
       <c r="BD4" s="2"/>
       <c r="BE4" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BF4" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BG4" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BH4" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BI4" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="BJ4" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BK4" s="2">
         <v>6</v>
       </c>
       <c r="BL4" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BM4" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BN4" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BO4" s="2"/>
-      <c r="BP4" s="2" t="s">
-        <v>150</v>
-      </c>
+      <c r="BP4" s="2"/>
       <c r="BQ4" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="BR4" s="2"/>
-      <c r="BS4" s="2" t="s">
         <v>152</v>
       </c>
+      <c r="BR4" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BS4" s="2"/>
       <c r="BT4" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="BU4" s="2"/>
-      <c r="BV4" s="2">
+        <v>154</v>
+      </c>
+      <c r="BU4" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="BV4" s="2"/>
+      <c r="BW4" s="2"/>
+      <c r="BX4" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3192,1862 +3219,1862 @@
   <dimension ref="A1:DI519"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1" style="2"/>
-    <col min="3" max="3" width="7.75" customWidth="1" style="2"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1" style="2"/>
-    <col min="9" max="9" width="7.33203125" customWidth="1" style="2"/>
-    <col min="10" max="10" width="15.75" customWidth="1" style="2"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="11.75" customWidth="1" style="2"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1" style="2"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1" style="2"/>
-    <col min="17" max="17" width="21.5" customWidth="1" style="2"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1" style="2"/>
-    <col min="22" max="22" width="17.75" customWidth="1" style="2"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1" style="2"/>
-    <col min="24" max="24" width="18.5" customWidth="1" style="2"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1" style="2"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1" style="2"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1" style="2"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1" style="2"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1" style="2"/>
-    <col min="32" max="32" width="13.75" customWidth="1" style="2"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1" style="2"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1" style="2"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="12.5" customWidth="1" style="2"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1" style="2"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="15" customWidth="1" style="2"/>
-    <col min="41" max="41" width="13.25" customWidth="1" style="2"/>
-    <col min="42" max="45" width="11.83203125" customWidth="1" style="2"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1" style="2"/>
-    <col min="47" max="47" width="12.25" customWidth="1" style="2"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1" style="2"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1" style="2"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1" style="2"/>
-    <col min="51" max="51" width="9" customWidth="1" style="2"/>
-    <col min="52" max="52" width="7" customWidth="1" style="2"/>
-    <col min="53" max="53" width="11.75" customWidth="1" style="2"/>
-    <col min="54" max="54" width="19.75" customWidth="1" style="2"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1" style="2"/>
-    <col min="56" max="56" width="8.5" customWidth="1" style="2"/>
-    <col min="57" max="57" width="13.5" customWidth="1" style="2"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1" style="2"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1" style="2"/>
-    <col min="60" max="60" width="8.25" customWidth="1" style="2"/>
-    <col min="61" max="67" width="8.33203125" customWidth="1" style="2"/>
-    <col min="68" max="70" width="11.25" customWidth="1" style="2"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1" style="2"/>
-    <col min="72" max="73" width="8" customWidth="1" style="2"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1" style="2"/>
-    <col min="75" max="76" width="8.5" customWidth="1" style="2"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1" style="2"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1" style="2"/>
-    <col min="80" max="80" width="13.5" customWidth="1" style="2"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1" style="2"/>
-    <col min="82" max="82" width="15.75" customWidth="1" style="2"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1" style="2"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1" style="2"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1" style="2"/>
-    <col min="86" max="86" width="9" customWidth="1" style="2"/>
-    <col min="87" max="87" width="16" customWidth="1" style="2"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1" style="2"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1" style="2"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1" style="2"/>
-    <col min="92" max="92" width="17.08203125" customWidth="1" style="2"/>
-    <col min="93" max="93" width="9.5" customWidth="1" style="2"/>
-    <col min="94" max="98" width="9" customWidth="1" style="2"/>
-    <col min="99" max="99" width="14" customWidth="1" style="2"/>
-    <col min="100" max="100" width="8" customWidth="1" style="2"/>
-    <col min="101" max="101" width="9" customWidth="1" style="2"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1" style="2"/>
-    <col min="103" max="103" width="13.75" customWidth="1" style="2"/>
-    <col min="104" max="104" width="9.5" customWidth="1" style="2"/>
-    <col min="105" max="106" width="9" customWidth="1" style="2"/>
-    <col min="107" max="108" width="9.5" customWidth="1" style="2"/>
-    <col min="109" max="109" width="9" customWidth="1" style="2"/>
-    <col min="110" max="110" width="15.5" customWidth="1" style="2"/>
-    <col min="111" max="111" width="9" customWidth="1" style="2"/>
-    <col min="112" max="113" width="9.5" customWidth="1" style="2"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1" style="3"/>
+    <col min="3" max="3" width="7.75" customWidth="1" style="3"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1" style="3"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1" style="3"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1" style="3"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1" style="3"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1" style="3"/>
+    <col min="9" max="9" width="7.33203125" customWidth="1" style="3"/>
+    <col min="10" max="10" width="15.75" customWidth="1" style="3"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1" style="3"/>
+    <col min="14" max="14" width="11.75" customWidth="1" style="3"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1" style="3"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1" style="3"/>
+    <col min="17" max="17" width="21.5" customWidth="1" style="3"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1" style="3"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1" style="3"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1" style="3"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1" style="3"/>
+    <col min="22" max="22" width="17.75" customWidth="1" style="3"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1" style="3"/>
+    <col min="24" max="24" width="18.5" customWidth="1" style="3"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1" style="3"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1" style="3"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1" style="3"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1" style="3"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1" style="3"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1" style="3"/>
+    <col min="32" max="32" width="13.75" customWidth="1" style="3"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1" style="3"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1" style="3"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1" style="3"/>
+    <col min="36" max="36" width="12.5" customWidth="1" style="3"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1" style="3"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1" style="3"/>
+    <col min="40" max="40" width="15" customWidth="1" style="3"/>
+    <col min="41" max="41" width="13.25" customWidth="1" style="3"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1" style="3"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1" style="3"/>
+    <col min="47" max="47" width="12.25" customWidth="1" style="3"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1" style="3"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1" style="3"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1" style="3"/>
+    <col min="51" max="51" width="9" customWidth="1" style="3"/>
+    <col min="52" max="52" width="7" customWidth="1" style="3"/>
+    <col min="53" max="53" width="11.75" customWidth="1" style="3"/>
+    <col min="54" max="54" width="19.75" customWidth="1" style="3"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1" style="3"/>
+    <col min="56" max="56" width="8.5" customWidth="1" style="3"/>
+    <col min="57" max="57" width="13.5" customWidth="1" style="3"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1" style="3"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1" style="3"/>
+    <col min="60" max="60" width="8.25" customWidth="1" style="3"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1" style="3"/>
+    <col min="68" max="70" width="11.25" customWidth="1" style="3"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1" style="3"/>
+    <col min="72" max="73" width="8" customWidth="1" style="3"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1" style="3"/>
+    <col min="75" max="76" width="8.5" customWidth="1" style="3"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1" style="3"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1" style="3"/>
+    <col min="80" max="80" width="13.5" customWidth="1" style="3"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1" style="3"/>
+    <col min="82" max="82" width="15.75" customWidth="1" style="3"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1" style="3"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1" style="3"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1" style="3"/>
+    <col min="86" max="86" width="9" customWidth="1" style="3"/>
+    <col min="87" max="87" width="16" customWidth="1" style="3"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1" style="3"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1" style="3"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1" style="3"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1" style="3"/>
+    <col min="93" max="93" width="9.5" customWidth="1" style="3"/>
+    <col min="94" max="98" width="9" customWidth="1" style="3"/>
+    <col min="99" max="99" width="14" customWidth="1" style="3"/>
+    <col min="100" max="100" width="8" customWidth="1" style="3"/>
+    <col min="101" max="101" width="9" customWidth="1" style="3"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1" style="3"/>
+    <col min="103" max="103" width="13.75" customWidth="1" style="3"/>
+    <col min="104" max="104" width="9.5" customWidth="1" style="3"/>
+    <col min="105" max="106" width="9" customWidth="1" style="3"/>
+    <col min="107" max="108" width="9.5" customWidth="1" style="3"/>
+    <col min="109" max="109" width="9" customWidth="1" style="3"/>
+    <col min="110" max="110" width="15.5" customWidth="1" style="3"/>
+    <col min="111" max="111" width="9" customWidth="1" style="3"/>
+    <col min="112" max="113" width="9.5" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="V1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="U1" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="V1" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AE1" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AH1" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AI1" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AK1" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AL1" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AM1" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AN1" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AO1" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AP1" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AR1" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AS1" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AT1" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AU1" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AV1" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AW1" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AX1" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="AY1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BA1" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BB1" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BC1" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BD1" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BE1" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BF1" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="BJ1" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BG1" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BH1" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BJ1" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="BK1" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BL1" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BM1" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BN1" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="BQ1" s="2" t="s">
+      <c r="BO1" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BP1" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BQ1" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="BT1" s="2" t="s">
+      <c r="BR1" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BS1" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="BV1" s="2" t="s">
+      <c r="BT1" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="BW1" s="2" t="s">
+      <c r="BU1" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="BX1" s="2" t="s">
+      <c r="BV1" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="BY1" s="2" t="s">
+      <c r="BW1" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="BZ1" s="2" t="s">
+      <c r="BX1" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="CA1" s="2" t="s">
+      <c r="BY1" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="CB1" s="2" t="s">
+      <c r="BZ1" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="CC1" s="2" t="s">
+      <c r="CA1" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="CD1" s="2" t="s">
+      <c r="CB1" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="CE1" s="2" t="s">
+      <c r="CC1" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="CF1" s="2" t="s">
+      <c r="CD1" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="CG1" s="2" t="s">
+      <c r="CE1" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="CH1" s="2" t="s">
+      <c r="CF1" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="CI1" s="2" t="s">
+      <c r="CG1" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CH1" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="CK1" s="2" t="s">
+      <c r="CI1" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CJ1" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="CM1" s="2" t="s">
+      <c r="CK1" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="CN1" s="2" t="s">
+      <c r="CL1" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="CO1" s="2" t="s">
+      <c r="CM1" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="CP1" s="2" t="s">
+      <c r="CN1" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="CQ1" s="2" t="s">
+      <c r="CO1" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="CR1" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="CS1" s="2" t="s">
+      <c r="CP1" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="CT1" s="2" t="s">
+      <c r="CQ1" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="CU1" s="2" t="s">
+      <c r="CR1" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="CS1" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="CV1" s="2" t="s">
+      <c r="CT1" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="CW1" s="2" t="s">
+      <c r="CU1" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="CX1" s="2" t="s">
+      <c r="CV1" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="CY1" s="2" t="s">
+      <c r="CW1" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="CZ1" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="DA1" s="2" t="s">
+      <c r="CX1" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="DB1" s="2" t="s">
+      <c r="CY1" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="DC1" s="2" t="s">
+      <c r="CZ1" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="DA1" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="DD1" s="2" t="s">
+      <c r="DB1" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="DE1" s="2" t="s">
+      <c r="DC1" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="DF1" s="2" t="s">
+      <c r="DD1" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="DG1" s="2" t="s">
+      <c r="DE1" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="DH1" s="2" t="s">
+      <c r="DF1" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="DI1" s="2" t="s">
+      <c r="DG1" s="3" t="s">
         <v>258</v>
       </c>
+      <c r="DH1" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="DI1" s="3" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="R2" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="S2" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="T2" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="U2" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="V2" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="W2" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="X2" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="Y2" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="Z2" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AA2" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AB2" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AC2" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AD2" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AE2" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AF2" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AG2" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AH2" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AI2" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AJ2" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AK2" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AL2" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AM2" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AN2" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AO2" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AP2" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AQ2" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AR2" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AS2" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AT2" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="AU2" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AV2" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="AW2" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="AX2" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="AY2" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="AZ2" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BA2" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="BD2" s="2" t="s">
+      <c r="BB2" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="BE2" s="2" t="s">
+      <c r="BC2" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BD2" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BE2" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BF2" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BG2" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BH2" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BI2" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BJ2" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BK2" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BL2" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="BO2" s="2" t="s">
+      <c r="BM2" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="BN2" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="BO2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="BP2" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="BQ2" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="BR2" s="2" t="s">
+      <c r="BP2" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BQ2" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="BT2" s="2" t="s">
+      <c r="BR2" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="BU2" s="2" t="s">
+      <c r="BS2" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="BT2" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="BU2" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="BV2" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="BW2" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="BX2" s="2" t="s">
+      <c r="BV2" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="BY2" s="2" t="s">
+      <c r="BW2" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="BZ2" s="2" t="s">
+      <c r="BX2" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="CA2" s="2" t="s">
+      <c r="BY2" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="CB2" s="2" t="s">
+      <c r="BZ2" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="CC2" s="2" t="s">
+      <c r="CA2" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="CD2" s="2" t="s">
+      <c r="CB2" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="CE2" s="2" t="s">
+      <c r="CC2" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="CF2" s="2" t="s">
+      <c r="CD2" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="CG2" s="2" t="s">
+      <c r="CE2" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="CH2" s="2" t="s">
+      <c r="CF2" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="CI2" s="2" t="s">
+      <c r="CG2" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="CJ2" s="2" t="s">
+      <c r="CH2" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="CK2" s="2" t="s">
+      <c r="CI2" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="CL2" s="2" t="s">
+      <c r="CJ2" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="CM2" s="2" t="s">
+      <c r="CK2" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="CN2" s="2" t="s">
+      <c r="CL2" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="CO2" s="2" t="s">
+      <c r="CM2" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="CP2" s="2" t="s">
+      <c r="CN2" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="CQ2" s="2" t="s">
+      <c r="CO2" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="CR2" s="2" t="s">
+      <c r="CP2" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="CS2" s="2" t="s">
+      <c r="CQ2" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="CT2" s="2" t="s">
+      <c r="CR2" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="CU2" s="2" t="s">
+      <c r="CS2" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="CV2" s="2" t="s">
+      <c r="CT2" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="CW2" s="2" t="s">
+      <c r="CU2" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="CX2" s="2" t="s">
+      <c r="CV2" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="CY2" s="2" t="s">
+      <c r="CW2" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="CZ2" s="2" t="s">
+      <c r="CX2" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="DA2" s="2" t="s">
+      <c r="CY2" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="DB2" s="2" t="s">
+      <c r="CZ2" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="DC2" s="2" t="s">
+      <c r="DA2" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="DD2" s="2" t="s">
+      <c r="DB2" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="DE2" s="2" t="s">
+      <c r="DC2" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="DF2" s="2" t="s">
+      <c r="DD2" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="DG2" s="2" t="s">
+      <c r="DE2" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="DH2" s="2" t="s">
+      <c r="DF2" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="DI2" s="2" t="s">
+      <c r="DG2" s="3" t="s">
         <v>364</v>
       </c>
+      <c r="DH2" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="DI2" s="3" t="s">
+        <v>366</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="M3" s="2" t="s">
+      <c r="U3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="V3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="W3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AI3" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AJ3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AO3" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="AU3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AW3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AX3" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="AY3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BA3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BB3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BC3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BE3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BF3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH3" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="BI3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BJ3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BK3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BL3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BM3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BO3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="BP3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC3" s="2" t="s">
+      <c r="BQ3" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="BR3" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="BS3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="AD3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI3" s="2" t="s">
+      <c r="BT3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BU3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BV3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BW3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BX3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BY3" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="BZ3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CA3" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="CB3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CC3" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="CD3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CE3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CF3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CG3" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="CH3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="CI3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="CK3" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="CL3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CM3" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="CN3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="CO3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CP3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CR3" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="CS3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CT3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CU3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CV3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="CW3" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="CX3" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="CY3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="CZ3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="DA3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="DB3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="DC3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="DD3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DE3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DF3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DG3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DH3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DI3" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="AC5" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO5" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="AT5" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="AX5" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="AZ5" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CB5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="CG5" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="CY5" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="BD6" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO6" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="BS6" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CN6" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="CO6" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="CR6" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO7" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="AT7" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="BD7" s="3">
+        <v>99</v>
+      </c>
+      <c r="BO7" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="BS7" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CN7" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="CR7" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO8" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="AV8" s="3">
+        <v>99</v>
+      </c>
+      <c r="AX8" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="AZ8" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="BD8" s="3">
+        <v>99</v>
+      </c>
+      <c r="BS8" s="3">
+        <v>1</v>
+      </c>
+      <c r="CL8" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="G10" s="3">
         <v>3</v>
       </c>
-      <c r="AK3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT3" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AV3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AW3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="AY3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BA3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BK3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BW3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BX3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BY3" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="BZ3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CA3" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="CB3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CC3" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="CD3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CE3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CF3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CG3" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="CH3" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="CI3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="CJ3" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="CK3" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="CL3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CM3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CP3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CQ3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CR3" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="CS3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CT3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CU3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CV3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="CW3" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="CX3" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="CY3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="CZ3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="DA3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="DB3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="DC3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="DD3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DF3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DG3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DH3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DI3" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="AC5" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO5" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="AT5" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="AX5" s="2" t="s">
+      <c r="J10" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="BD10" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO10" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="BT10" s="3">
+        <v>30</v>
+      </c>
+      <c r="BV10" s="3">
+        <v>0</v>
+      </c>
+      <c r="BW10" s="3">
+        <v>16</v>
+      </c>
+      <c r="BX10" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY10" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="CG10" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="CN10" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="CO10" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="CP10" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="CR10" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="AC11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="BD11" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN11" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="CO11" s="3">
+        <v>1</v>
+      </c>
+      <c r="CR11" s="3">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO12" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="AZ5" s="2">
+      <c r="AT12" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="AX12" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="AZ12" s="3">
         <v>1</v>
       </c>
-      <c r="BD5" s="2">
+      <c r="BD12" s="3">
         <v>1</v>
       </c>
-      <c r="CB5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="CG5" s="2" t="s">
+      <c r="CB12" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="CG12" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="CY12" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="I13" s="3">
+        <v>1</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD13" s="3">
+        <v>1</v>
+      </c>
+      <c r="CL13" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="CY13" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="DD13" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="G15" s="3">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="AT15" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="BD15" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO15" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="BP15" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="BT15" s="3">
+        <v>20</v>
+      </c>
+      <c r="BV15" s="3">
+        <v>20</v>
+      </c>
+      <c r="BW15" s="3">
+        <v>26</v>
+      </c>
+      <c r="BX15" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY15" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="CB15" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="CG15" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="CN15" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="CO15" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="CP15" s="3">
+        <v>2.9</v>
+      </c>
+      <c r="CQ15" s="3">
+        <v>2</v>
+      </c>
+      <c r="CR15" s="3">
+        <v>20</v>
+      </c>
+      <c r="CW15" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AC16" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO16" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="AP16" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="AT16" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="AX16" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="AZ16" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD16" s="3">
+        <v>99</v>
+      </c>
+      <c r="CU16" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO17" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="AT17" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="CY5" s="2" t="s">
+      <c r="AX17" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="AZ17" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD17" s="3">
+        <v>1</v>
+      </c>
+      <c r="CB17" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="CG17" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="CY17" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="G19" s="3">
+        <v>3</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="AC19" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="BD19" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO19" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="BP19" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="BT19" s="3">
+        <v>45</v>
+      </c>
+      <c r="BV19" s="3">
+        <v>42</v>
+      </c>
+      <c r="BW19" s="3">
+        <v>55</v>
+      </c>
+      <c r="BX19" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY19" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="CG19" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="CN19" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="CO19" s="3">
+        <v>1.1</v>
+      </c>
+      <c r="CP19" s="3">
+        <v>1.1</v>
+      </c>
+      <c r="CQ19" s="3">
+        <v>1.1</v>
+      </c>
+      <c r="CR19" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO20" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="AX20" s="3" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="AZ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="BB20" s="3">
+        <v>2</v>
+      </c>
+      <c r="BD20" s="3">
+        <v>1</v>
+      </c>
+      <c r="CL20" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="CU20" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="CY20" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO21" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="AT21" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="AX21" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="AZ21" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD21" s="3">
+        <v>1</v>
+      </c>
+      <c r="CB21" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="CG21" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="CY21" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="AC6" s="2">
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="I22" s="3">
         <v>1</v>
       </c>
-      <c r="AG6" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="BD6" s="2">
+      <c r="K22" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AC22" s="3">
         <v>1</v>
       </c>
-      <c r="BO6" s="2" t="s">
+      <c r="AG22" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="BD22" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS22" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="CB22" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="CG22" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="DD22" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG22" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH22" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="BS6" s="2">
+      <c r="I23" s="3">
+        <v>1</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG23" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="BD23" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS23" s="3">
+        <v>0.1667</v>
+      </c>
+      <c r="CB23" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="CG23" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="DD23" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG23" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH23" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="CL499" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="CL501" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="CL502" s="3">
         <v>0.1</v>
       </c>
-      <c r="CN6" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="CO6" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="CR6" s="2">
+    </row>
+    <row r="504">
+      <c r="CL504" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="AC7" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO7" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="AT7" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="BD7" s="2">
-        <v>99</v>
-      </c>
-      <c r="BO7" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="BS7" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CN7" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="CR7" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="AC8" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO8" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="AV8" s="2">
-        <v>99</v>
-      </c>
-      <c r="AX8" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="AZ8" s="2">
+    <row r="511">
+      <c r="CL511" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="CL513" s="3">
         <v>0.4</v>
       </c>
-      <c r="BD8" s="2">
-        <v>99</v>
-      </c>
-      <c r="BS8" s="2">
-        <v>1</v>
-      </c>
-      <c r="CL8" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="G10" s="2">
-        <v>3</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="AC10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="BD10" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO10" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="BT10" s="2">
-        <v>30</v>
-      </c>
-      <c r="BV10" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW10" s="2">
-        <v>16</v>
-      </c>
-      <c r="BX10" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY10" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="CG10" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="CN10" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="CO10" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="CP10" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="CR10" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="AC11" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="BD11" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN11" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="CO11" s="2">
-        <v>1</v>
-      </c>
-      <c r="CR11" s="2">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="AC12" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO12" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="AT12" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="AX12" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="AZ12" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD12" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB12" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="CG12" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="CY12" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="AC13" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD13" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE13" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD13" s="2">
-        <v>1</v>
-      </c>
-      <c r="CL13" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="CY13" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="DD13" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH13" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="G15" s="2">
-        <v>3</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="AC15" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG15" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="AT15" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="BD15" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO15" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="BP15" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="BT15" s="2">
-        <v>20</v>
-      </c>
-      <c r="BV15" s="2">
-        <v>20</v>
-      </c>
-      <c r="BW15" s="2">
-        <v>26</v>
-      </c>
-      <c r="BX15" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY15" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="CB15" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="CG15" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="CN15" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="CO15" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="CP15" s="2">
-        <v>2.9</v>
-      </c>
-      <c r="CQ15" s="2">
-        <v>2</v>
-      </c>
-      <c r="CR15" s="2">
-        <v>20</v>
-      </c>
-      <c r="CW15" s="2" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="AC16" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO16" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="AP16" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="AT16" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="AX16" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="AZ16" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD16" s="2">
-        <v>99</v>
-      </c>
-      <c r="CU16" s="2" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="AC17" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO17" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="AT17" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="AX17" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="AZ17" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD17" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB17" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="CG17" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="CY17" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="G19" s="2">
-        <v>3</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="AC19" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG19" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="BD19" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO19" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="BP19" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="BT19" s="2">
-        <v>45</v>
-      </c>
-      <c r="BV19" s="2">
-        <v>42</v>
-      </c>
-      <c r="BW19" s="2">
-        <v>55</v>
-      </c>
-      <c r="BX19" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY19" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="CG19" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="CN19" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="CO19" s="2">
-        <v>1.1</v>
-      </c>
-      <c r="CP19" s="2">
-        <v>1.1</v>
-      </c>
-      <c r="CQ19" s="2">
-        <v>1.1</v>
-      </c>
-      <c r="CR19" s="2">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="AC20" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO20" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="AX20" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="AZ20" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB20" s="2">
-        <v>2</v>
-      </c>
-      <c r="BD20" s="2">
-        <v>1</v>
-      </c>
-      <c r="CL20" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="CU20" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="CY20" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="AC21" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO21" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="AT21" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="AX21" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="AZ21" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD21" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB21" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="CG21" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="CY21" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="I22" s="2">
-        <v>1</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="AC22" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG22" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="BD22" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS22" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="CB22" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="CG22" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="DD22" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG22" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH22" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="I23" s="2">
-        <v>1</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="AC23" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG23" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="BD23" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS23" s="2">
-        <v>0.1667</v>
-      </c>
-      <c r="CB23" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="CG23" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="DD23" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG23" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH23" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="499">
-      <c r="CL499" s="2">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="501">
-      <c r="CL501" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="502">
-      <c r="CL502" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="504">
-      <c r="CL504" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="511">
-      <c r="CL511" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="513">
-      <c r="CL513" s="2">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="514">
-      <c r="CL514" s="2">
+      <c r="CL514" s="3">
         <v>0.6</v>
       </c>
     </row>
     <row r="517">
-      <c r="CL517" s="2">
+      <c r="CL517" s="3">
         <v>0.5</v>
       </c>
     </row>
     <row r="518">
-      <c r="CL518" s="2">
+      <c r="CL518" s="3">
         <v>0.667</v>
       </c>
     </row>
     <row r="519">
-      <c r="CL519" s="2">
+      <c r="CL519" s="3">
         <v>0.2</v>
       </c>
     </row>
@@ -5065,216 +5092,216 @@
   <dimension ref="A1:Q279"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1" style="2"/>
-    <col min="2" max="2" width="31.25" customWidth="1" style="2"/>
-    <col min="3" max="6" width="9" customWidth="1" style="2"/>
-    <col min="7" max="7" width="18.75" customWidth="1" style="2"/>
-    <col min="8" max="8" width="15" customWidth="1" style="2"/>
-    <col min="9" max="13" width="9" customWidth="1" style="2"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1" style="2"/>
-    <col min="15" max="15" width="9.5" customWidth="1" style="2"/>
-    <col min="16" max="16" width="22.1640625" customWidth="1" style="2"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="13" customWidth="1" style="3"/>
+    <col min="2" max="2" width="31.25" customWidth="1" style="3"/>
+    <col min="3" max="6" width="9" customWidth="1" style="3"/>
+    <col min="7" max="7" width="18.75" customWidth="1" style="3"/>
+    <col min="8" max="8" width="15" customWidth="1" style="3"/>
+    <col min="9" max="13" width="9" customWidth="1" style="3"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1" style="3"/>
+    <col min="15" max="15" width="9.5" customWidth="1" style="3"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1" style="3"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>460</v>
       </c>
+      <c r="O1" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>350</v>
+      <c r="O2" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>132</v>
+      <c r="L3" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="A4" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="F4" s="3">
         <v>1</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>473</v>
+      <c r="Q4" s="3" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="A5" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="F5" s="2">
+      <c r="Q7" s="3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H9" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="H9" s="2">
+      <c r="Q9" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="P278" s="3">
         <v>1</v>
       </c>
-      <c r="Q9" s="2" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="P278" s="2">
-        <v>1</v>
-      </c>
     </row>
     <row r="279">
-      <c r="P279" s="2">
+      <c r="P279" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5291,46 +5318,46 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="11.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="27.5" customWidth="1" style="2"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="11.25" customWidth="1" style="3"/>
+    <col min="3" max="3" width="9" customWidth="1" style="3"/>
+    <col min="4" max="4" width="27.5" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>478</v>
+      <c r="C1" s="3" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>350</v>
+      <c r="C2" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>132</v>
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -5346,80 +5373,80 @@
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="27.25" customWidth="1" style="2"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
+    <col min="2" max="2" width="9" customWidth="1" style="3"/>
+    <col min="3" max="3" width="27.25" customWidth="1" style="3"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1" style="3"/>
+    <col min="5" max="10" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="I1" s="2" t="s">
-        <v>235</v>
+      <c r="I1" s="3" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>350</v>
+      <c r="G2" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>132</v>
+      <c r="F3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -5435,123 +5462,123 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28" customWidth="1" style="2"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="11.25" customWidth="1" style="2"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1" style="2"/>
-    <col min="12" max="12" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
+    <col min="2" max="2" width="28" customWidth="1" style="3"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1" style="3"/>
+    <col min="5" max="10" width="11.25" customWidth="1" style="3"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1" style="3"/>
+    <col min="12" max="12" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>493</v>
       </c>
+      <c r="K1" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>495</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="I2" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -5568,45 +5595,45 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="16.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1" style="2"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="10.25" customWidth="1" style="2"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1" style="2"/>
-    <col min="7" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="16.25" customWidth="1" style="3"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1" style="3"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1" style="3"/>
+    <col min="5" max="5" width="10.25" customWidth="1" style="3"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1" style="3"/>
+    <col min="7" max="9" width="9" customWidth="1" style="3"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -5624,22 +5651,22 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -5654,147 +5681,147 @@
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5" customWidth="1" style="2"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1" style="2"/>
-    <col min="3" max="3" width="21.9140625" customWidth="1" style="2"/>
-    <col min="4" max="4" width="16.25" customWidth="1" style="2"/>
-    <col min="5" max="5" width="14" customWidth="1" style="2"/>
-    <col min="6" max="7" width="15.1640625" customWidth="1" style="2"/>
-    <col min="8" max="8" width="12.9140625" customWidth="1" style="2"/>
-    <col min="9" max="9" width="14" customWidth="1" style="2"/>
+    <col min="1" max="1" width="7.5" customWidth="1" style="3"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1" style="3"/>
+    <col min="3" max="3" width="21.9140625" customWidth="1" style="3"/>
+    <col min="4" max="4" width="16.25" customWidth="1" style="3"/>
+    <col min="5" max="5" width="14" customWidth="1" style="3"/>
+    <col min="6" max="7" width="15.1640625" customWidth="1" style="3"/>
+    <col min="8" max="8" width="12.9140625" customWidth="1" style="3"/>
+    <col min="9" max="9" width="14" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>515</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>517</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>523</v>
       </c>
+      <c r="H2" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="C4" s="2">
+      <c r="A4" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="C4" s="3">
         <v>1</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>530</v>
       </c>
+      <c r="H4" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="A5" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="B5" s="3">
         <v>1</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>1</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>534</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>536</v>
       </c>
     </row>
   </sheetData>
